--- a/fon_kategori_eslestirme.xlsx
+++ b/fon_kategori_eslestirme.xlsx
@@ -10,7 +10,7 @@
     <sheet sheetId="1" r:id="rId1" name="fon_kategori_eslestirme"/>
   </sheets>
   <definedNames>
-    <definedName name="fon_kategori_eslestirme">'fon_kategori_eslestirme'!$A$1:$F$1039</definedName>
+    <definedName name="fon_kategori_eslestirme">'fon_kategori_eslestirme'!$A$1:$F$1041</definedName>
   </definedNames>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
@@ -343,7 +343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1039"/>
+  <dimension ref="A1:F1041"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row outlineLevel="0" r="1">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="D27" s="0" t="inlineStr">
         <is>
-          <t>Kira Sertifikası</t>
+          <t>Para Piyasası</t>
         </is>
       </c>
       <c r="E27" s="0" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="D70" s="0" t="inlineStr">
         <is>
-          <t>Tematik</t>
+          <t>İstatiksel Arbitraj</t>
         </is>
       </c>
       <c r="E70" s="0" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="E97" s="0" t="inlineStr">
         <is>
-          <t>GLOBAL</t>
+          <t>GLOBAL MD</t>
         </is>
       </c>
       <c r="F97" s="0" t="inlineStr">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="E156" s="0" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A1 CAPİTAL</t>
         </is>
       </c>
       <c r="F156" s="0" t="inlineStr">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="E297" s="0" t="inlineStr">
         <is>
-          <t>GLOBAL</t>
+          <t>GLOBAL MD</t>
         </is>
       </c>
       <c r="F297" s="0" t="inlineStr">
@@ -10225,7 +10225,7 @@
       </c>
       <c r="E309" s="0" t="inlineStr">
         <is>
-          <t>GOLDEN</t>
+          <t>GOLDEN GLOBAL</t>
         </is>
       </c>
       <c r="F309" s="0" t="inlineStr">
@@ -10348,7 +10348,7 @@
       </c>
       <c r="D313" s="0" t="inlineStr">
         <is>
-          <t>Diğer Katılım</t>
+          <t>Çoklu Varlık</t>
         </is>
       </c>
       <c r="E313" s="0" t="inlineStr">
@@ -17292,7 +17292,7 @@
       </c>
       <c r="D530" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi</t>
+          <t>İstatiksel Arbitraj</t>
         </is>
       </c>
       <c r="E530" s="0" t="inlineStr">
@@ -19121,7 +19121,7 @@
       </c>
       <c r="E587" s="0" t="inlineStr">
         <is>
-          <t>MARMARA</t>
+          <t>MARMARA CAPITAL</t>
         </is>
       </c>
       <c r="F587" s="0" t="inlineStr">
@@ -26813,27 +26813,27 @@
     <row outlineLevel="0" r="828">
       <c r="A828" s="0" t="inlineStr">
         <is>
-          <t>SFS</t>
+          <t>SD1</t>
         </is>
       </c>
       <c r="B828" s="0" t="inlineStr">
         <is>
-          <t>AZİMUT PORTFÖY AGRESİF FON SEPETİ FONU</t>
+          <t>SPARTA PORTFÖY BİRİNCİ DEĞİŞKEN FON</t>
         </is>
       </c>
       <c r="C828" s="0" t="inlineStr">
         <is>
-          <t>Fon Sepeti Şemsiye Fonu</t>
+          <t>Değişken Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D828" s="0" t="inlineStr">
         <is>
-          <t>Fon Sepeti</t>
+          <t>Değişken</t>
         </is>
       </c>
       <c r="E828" s="0" t="inlineStr">
         <is>
-          <t>AZİMUT</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="F828" s="0" t="inlineStr">
@@ -26845,27 +26845,27 @@
     <row outlineLevel="0" r="829">
       <c r="A829" s="0" t="inlineStr">
         <is>
-          <t>SGT</t>
+          <t>SFS</t>
         </is>
       </c>
       <c r="B829" s="0" t="inlineStr">
         <is>
-          <t>GARANTİ PORTFÖY SİBER GÜVENLİK TEKNOLOJİLERİ DEĞİŞKEN FON</t>
+          <t>AZİMUT PORTFÖY AGRESİF FON SEPETİ FONU</t>
         </is>
       </c>
       <c r="C829" s="0" t="inlineStr">
         <is>
-          <t>Değişken Şemsiye Fonu</t>
+          <t>Fon Sepeti Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D829" s="0" t="inlineStr">
         <is>
-          <t>Teknoloji Temalı</t>
+          <t>Fon Sepeti</t>
         </is>
       </c>
       <c r="E829" s="0" t="inlineStr">
         <is>
-          <t>GARANTİ</t>
+          <t>AZİMUT</t>
         </is>
       </c>
       <c r="F829" s="0" t="inlineStr">
@@ -26877,12 +26877,12 @@
     <row outlineLevel="0" r="830">
       <c r="A830" s="0" t="inlineStr">
         <is>
-          <t>SHE</t>
+          <t>SGT</t>
         </is>
       </c>
       <c r="B830" s="0" t="inlineStr">
         <is>
-          <t>TEB PORTFÖY ÖNCE KADIN DEĞİŞKEN FON</t>
+          <t>GARANTİ PORTFÖY SİBER GÜVENLİK TEKNOLOJİLERİ DEĞİŞKEN FON</t>
         </is>
       </c>
       <c r="C830" s="0" t="inlineStr">
@@ -26892,12 +26892,12 @@
       </c>
       <c r="D830" s="0" t="inlineStr">
         <is>
-          <t>Tematik</t>
+          <t>Teknoloji Temalı</t>
         </is>
       </c>
       <c r="E830" s="0" t="inlineStr">
         <is>
-          <t>TEB</t>
+          <t>GARANTİ</t>
         </is>
       </c>
       <c r="F830" s="0" t="inlineStr">
@@ -26909,17 +26909,17 @@
     <row outlineLevel="0" r="831">
       <c r="A831" s="0" t="inlineStr">
         <is>
-          <t>SHU</t>
+          <t>SHC</t>
         </is>
       </c>
       <c r="B831" s="0" t="inlineStr">
         <is>
-          <t>SPARTA PORTFÖY ÜÇÜNCÜ HİSSE SENEDİ SERBEST (TL) FON (HİSSE SENEDİ YOĞUN FON)</t>
+          <t>STRATEJİ PORTFÖY İKİNCİ HİSSE SENEDİ FONU (HİSSE SENEDİ YOĞUN FON)</t>
         </is>
       </c>
       <c r="C831" s="0" t="inlineStr">
         <is>
-          <t>Serbest Şemsiye Fonu</t>
+          <t>Hisse Senedi Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D831" s="0" t="inlineStr">
@@ -26929,7 +26929,7 @@
       </c>
       <c r="E831" s="0" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>STRATEJİ</t>
         </is>
       </c>
       <c r="F831" s="0" t="inlineStr">
@@ -26941,27 +26941,27 @@
     <row outlineLevel="0" r="832">
       <c r="A832" s="0" t="inlineStr">
         <is>
-          <t>SKO</t>
+          <t>SHE</t>
         </is>
       </c>
       <c r="B832" s="0" t="inlineStr">
         <is>
-          <t>STRATEJİ PORTFÖY KAR PAYI ÖDEYEN HİSSE SENEDİ FONU (HİSSE SENEDİ YOĞUN FON)</t>
+          <t>TEB PORTFÖY ÖNCE KADIN DEĞİŞKEN FON</t>
         </is>
       </c>
       <c r="C832" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi Şemsiye Fonu</t>
+          <t>Değişken Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D832" s="0" t="inlineStr">
         <is>
-          <t>Kar Payı Ödeyen</t>
+          <t>Tematik</t>
         </is>
       </c>
       <c r="E832" s="0" t="inlineStr">
         <is>
-          <t>STRATEJİ</t>
+          <t>TEB</t>
         </is>
       </c>
       <c r="F832" s="0" t="inlineStr">
@@ -26973,12 +26973,12 @@
     <row outlineLevel="0" r="833">
       <c r="A833" s="0" t="inlineStr">
         <is>
-          <t>SKZ</t>
+          <t>SHU</t>
         </is>
       </c>
       <c r="B833" s="0" t="inlineStr">
         <is>
-          <t>NEO PORTFÖY SEKİZİNCİ SERBEST FON</t>
+          <t>SPARTA PORTFÖY ÜÇÜNCÜ HİSSE SENEDİ SERBEST (TL) FON (HİSSE SENEDİ YOĞUN FON)</t>
         </is>
       </c>
       <c r="C833" s="0" t="inlineStr">
@@ -26988,12 +26988,12 @@
       </c>
       <c r="D833" s="0" t="inlineStr">
         <is>
-          <t>Diğer Serbest</t>
+          <t>Hisse Senedi</t>
         </is>
       </c>
       <c r="E833" s="0" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="F833" s="0" t="inlineStr">
@@ -27005,12 +27005,12 @@
     <row outlineLevel="0" r="834">
       <c r="A834" s="0" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>SKO</t>
         </is>
       </c>
       <c r="B834" s="0" t="inlineStr">
         <is>
-          <t>QNB PORTFÖY ALGORİTMİK STRATEJİLER HİSSE SENEDİ FONU (HİSSE SENEDİ YOĞUN FON)</t>
+          <t>STRATEJİ PORTFÖY KAR PAYI ÖDEYEN HİSSE SENEDİ FONU (HİSSE SENEDİ YOĞUN FON)</t>
         </is>
       </c>
       <c r="C834" s="0" t="inlineStr">
@@ -27020,12 +27020,12 @@
       </c>
       <c r="D834" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi</t>
+          <t>Kar Payı Ödeyen</t>
         </is>
       </c>
       <c r="E834" s="0" t="inlineStr">
         <is>
-          <t>QNB</t>
+          <t>STRATEJİ</t>
         </is>
       </c>
       <c r="F834" s="0" t="inlineStr">
@@ -27037,12 +27037,12 @@
     <row outlineLevel="0" r="835">
       <c r="A835" s="0" t="inlineStr">
         <is>
-          <t>SNY</t>
+          <t>SKZ</t>
         </is>
       </c>
       <c r="B835" s="0" t="inlineStr">
         <is>
-          <t>ATLAS PORTFÖY SANAYİ SEKTÖRÜ HİSSE SENEDİ SERBEST FON (HİSSE SENEDİ YOĞUN FON)</t>
+          <t>NEO PORTFÖY SEKİZİNCİ SERBEST FON</t>
         </is>
       </c>
       <c r="C835" s="0" t="inlineStr">
@@ -27052,12 +27052,12 @@
       </c>
       <c r="D835" s="0" t="inlineStr">
         <is>
-          <t>Tematik</t>
+          <t>Diğer Serbest</t>
         </is>
       </c>
       <c r="E835" s="0" t="inlineStr">
         <is>
-          <t>ATLAS</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="F835" s="0" t="inlineStr">
@@ -27069,27 +27069,27 @@
     <row outlineLevel="0" r="836">
       <c r="A836" s="0" t="inlineStr">
         <is>
-          <t>SOS</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="B836" s="0" t="inlineStr">
         <is>
-          <t>HEDEF PORTFÖY SAĞLIK SEKTÖRÜ DEĞİŞKEN FON</t>
+          <t>QNB PORTFÖY ALGORİTMİK STRATEJİLER HİSSE SENEDİ FONU (HİSSE SENEDİ YOĞUN FON)</t>
         </is>
       </c>
       <c r="C836" s="0" t="inlineStr">
         <is>
-          <t>Değişken Şemsiye Fonu</t>
+          <t>Hisse Senedi Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D836" s="0" t="inlineStr">
         <is>
-          <t>Tematik</t>
+          <t>Hisse Senedi</t>
         </is>
       </c>
       <c r="E836" s="0" t="inlineStr">
         <is>
-          <t>HEDEF</t>
+          <t>QNB</t>
         </is>
       </c>
       <c r="F836" s="0" t="inlineStr">
@@ -27101,12 +27101,12 @@
     <row outlineLevel="0" r="837">
       <c r="A837" s="0" t="inlineStr">
         <is>
-          <t>SPE</t>
+          <t>SNY</t>
         </is>
       </c>
       <c r="B837" s="0" t="inlineStr">
         <is>
-          <t>AZIMUT PORTFÖY 5.0 SERBEST (DÖVIZ) FON</t>
+          <t>ATLAS PORTFÖY SANAYİ SEKTÖRÜ HİSSE SENEDİ SERBEST FON (HİSSE SENEDİ YOĞUN FON)</t>
         </is>
       </c>
       <c r="C837" s="0" t="inlineStr">
@@ -27116,44 +27116,44 @@
       </c>
       <c r="D837" s="0" t="inlineStr">
         <is>
-          <t>Döviz</t>
+          <t>Tematik</t>
         </is>
       </c>
       <c r="E837" s="0" t="inlineStr">
         <is>
-          <t>AZİMUT</t>
+          <t>ATLAS</t>
         </is>
       </c>
       <c r="F837" s="0" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>TL</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="838">
       <c r="A838" s="0" t="inlineStr">
         <is>
-          <t>SPN</t>
+          <t>SOS</t>
         </is>
       </c>
       <c r="B838" s="0" t="inlineStr">
         <is>
-          <t>AZİMUT PORTFÖY İSTATİSTİKSEL ARBİTRAJ HİSSE SENEDİ SERBEST FON (HİSSE SENEDİ YOĞUN FON)</t>
+          <t>HEDEF PORTFÖY SAĞLIK SEKTÖRÜ DEĞİŞKEN FON</t>
         </is>
       </c>
       <c r="C838" s="0" t="inlineStr">
         <is>
-          <t>Serbest Şemsiye Fonu</t>
+          <t>Değişken Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D838" s="0" t="inlineStr">
         <is>
-          <t>İstatiksel Arbitraj</t>
+          <t>Tematik</t>
         </is>
       </c>
       <c r="E838" s="0" t="inlineStr">
         <is>
-          <t>AZİMUT</t>
+          <t>HEDEF</t>
         </is>
       </c>
       <c r="F838" s="0" t="inlineStr">
@@ -27165,59 +27165,59 @@
     <row outlineLevel="0" r="839">
       <c r="A839" s="0" t="inlineStr">
         <is>
-          <t>SPP</t>
+          <t>SPE</t>
         </is>
       </c>
       <c r="B839" s="0" t="inlineStr">
         <is>
-          <t>SPARTA PORTFÖY BİRİNCİ PARA PİYASASI (TL) FONU</t>
+          <t>AZIMUT PORTFÖY 5.0 SERBEST (DÖVIZ) FON</t>
         </is>
       </c>
       <c r="C839" s="0" t="inlineStr">
         <is>
-          <t>Para Piyasası Şemsiye Fonu</t>
+          <t>Serbest Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D839" s="0" t="inlineStr">
         <is>
-          <t>Para Piyasası</t>
+          <t>Döviz</t>
         </is>
       </c>
       <c r="E839" s="0" t="inlineStr">
         <is>
-          <t>SPARTA</t>
+          <t>AZİMUT</t>
         </is>
       </c>
       <c r="F839" s="0" t="inlineStr">
         <is>
-          <t>TL</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="840">
       <c r="A840" s="0" t="inlineStr">
         <is>
-          <t>SPR</t>
+          <t>SPN</t>
         </is>
       </c>
       <c r="B840" s="0" t="inlineStr">
         <is>
-          <t>BV PORTFÖY SPOR ENDÜSTRİSİ DEĞİŞKEN FON</t>
+          <t>AZİMUT PORTFÖY İSTATİSTİKSEL ARBİTRAJ HİSSE SENEDİ SERBEST FON (HİSSE SENEDİ YOĞUN FON)</t>
         </is>
       </c>
       <c r="C840" s="0" t="inlineStr">
         <is>
-          <t>Değişken Şemsiye Fonu</t>
+          <t>Serbest Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D840" s="0" t="inlineStr">
         <is>
-          <t>Tematik</t>
+          <t>İstatiksel Arbitraj</t>
         </is>
       </c>
       <c r="E840" s="0" t="inlineStr">
         <is>
-          <t>BV</t>
+          <t>AZİMUT</t>
         </is>
       </c>
       <c r="F840" s="0" t="inlineStr">
@@ -27229,27 +27229,27 @@
     <row outlineLevel="0" r="841">
       <c r="A841" s="0" t="inlineStr">
         <is>
-          <t>SPT</t>
+          <t>SPP</t>
         </is>
       </c>
       <c r="B841" s="0" t="inlineStr">
         <is>
-          <t>AKTİF PORTFÖY KATILIM FON SEPETİ FONU</t>
+          <t>SPARTA PORTFÖY BİRİNCİ PARA PİYASASI (TL) FONU</t>
         </is>
       </c>
       <c r="C841" s="0" t="inlineStr">
         <is>
-          <t>Fon Sepeti Şemsiye Fonu</t>
+          <t>Para Piyasası Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D841" s="0" t="inlineStr">
         <is>
-          <t>Fon Sepeti</t>
+          <t>Para Piyasası</t>
         </is>
       </c>
       <c r="E841" s="0" t="inlineStr">
         <is>
-          <t>AKTİF</t>
+          <t>SPARTA</t>
         </is>
       </c>
       <c r="F841" s="0" t="inlineStr">
@@ -27261,27 +27261,27 @@
     <row outlineLevel="0" r="842">
       <c r="A842" s="0" t="inlineStr">
         <is>
-          <t>SRL</t>
+          <t>SPR</t>
         </is>
       </c>
       <c r="B842" s="0" t="inlineStr">
         <is>
-          <t>PARDUS PORTFÖY SÜRDÜRÜLEBİLİRLİK HİSSE SENEDİ (TL) FONU (HİSSE SENEDİ YOĞUN FON)</t>
+          <t>BV PORTFÖY SPOR ENDÜSTRİSİ DEĞİŞKEN FON</t>
         </is>
       </c>
       <c r="C842" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi Şemsiye Fonu</t>
+          <t>Değişken Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D842" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi</t>
+          <t>Tematik</t>
         </is>
       </c>
       <c r="E842" s="0" t="inlineStr">
         <is>
-          <t>PARDUS</t>
+          <t>BV</t>
         </is>
       </c>
       <c r="F842" s="0" t="inlineStr">
@@ -27293,27 +27293,27 @@
     <row outlineLevel="0" r="843">
       <c r="A843" s="0" t="inlineStr">
         <is>
-          <t>SSK</t>
+          <t>SPT</t>
         </is>
       </c>
       <c r="B843" s="0" t="inlineStr">
         <is>
-          <t>DENİZ PORTFÖY SAĞLIK SEKTÖRÜ DEĞİŞKEN FON</t>
+          <t>AKTİF PORTFÖY KATILIM FON SEPETİ FONU</t>
         </is>
       </c>
       <c r="C843" s="0" t="inlineStr">
         <is>
-          <t>Değişken Şemsiye Fonu</t>
+          <t>Fon Sepeti Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D843" s="0" t="inlineStr">
         <is>
-          <t>Tematik</t>
+          <t>Fon Sepeti</t>
         </is>
       </c>
       <c r="E843" s="0" t="inlineStr">
         <is>
-          <t>DENİZ</t>
+          <t>AKTİF</t>
         </is>
       </c>
       <c r="F843" s="0" t="inlineStr">
@@ -27325,12 +27325,12 @@
     <row outlineLevel="0" r="844">
       <c r="A844" s="0" t="inlineStr">
         <is>
-          <t>SSS</t>
+          <t>SRL</t>
         </is>
       </c>
       <c r="B844" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY SAVUNMA SANAYİİ ŞİRKETLERİ ENDEKSİ HİSSE SENEDİ FONU (HİSSE SENEDİ YOĞUN FON)</t>
+          <t>PARDUS PORTFÖY SÜRDÜRÜLEBİLİRLİK HİSSE SENEDİ (TL) FONU (HİSSE SENEDİ YOĞUN FON)</t>
         </is>
       </c>
       <c r="C844" s="0" t="inlineStr">
@@ -27340,12 +27340,12 @@
       </c>
       <c r="D844" s="0" t="inlineStr">
         <is>
-          <t>BIST Endeks</t>
+          <t>Hisse Senedi</t>
         </is>
       </c>
       <c r="E844" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ</t>
+          <t>PARDUS</t>
         </is>
       </c>
       <c r="F844" s="0" t="inlineStr">
@@ -27357,27 +27357,27 @@
     <row outlineLevel="0" r="845">
       <c r="A845" s="0" t="inlineStr">
         <is>
-          <t>ST1</t>
+          <t>SSK</t>
         </is>
       </c>
       <c r="B845" s="0" t="inlineStr">
         <is>
-          <t>STRATEJİ PORTFÖY BİRİNCİ HİSSE SENEDİ FONU (HİSSE SENEDİ YOĞUN FON)</t>
+          <t>DENİZ PORTFÖY SAĞLIK SEKTÖRÜ DEĞİŞKEN FON</t>
         </is>
       </c>
       <c r="C845" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi Şemsiye Fonu</t>
+          <t>Değişken Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D845" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi</t>
+          <t>Tematik</t>
         </is>
       </c>
       <c r="E845" s="0" t="inlineStr">
         <is>
-          <t>STRATEJİ</t>
+          <t>DENİZ</t>
         </is>
       </c>
       <c r="F845" s="0" t="inlineStr">
@@ -27389,27 +27389,27 @@
     <row outlineLevel="0" r="846">
       <c r="A846" s="0" t="inlineStr">
         <is>
-          <t>STI</t>
+          <t>SSS</t>
         </is>
       </c>
       <c r="B846" s="0" t="inlineStr">
         <is>
-          <t>ATLAS PORTFÖY SENTİMENT SERBEST FON</t>
+          <t>YAPI KREDİ PORTFÖY SAVUNMA SANAYİİ ŞİRKETLERİ ENDEKSİ HİSSE SENEDİ FONU (HİSSE SENEDİ YOĞUN FON)</t>
         </is>
       </c>
       <c r="C846" s="0" t="inlineStr">
         <is>
-          <t>Serbest Şemsiye Fonu</t>
+          <t>Hisse Senedi Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D846" s="0" t="inlineStr">
         <is>
-          <t>Diğer Serbest</t>
+          <t>BIST Endeks</t>
         </is>
       </c>
       <c r="E846" s="0" t="inlineStr">
         <is>
-          <t>ATLAS</t>
+          <t>YAPI KREDİ</t>
         </is>
       </c>
       <c r="F846" s="0" t="inlineStr">
@@ -27421,27 +27421,27 @@
     <row outlineLevel="0" r="847">
       <c r="A847" s="0" t="inlineStr">
         <is>
-          <t>SUA</t>
+          <t>ST1</t>
         </is>
       </c>
       <c r="B847" s="0" t="inlineStr">
         <is>
-          <t>ÜNLÜ PORTFÖY BİRİNCİ DEĞİŞKEN FON</t>
+          <t>STRATEJİ PORTFÖY BİRİNCİ HİSSE SENEDİ FONU (HİSSE SENEDİ YOĞUN FON)</t>
         </is>
       </c>
       <c r="C847" s="0" t="inlineStr">
         <is>
-          <t>Değişken Şemsiye Fonu</t>
+          <t>Hisse Senedi Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D847" s="0" t="inlineStr">
         <is>
-          <t>Değişken</t>
+          <t>Hisse Senedi</t>
         </is>
       </c>
       <c r="E847" s="0" t="inlineStr">
         <is>
-          <t>ÜNLÜ</t>
+          <t>STRATEJİ</t>
         </is>
       </c>
       <c r="F847" s="0" t="inlineStr">
@@ -27453,27 +27453,27 @@
     <row outlineLevel="0" r="848">
       <c r="A848" s="0" t="inlineStr">
         <is>
-          <t>SUB</t>
+          <t>STI</t>
         </is>
       </c>
       <c r="B848" s="0" t="inlineStr">
         <is>
-          <t>ÜNLÜ PORTFÖY İKİNCİ DEĞİŞKEN FON</t>
+          <t>ATLAS PORTFÖY SENTİMENT SERBEST FON</t>
         </is>
       </c>
       <c r="C848" s="0" t="inlineStr">
         <is>
-          <t>Değişken Şemsiye Fonu</t>
+          <t>Serbest Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D848" s="0" t="inlineStr">
         <is>
-          <t>Değişken</t>
+          <t>Diğer Serbest</t>
         </is>
       </c>
       <c r="E848" s="0" t="inlineStr">
         <is>
-          <t>ÜNLÜ</t>
+          <t>ATLAS</t>
         </is>
       </c>
       <c r="F848" s="0" t="inlineStr">
@@ -27485,12 +27485,12 @@
     <row outlineLevel="0" r="849">
       <c r="A849" s="0" t="inlineStr">
         <is>
-          <t>SUC</t>
+          <t>SUA</t>
         </is>
       </c>
       <c r="B849" s="0" t="inlineStr">
         <is>
-          <t>ÜNLÜ PORTFÖY ÜÇÜNCÜ DEĞIŞKEN FON</t>
+          <t>ÜNLÜ PORTFÖY BİRİNCİ DEĞİŞKEN FON</t>
         </is>
       </c>
       <c r="C849" s="0" t="inlineStr">
@@ -27517,27 +27517,27 @@
     <row outlineLevel="0" r="850">
       <c r="A850" s="0" t="inlineStr">
         <is>
-          <t>SUR</t>
+          <t>SUB</t>
         </is>
       </c>
       <c r="B850" s="0" t="inlineStr">
         <is>
-          <t>EMAA BLUE PORTFÖY SÜRDÜRÜLEBİLİRLİK HİSSE SENEDİ FONU (HİSSE SENEDİ YOĞUN FON)</t>
+          <t>ÜNLÜ PORTFÖY İKİNCİ DEĞİŞKEN FON</t>
         </is>
       </c>
       <c r="C850" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi Şemsiye Fonu</t>
+          <t>Değişken Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D850" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi</t>
+          <t>Değişken</t>
         </is>
       </c>
       <c r="E850" s="0" t="inlineStr">
         <is>
-          <t>EMAA BLUE</t>
+          <t>ÜNLÜ</t>
         </is>
       </c>
       <c r="F850" s="0" t="inlineStr">
@@ -27549,12 +27549,12 @@
     <row outlineLevel="0" r="851">
       <c r="A851" s="0" t="inlineStr">
         <is>
-          <t>SVB</t>
+          <t>SUC</t>
         </is>
       </c>
       <c r="B851" s="0" t="inlineStr">
         <is>
-          <t>STRATEJİ PORTFÖY AGRESİF DEĞİŞKEN FON</t>
+          <t>ÜNLÜ PORTFÖY ÜÇÜNCÜ DEĞIŞKEN FON</t>
         </is>
       </c>
       <c r="C851" s="0" t="inlineStr">
@@ -27569,7 +27569,7 @@
       </c>
       <c r="E851" s="0" t="inlineStr">
         <is>
-          <t>STRATEJİ</t>
+          <t>ÜNLÜ</t>
         </is>
       </c>
       <c r="F851" s="0" t="inlineStr">
@@ -27581,27 +27581,27 @@
     <row outlineLevel="0" r="852">
       <c r="A852" s="0" t="inlineStr">
         <is>
-          <t>TAL</t>
+          <t>SUR</t>
         </is>
       </c>
       <c r="B852" s="0" t="inlineStr">
         <is>
-          <t>ATLAS PORTFÖY ALTIN KATILIM FONU</t>
+          <t>EMAA BLUE PORTFÖY SÜRDÜRÜLEBİLİRLİK HİSSE SENEDİ FONU (HİSSE SENEDİ YOĞUN FON)</t>
         </is>
       </c>
       <c r="C852" s="0" t="inlineStr">
         <is>
-          <t>Kıymetli Madenler Şemsiye Fonu</t>
+          <t>Hisse Senedi Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D852" s="0" t="inlineStr">
         <is>
-          <t>Altın</t>
+          <t>Hisse Senedi</t>
         </is>
       </c>
       <c r="E852" s="0" t="inlineStr">
         <is>
-          <t>ATLAS</t>
+          <t>EMAA BLUE</t>
         </is>
       </c>
       <c r="F852" s="0" t="inlineStr">
@@ -27613,12 +27613,12 @@
     <row outlineLevel="0" r="853">
       <c r="A853" s="0" t="inlineStr">
         <is>
-          <t>TAR</t>
+          <t>SVB</t>
         </is>
       </c>
       <c r="B853" s="0" t="inlineStr">
         <is>
-          <t>AK PORTFÖY TARIM VE GIDA TEKNOLOJİLERİ DEĞİŞKEN FON</t>
+          <t>STRATEJİ PORTFÖY AGRESİF DEĞİŞKEN FON</t>
         </is>
       </c>
       <c r="C853" s="0" t="inlineStr">
@@ -27628,12 +27628,12 @@
       </c>
       <c r="D853" s="0" t="inlineStr">
         <is>
-          <t>Teknoloji Temalı</t>
+          <t>Değişken</t>
         </is>
       </c>
       <c r="E853" s="0" t="inlineStr">
         <is>
-          <t>AK</t>
+          <t>STRATEJİ</t>
         </is>
       </c>
       <c r="F853" s="0" t="inlineStr">
@@ -27645,27 +27645,27 @@
     <row outlineLevel="0" r="854">
       <c r="A854" s="0" t="inlineStr">
         <is>
-          <t>TAU</t>
+          <t>TAL</t>
         </is>
       </c>
       <c r="B854" s="0" t="inlineStr">
         <is>
-          <t>İŞ PORTFÖY BIST BANKA ENDEKSİ HİSSE SENEDİ (TL) FONU (HİSSE SENEDİ YOĞUN FON)</t>
+          <t>ATLAS PORTFÖY ALTIN KATILIM FONU</t>
         </is>
       </c>
       <c r="C854" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi Şemsiye Fonu</t>
+          <t>Kıymetli Madenler Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D854" s="0" t="inlineStr">
         <is>
-          <t>BIST Endeks</t>
+          <t>Altın</t>
         </is>
       </c>
       <c r="E854" s="0" t="inlineStr">
         <is>
-          <t>İŞ</t>
+          <t>ATLAS</t>
         </is>
       </c>
       <c r="F854" s="0" t="inlineStr">
@@ -27677,27 +27677,27 @@
     <row outlineLevel="0" r="855">
       <c r="A855" s="0" t="inlineStr">
         <is>
-          <t>TBT</t>
+          <t>TAR</t>
         </is>
       </c>
       <c r="B855" s="0" t="inlineStr">
         <is>
-          <t>TEB PORTFÖY BORÇLANMA ARAÇLARI FONU</t>
+          <t>AK PORTFÖY TARIM VE GIDA TEKNOLOJİLERİ DEĞİŞKEN FON</t>
         </is>
       </c>
       <c r="C855" s="0" t="inlineStr">
         <is>
-          <t>Borçlanma Araçları Şemsiye Fonu</t>
+          <t>Değişken Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D855" s="0" t="inlineStr">
         <is>
-          <t>Borçlanma Araçları</t>
+          <t>Teknoloji Temalı</t>
         </is>
       </c>
       <c r="E855" s="0" t="inlineStr">
         <is>
-          <t>TEB</t>
+          <t>AK</t>
         </is>
       </c>
       <c r="F855" s="0" t="inlineStr">
@@ -27709,22 +27709,22 @@
     <row outlineLevel="0" r="856">
       <c r="A856" s="0" t="inlineStr">
         <is>
-          <t>TBV</t>
+          <t>TAU</t>
         </is>
       </c>
       <c r="B856" s="0" t="inlineStr">
         <is>
-          <t>İŞ PORTFÖY ÖZEL SEKTÖR BORÇLANMA ARAÇLARI (TL) FONU</t>
+          <t>İŞ PORTFÖY BIST BANKA ENDEKSİ HİSSE SENEDİ (TL) FONU (HİSSE SENEDİ YOĞUN FON)</t>
         </is>
       </c>
       <c r="C856" s="0" t="inlineStr">
         <is>
-          <t>Borçlanma Araçları Şemsiye Fonu</t>
+          <t>Hisse Senedi Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D856" s="0" t="inlineStr">
         <is>
-          <t>Özel Sektör Borçlanma Araçları</t>
+          <t>BIST Endeks</t>
         </is>
       </c>
       <c r="E856" s="0" t="inlineStr">
@@ -27741,27 +27741,27 @@
     <row outlineLevel="0" r="857">
       <c r="A857" s="0" t="inlineStr">
         <is>
-          <t>TCA</t>
+          <t>TBT</t>
         </is>
       </c>
       <c r="B857" s="0" t="inlineStr">
         <is>
-          <t>ZİRAAT PORTFÖY ALTIN KATILIM FONU</t>
+          <t>TEB PORTFÖY BORÇLANMA ARAÇLARI FONU</t>
         </is>
       </c>
       <c r="C857" s="0" t="inlineStr">
         <is>
-          <t>Katılım Şemsiye Fonu</t>
+          <t>Borçlanma Araçları Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D857" s="0" t="inlineStr">
         <is>
-          <t>Altın</t>
+          <t>Borçlanma Araçları</t>
         </is>
       </c>
       <c r="E857" s="0" t="inlineStr">
         <is>
-          <t>ZİRAAT</t>
+          <t>TEB</t>
         </is>
       </c>
       <c r="F857" s="0" t="inlineStr">
@@ -27773,27 +27773,27 @@
     <row outlineLevel="0" r="858">
       <c r="A858" s="0" t="inlineStr">
         <is>
-          <t>TCB</t>
+          <t>TBV</t>
         </is>
       </c>
       <c r="B858" s="0" t="inlineStr">
         <is>
-          <t>TACİRLER PORTFÖY PARA PİYASASI FONU</t>
+          <t>İŞ PORTFÖY ÖZEL SEKTÖR BORÇLANMA ARAÇLARI (TL) FONU</t>
         </is>
       </c>
       <c r="C858" s="0" t="inlineStr">
         <is>
-          <t>Para Piyasası Şemsiye Fonu</t>
+          <t>Borçlanma Araçları Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D858" s="0" t="inlineStr">
         <is>
-          <t>Para Piyasası</t>
+          <t>Özel Sektör Borçlanma Araçları</t>
         </is>
       </c>
       <c r="E858" s="0" t="inlineStr">
         <is>
-          <t>TACİRLER</t>
+          <t>İŞ</t>
         </is>
       </c>
       <c r="F858" s="0" t="inlineStr">
@@ -27805,54 +27805,54 @@
     <row outlineLevel="0" r="859">
       <c r="A859" s="0" t="inlineStr">
         <is>
-          <t>TCC</t>
+          <t>TCA</t>
         </is>
       </c>
       <c r="B859" s="0" t="inlineStr">
         <is>
-          <t>TACİRLER PORTFÖY SERBEST ( DÖVİZ ) FON</t>
+          <t>ZİRAAT PORTFÖY ALTIN KATILIM FONU</t>
         </is>
       </c>
       <c r="C859" s="0" t="inlineStr">
         <is>
-          <t>Serbest Şemsiye Fonu</t>
+          <t>Katılım Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D859" s="0" t="inlineStr">
         <is>
-          <t>Döviz</t>
+          <t>Altın</t>
         </is>
       </c>
       <c r="E859" s="0" t="inlineStr">
         <is>
-          <t>TACİRLER</t>
+          <t>ZİRAAT</t>
         </is>
       </c>
       <c r="F859" s="0" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>TL</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="860">
       <c r="A860" s="0" t="inlineStr">
         <is>
-          <t>TCD</t>
+          <t>TCB</t>
         </is>
       </c>
       <c r="B860" s="0" t="inlineStr">
         <is>
-          <t>TACİRLER PORTFÖY DEĞIŞKEN FON</t>
+          <t>TACİRLER PORTFÖY PARA PİYASASI FONU</t>
         </is>
       </c>
       <c r="C860" s="0" t="inlineStr">
         <is>
-          <t>Değişken Şemsiye Fonu</t>
+          <t>Para Piyasası Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D860" s="0" t="inlineStr">
         <is>
-          <t>Değişken</t>
+          <t>Para Piyasası</t>
         </is>
       </c>
       <c r="E860" s="0" t="inlineStr">
@@ -27869,59 +27869,59 @@
     <row outlineLevel="0" r="861">
       <c r="A861" s="0" t="inlineStr">
         <is>
-          <t>TCF</t>
+          <t>TCC</t>
         </is>
       </c>
       <c r="B861" s="0" t="inlineStr">
         <is>
-          <t>TEB PORTFÖY ÜÇÜNCÜ FON SEPETİ FONU</t>
+          <t>TACİRLER PORTFÖY SERBEST ( DÖVİZ ) FON</t>
         </is>
       </c>
       <c r="C861" s="0" t="inlineStr">
         <is>
-          <t>Fon Sepeti Şemsiye Fonu</t>
+          <t>Serbest Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D861" s="0" t="inlineStr">
         <is>
-          <t>Fon Sepeti</t>
+          <t>Döviz</t>
         </is>
       </c>
       <c r="E861" s="0" t="inlineStr">
         <is>
-          <t>TEB</t>
+          <t>TACİRLER</t>
         </is>
       </c>
       <c r="F861" s="0" t="inlineStr">
         <is>
-          <t>TL</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="862">
       <c r="A862" s="0" t="inlineStr">
         <is>
-          <t>TDG</t>
+          <t>TCD</t>
         </is>
       </c>
       <c r="B862" s="0" t="inlineStr">
         <is>
-          <t>İŞ PORTFÖY YABANCI BORÇLANMA ARAÇLARI FONU</t>
+          <t>TACİRLER PORTFÖY DEĞIŞKEN FON</t>
         </is>
       </c>
       <c r="C862" s="0" t="inlineStr">
         <is>
-          <t>Borçlanma Araçları Şemsiye Fonu</t>
+          <t>Değişken Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D862" s="0" t="inlineStr">
         <is>
-          <t>Borçlanma Araçları</t>
+          <t>Değişken</t>
         </is>
       </c>
       <c r="E862" s="0" t="inlineStr">
         <is>
-          <t>İŞ</t>
+          <t>TACİRLER</t>
         </is>
       </c>
       <c r="F862" s="0" t="inlineStr">
@@ -27933,22 +27933,22 @@
     <row outlineLevel="0" r="863">
       <c r="A863" s="0" t="inlineStr">
         <is>
-          <t>TE3</t>
+          <t>TCF</t>
         </is>
       </c>
       <c r="B863" s="0" t="inlineStr">
         <is>
-          <t>TEB PORTFÖY MUTLAK GETİRİ HEDEFLİ DEĞİŞKEN FON</t>
+          <t>TEB PORTFÖY ÜÇÜNCÜ FON SEPETİ FONU</t>
         </is>
       </c>
       <c r="C863" s="0" t="inlineStr">
         <is>
-          <t>Değişken Şemsiye Fonu</t>
+          <t>Fon Sepeti Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D863" s="0" t="inlineStr">
         <is>
-          <t>İstatiksel Arbitraj</t>
+          <t>Fon Sepeti</t>
         </is>
       </c>
       <c r="E863" s="0" t="inlineStr">
@@ -27965,27 +27965,27 @@
     <row outlineLevel="0" r="864">
       <c r="A864" s="0" t="inlineStr">
         <is>
-          <t>TE4</t>
+          <t>TDG</t>
         </is>
       </c>
       <c r="B864" s="0" t="inlineStr">
         <is>
-          <t>TEB PORTFÖY BİRİNCİ DEĞİŞKEN FON</t>
+          <t>İŞ PORTFÖY YABANCI BORÇLANMA ARAÇLARI FONU</t>
         </is>
       </c>
       <c r="C864" s="0" t="inlineStr">
         <is>
-          <t>Değişken Şemsiye Fonu</t>
+          <t>Borçlanma Araçları Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D864" s="0" t="inlineStr">
         <is>
-          <t>Değişken</t>
+          <t>Borçlanma Araçları</t>
         </is>
       </c>
       <c r="E864" s="0" t="inlineStr">
         <is>
-          <t>TEB</t>
+          <t>İŞ</t>
         </is>
       </c>
       <c r="F864" s="0" t="inlineStr">
@@ -27997,27 +27997,27 @@
     <row outlineLevel="0" r="865">
       <c r="A865" s="0" t="inlineStr">
         <is>
-          <t>TEJ</t>
+          <t>TE3</t>
         </is>
       </c>
       <c r="B865" s="0" t="inlineStr">
         <is>
-          <t>AZİMUT PORTFÖY TEKNOLOJİ FON SEPETİ FONU</t>
+          <t>TEB PORTFÖY MUTLAK GETİRİ HEDEFLİ DEĞİŞKEN FON</t>
         </is>
       </c>
       <c r="C865" s="0" t="inlineStr">
         <is>
-          <t>Fon Sepeti Şemsiye Fonu</t>
+          <t>Değişken Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D865" s="0" t="inlineStr">
         <is>
-          <t>Teknoloji Temalı</t>
+          <t>İstatiksel Arbitraj</t>
         </is>
       </c>
       <c r="E865" s="0" t="inlineStr">
         <is>
-          <t>AZİMUT</t>
+          <t>TEB</t>
         </is>
       </c>
       <c r="F865" s="0" t="inlineStr">
@@ -28029,22 +28029,22 @@
     <row outlineLevel="0" r="866">
       <c r="A866" s="0" t="inlineStr">
         <is>
-          <t>TFF</t>
+          <t>TE4</t>
         </is>
       </c>
       <c r="B866" s="0" t="inlineStr">
         <is>
-          <t>TEB PORTFÖY AMERİKA TEKNOLOJİ YABANCI BYF FON SEPETİ FONU</t>
+          <t>TEB PORTFÖY BİRİNCİ DEĞİŞKEN FON</t>
         </is>
       </c>
       <c r="C866" s="0" t="inlineStr">
         <is>
-          <t>Fon Sepeti Şemsiye Fonu</t>
+          <t>Değişken Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D866" s="0" t="inlineStr">
         <is>
-          <t>Teknoloji Temalı</t>
+          <t>Değişken</t>
         </is>
       </c>
       <c r="E866" s="0" t="inlineStr">
@@ -28061,27 +28061,27 @@
     <row outlineLevel="0" r="867">
       <c r="A867" s="0" t="inlineStr">
         <is>
-          <t>TFU</t>
+          <t>TEJ</t>
         </is>
       </c>
       <c r="B867" s="0" t="inlineStr">
         <is>
-          <t>İŞ PORTFÖY TÜFEYE ENDEKSLİ BORÇLANMA ARAÇLARI (TL) FONU</t>
+          <t>AZİMUT PORTFÖY TEKNOLOJİ FON SEPETİ FONU</t>
         </is>
       </c>
       <c r="C867" s="0" t="inlineStr">
         <is>
-          <t>Borçlanma Araçları Şemsiye Fonu</t>
+          <t>Fon Sepeti Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D867" s="0" t="inlineStr">
         <is>
-          <t>Borçlanma Araçları</t>
+          <t>Teknoloji Temalı</t>
         </is>
       </c>
       <c r="E867" s="0" t="inlineStr">
         <is>
-          <t>İŞ</t>
+          <t>AZİMUT</t>
         </is>
       </c>
       <c r="F867" s="0" t="inlineStr">
@@ -28093,27 +28093,27 @@
     <row outlineLevel="0" r="868">
       <c r="A868" s="0" t="inlineStr">
         <is>
-          <t>TGA</t>
+          <t>TFF</t>
         </is>
       </c>
       <c r="B868" s="0" t="inlineStr">
         <is>
-          <t>GARANTİ PORTFÖY AGRESİF DEĞİŞKEN FON</t>
+          <t>TEB PORTFÖY AMERİKA TEKNOLOJİ YABANCI BYF FON SEPETİ FONU</t>
         </is>
       </c>
       <c r="C868" s="0" t="inlineStr">
         <is>
-          <t>Değişken Şemsiye Fonu</t>
+          <t>Fon Sepeti Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D868" s="0" t="inlineStr">
         <is>
-          <t>Değişken</t>
+          <t>Teknoloji Temalı</t>
         </is>
       </c>
       <c r="E868" s="0" t="inlineStr">
         <is>
-          <t>GARANTİ</t>
+          <t>TEB</t>
         </is>
       </c>
       <c r="F868" s="0" t="inlineStr">
@@ -28125,22 +28125,22 @@
     <row outlineLevel="0" r="869">
       <c r="A869" s="0" t="inlineStr">
         <is>
-          <t>TGE</t>
+          <t>TFU</t>
         </is>
       </c>
       <c r="B869" s="0" t="inlineStr">
         <is>
-          <t>İŞ PORTFÖY EMTİA YABANCI BYF FON SEPETİ FONU</t>
+          <t>İŞ PORTFÖY TÜFEYE ENDEKSLİ BORÇLANMA ARAÇLARI (TL) FONU</t>
         </is>
       </c>
       <c r="C869" s="0" t="inlineStr">
         <is>
-          <t>Fon Sepeti Şemsiye Fonu</t>
+          <t>Borçlanma Araçları Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D869" s="0" t="inlineStr">
         <is>
-          <t>Emtia</t>
+          <t>Borçlanma Araçları</t>
         </is>
       </c>
       <c r="E869" s="0" t="inlineStr">
@@ -28157,12 +28157,12 @@
     <row outlineLevel="0" r="870">
       <c r="A870" s="0" t="inlineStr">
         <is>
-          <t>TGR</t>
+          <t>TGA</t>
         </is>
       </c>
       <c r="B870" s="0" t="inlineStr">
         <is>
-          <t>AK PORTFÖY TURİZM VE SEYAHAT SEKTÖRÜ DEĞİŞKEN FON</t>
+          <t>GARANTİ PORTFÖY AGRESİF DEĞİŞKEN FON</t>
         </is>
       </c>
       <c r="C870" s="0" t="inlineStr">
@@ -28172,12 +28172,12 @@
       </c>
       <c r="D870" s="0" t="inlineStr">
         <is>
-          <t>Tematik</t>
+          <t>Değişken</t>
         </is>
       </c>
       <c r="E870" s="0" t="inlineStr">
         <is>
-          <t>AK</t>
+          <t>GARANTİ</t>
         </is>
       </c>
       <c r="F870" s="0" t="inlineStr">
@@ -28189,27 +28189,27 @@
     <row outlineLevel="0" r="871">
       <c r="A871" s="0" t="inlineStr">
         <is>
-          <t>THD</t>
+          <t>TGE</t>
         </is>
       </c>
       <c r="B871" s="0" t="inlineStr">
         <is>
-          <t>TRIVE PORTFÖY BİRİNCİ HİSSE SENEDİ (TL) FON (HİSSE SENEDİ YOĞUN FON)</t>
+          <t>İŞ PORTFÖY EMTİA YABANCI BYF FON SEPETİ FONU</t>
         </is>
       </c>
       <c r="C871" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi Şemsiye Fonu</t>
+          <t>Fon Sepeti Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D871" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi</t>
+          <t>Emtia</t>
         </is>
       </c>
       <c r="E871" s="0" t="inlineStr">
         <is>
-          <t>TRIVE</t>
+          <t>İŞ</t>
         </is>
       </c>
       <c r="F871" s="0" t="inlineStr">
@@ -28221,27 +28221,27 @@
     <row outlineLevel="0" r="872">
       <c r="A872" s="0" t="inlineStr">
         <is>
-          <t>THF</t>
+          <t>TGR</t>
         </is>
       </c>
       <c r="B872" s="0" t="inlineStr">
         <is>
-          <t>TERA PORTFÖY HİSSE SENEDİ (TL) FONU (HİSSE SENEDİ YOĞUN FON)</t>
+          <t>AK PORTFÖY TURİZM VE SEYAHAT SEKTÖRÜ DEĞİŞKEN FON</t>
         </is>
       </c>
       <c r="C872" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi Şemsiye Fonu</t>
+          <t>Değişken Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D872" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi</t>
+          <t>Tematik</t>
         </is>
       </c>
       <c r="E872" s="0" t="inlineStr">
         <is>
-          <t>TERA</t>
+          <t>AK</t>
         </is>
       </c>
       <c r="F872" s="0" t="inlineStr">
@@ -28253,17 +28253,17 @@
     <row outlineLevel="0" r="873">
       <c r="A873" s="0" t="inlineStr">
         <is>
-          <t>THT</t>
+          <t>THD</t>
         </is>
       </c>
       <c r="B873" s="0" t="inlineStr">
         <is>
-          <t>TRİVE PORTFÖY HİSSE SENEDİ SERBEST FON (HİSSE SENEDİ YOĞUN FON)</t>
+          <t>TRIVE PORTFÖY BİRİNCİ HİSSE SENEDİ (TL) FON (HİSSE SENEDİ YOĞUN FON)</t>
         </is>
       </c>
       <c r="C873" s="0" t="inlineStr">
         <is>
-          <t>Serbest Şemsiye Fonu</t>
+          <t>Hisse Senedi Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D873" s="0" t="inlineStr">
@@ -28285,17 +28285,17 @@
     <row outlineLevel="0" r="874">
       <c r="A874" s="0" t="inlineStr">
         <is>
-          <t>THV</t>
+          <t>THF</t>
         </is>
       </c>
       <c r="B874" s="0" t="inlineStr">
         <is>
-          <t>ATA PORTFÖY BARBAROS HİSSE SENEDİ SERBEST (TL) FON (HİSSE SENEDİ YOĞUN FON)</t>
+          <t>TERA PORTFÖY HİSSE SENEDİ (TL) FONU (HİSSE SENEDİ YOĞUN FON)</t>
         </is>
       </c>
       <c r="C874" s="0" t="inlineStr">
         <is>
-          <t>Serbest Şemsiye Fonu</t>
+          <t>Hisse Senedi Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D874" s="0" t="inlineStr">
@@ -28305,7 +28305,7 @@
       </c>
       <c r="E874" s="0" t="inlineStr">
         <is>
-          <t>ATA</t>
+          <t>TERA</t>
         </is>
       </c>
       <c r="F874" s="0" t="inlineStr">
@@ -28317,17 +28317,17 @@
     <row outlineLevel="0" r="875">
       <c r="A875" s="0" t="inlineStr">
         <is>
-          <t>TI2</t>
+          <t>THT</t>
         </is>
       </c>
       <c r="B875" s="0" t="inlineStr">
         <is>
-          <t>İŞ PORTFÖY HİSSE SENEDİ (TL) FONU (HİSSE SENEDİ YOĞUN FON)</t>
+          <t>TRİVE PORTFÖY HİSSE SENEDİ SERBEST FON (HİSSE SENEDİ YOĞUN FON)</t>
         </is>
       </c>
       <c r="C875" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi Şemsiye Fonu</t>
+          <t>Serbest Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D875" s="0" t="inlineStr">
@@ -28337,7 +28337,7 @@
       </c>
       <c r="E875" s="0" t="inlineStr">
         <is>
-          <t>İŞ</t>
+          <t>TRIVE</t>
         </is>
       </c>
       <c r="F875" s="0" t="inlineStr">
@@ -28349,27 +28349,27 @@
     <row outlineLevel="0" r="876">
       <c r="A876" s="0" t="inlineStr">
         <is>
-          <t>TI3</t>
+          <t>THV</t>
         </is>
       </c>
       <c r="B876" s="0" t="inlineStr">
         <is>
-          <t>İŞ PORTFÖY İŞ BANKASI İŞTİRAKLERİ ENDEKSİ HİSSE SENEDİ (TL) FONU (HİSSE SENEDİ YOĞUN FON)</t>
+          <t>ATA PORTFÖY BARBAROS HİSSE SENEDİ SERBEST (TL) FON (HİSSE SENEDİ YOĞUN FON)</t>
         </is>
       </c>
       <c r="C876" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi Şemsiye Fonu</t>
+          <t>Serbest Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D876" s="0" t="inlineStr">
         <is>
-          <t>BIST Endeks</t>
+          <t>Hisse Senedi</t>
         </is>
       </c>
       <c r="E876" s="0" t="inlineStr">
         <is>
-          <t>İŞ</t>
+          <t>ATA</t>
         </is>
       </c>
       <c r="F876" s="0" t="inlineStr">
@@ -28381,22 +28381,22 @@
     <row outlineLevel="0" r="877">
       <c r="A877" s="0" t="inlineStr">
         <is>
-          <t>TI4</t>
+          <t>TI2</t>
         </is>
       </c>
       <c r="B877" s="0" t="inlineStr">
         <is>
-          <t>İŞ PORTFÖY TEMKİNLİ DEĞİŞKEN FON</t>
+          <t>İŞ PORTFÖY HİSSE SENEDİ (TL) FONU (HİSSE SENEDİ YOĞUN FON)</t>
         </is>
       </c>
       <c r="C877" s="0" t="inlineStr">
         <is>
-          <t>Değişken Şemsiye Fonu</t>
+          <t>Hisse Senedi Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D877" s="0" t="inlineStr">
         <is>
-          <t>Değişken</t>
+          <t>Hisse Senedi</t>
         </is>
       </c>
       <c r="E877" s="0" t="inlineStr">
@@ -28413,22 +28413,22 @@
     <row outlineLevel="0" r="878">
       <c r="A878" s="0" t="inlineStr">
         <is>
-          <t>TI6</t>
+          <t>TI3</t>
         </is>
       </c>
       <c r="B878" s="0" t="inlineStr">
         <is>
-          <t>İŞ PORTFÖY BORÇLANMA ARAÇLARI (TL) FONU</t>
+          <t>İŞ PORTFÖY İŞ BANKASI İŞTİRAKLERİ ENDEKSİ HİSSE SENEDİ (TL) FONU (HİSSE SENEDİ YOĞUN FON)</t>
         </is>
       </c>
       <c r="C878" s="0" t="inlineStr">
         <is>
-          <t>Borçlanma Araçları Şemsiye Fonu</t>
+          <t>Hisse Senedi Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D878" s="0" t="inlineStr">
         <is>
-          <t>Borçlanma Araçları</t>
+          <t>BIST Endeks</t>
         </is>
       </c>
       <c r="E878" s="0" t="inlineStr">
@@ -28445,12 +28445,12 @@
     <row outlineLevel="0" r="879">
       <c r="A879" s="0" t="inlineStr">
         <is>
-          <t>TI7</t>
+          <t>TI4</t>
         </is>
       </c>
       <c r="B879" s="0" t="inlineStr">
         <is>
-          <t>İŞ PORTFÖY DENGELİ DEĞİŞKEN FON</t>
+          <t>İŞ PORTFÖY TEMKİNLİ DEĞİŞKEN FON</t>
         </is>
       </c>
       <c r="C879" s="0" t="inlineStr">
@@ -28477,22 +28477,22 @@
     <row outlineLevel="0" r="880">
       <c r="A880" s="0" t="inlineStr">
         <is>
-          <t>TIE</t>
+          <t>TI6</t>
         </is>
       </c>
       <c r="B880" s="0" t="inlineStr">
         <is>
-          <t>İŞ PORTFÖY BIST 30 ENDEKSİ HİSSE SENEDİ (TL) FONU (HİSSE SENEDİ YOĞUN FON)</t>
+          <t>İŞ PORTFÖY BORÇLANMA ARAÇLARI (TL) FONU</t>
         </is>
       </c>
       <c r="C880" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi Şemsiye Fonu</t>
+          <t>Borçlanma Araçları Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D880" s="0" t="inlineStr">
         <is>
-          <t>BIST Endeks</t>
+          <t>Borçlanma Araçları</t>
         </is>
       </c>
       <c r="E880" s="0" t="inlineStr">
@@ -28509,22 +28509,22 @@
     <row outlineLevel="0" r="881">
       <c r="A881" s="0" t="inlineStr">
         <is>
-          <t>TIL</t>
+          <t>TI7</t>
         </is>
       </c>
       <c r="B881" s="0" t="inlineStr">
         <is>
-          <t>İŞ PORTFÖY KATILIM HİSSE SENEDİ (TL) FONU (HİSSE SENEDİ YOĞUN FON)</t>
+          <t>İŞ PORTFÖY DENGELİ DEĞİŞKEN FON</t>
         </is>
       </c>
       <c r="C881" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi Şemsiye Fonu</t>
+          <t>Değişken Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D881" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi</t>
+          <t>Değişken</t>
         </is>
       </c>
       <c r="E881" s="0" t="inlineStr">
@@ -28541,27 +28541,27 @@
     <row outlineLevel="0" r="882">
       <c r="A882" s="0" t="inlineStr">
         <is>
-          <t>TJF</t>
+          <t>TIE</t>
         </is>
       </c>
       <c r="B882" s="0" t="inlineStr">
         <is>
-          <t>TEB PORTFÖY SÜRDÜRÜLEBİLİRLİK FON SEPETİ FONU</t>
+          <t>İŞ PORTFÖY BIST 30 ENDEKSİ HİSSE SENEDİ (TL) FONU (HİSSE SENEDİ YOĞUN FON)</t>
         </is>
       </c>
       <c r="C882" s="0" t="inlineStr">
         <is>
-          <t>Fon Sepeti Şemsiye Fonu</t>
+          <t>Hisse Senedi Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D882" s="0" t="inlineStr">
         <is>
-          <t>Tematik</t>
+          <t>BIST Endeks</t>
         </is>
       </c>
       <c r="E882" s="0" t="inlineStr">
         <is>
-          <t>TEB</t>
+          <t>İŞ</t>
         </is>
       </c>
       <c r="F882" s="0" t="inlineStr">
@@ -28573,27 +28573,27 @@
     <row outlineLevel="0" r="883">
       <c r="A883" s="0" t="inlineStr">
         <is>
-          <t>TJI</t>
+          <t>TIL</t>
         </is>
       </c>
       <c r="B883" s="0" t="inlineStr">
         <is>
-          <t>TEB PORTFÖY İKİNCİ FON SEPETİ FONU</t>
+          <t>İŞ PORTFÖY KATILIM HİSSE SENEDİ (TL) FONU (HİSSE SENEDİ YOĞUN FON)</t>
         </is>
       </c>
       <c r="C883" s="0" t="inlineStr">
         <is>
-          <t>Fon Sepeti Şemsiye Fonu</t>
+          <t>Hisse Senedi Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D883" s="0" t="inlineStr">
         <is>
-          <t>Fon Sepeti</t>
+          <t>Hisse Senedi</t>
         </is>
       </c>
       <c r="E883" s="0" t="inlineStr">
         <is>
-          <t>TEB</t>
+          <t>İŞ</t>
         </is>
       </c>
       <c r="F883" s="0" t="inlineStr">
@@ -28605,22 +28605,22 @@
     <row outlineLevel="0" r="884">
       <c r="A884" s="0" t="inlineStr">
         <is>
-          <t>TJT</t>
+          <t>TJF</t>
         </is>
       </c>
       <c r="B884" s="0" t="inlineStr">
         <is>
-          <t>TEB PORTFÖY ALTINCI SERBEST (DÖVİZ-AVRO) FON</t>
+          <t>TEB PORTFÖY SÜRDÜRÜLEBİLİRLİK FON SEPETİ FONU</t>
         </is>
       </c>
       <c r="C884" s="0" t="inlineStr">
         <is>
-          <t>Serbest Şemsiye Fonu</t>
+          <t>Fon Sepeti Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D884" s="0" t="inlineStr">
         <is>
-          <t>Döviz</t>
+          <t>Tematik</t>
         </is>
       </c>
       <c r="E884" s="0" t="inlineStr">
@@ -28630,34 +28630,34 @@
       </c>
       <c r="F884" s="0" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>TL</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="885">
       <c r="A885" s="0" t="inlineStr">
         <is>
-          <t>TKF</t>
+          <t>TJI</t>
         </is>
       </c>
       <c r="B885" s="0" t="inlineStr">
         <is>
-          <t>TACİRLER PORTFÖY HİSSE SENEDİ FONU (HİSSE SENEDİ YOĞUN FON)</t>
+          <t>TEB PORTFÖY İKİNCİ FON SEPETİ FONU</t>
         </is>
       </c>
       <c r="C885" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi Şemsiye Fonu</t>
+          <t>Fon Sepeti Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D885" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi</t>
+          <t>Fon Sepeti</t>
         </is>
       </c>
       <c r="E885" s="0" t="inlineStr">
         <is>
-          <t>TACİRLER</t>
+          <t>TEB</t>
         </is>
       </c>
       <c r="F885" s="0" t="inlineStr">
@@ -28669,44 +28669,44 @@
     <row outlineLevel="0" r="886">
       <c r="A886" s="0" t="inlineStr">
         <is>
-          <t>TLE</t>
+          <t>TJT</t>
         </is>
       </c>
       <c r="B886" s="0" t="inlineStr">
         <is>
-          <t>AURA PORTFÖY YABANCI BORÇLANMA ARAÇLARI FONU</t>
+          <t>TEB PORTFÖY ALTINCI SERBEST (DÖVİZ-AVRO) FON</t>
         </is>
       </c>
       <c r="C886" s="0" t="inlineStr">
         <is>
-          <t>Borçlanma Araçları Şemsiye Fonu</t>
+          <t>Serbest Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D886" s="0" t="inlineStr">
         <is>
-          <t>Borçlanma Araçları</t>
+          <t>Döviz</t>
         </is>
       </c>
       <c r="E886" s="0" t="inlineStr">
         <is>
-          <t>AURA</t>
+          <t>TEB</t>
         </is>
       </c>
       <c r="F886" s="0" t="inlineStr">
         <is>
-          <t>TL</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="887">
       <c r="A887" s="0" t="inlineStr">
         <is>
-          <t>TLH</t>
+          <t>TKF</t>
         </is>
       </c>
       <c r="B887" s="0" t="inlineStr">
         <is>
-          <t>AURA PORTFÖY HİSSE SENEDİ FONU (HİSSE SENEDİ YOĞUN FON)</t>
+          <t>TACİRLER PORTFÖY HİSSE SENEDİ FONU (HİSSE SENEDİ YOĞUN FON)</t>
         </is>
       </c>
       <c r="C887" s="0" t="inlineStr">
@@ -28721,7 +28721,7 @@
       </c>
       <c r="E887" s="0" t="inlineStr">
         <is>
-          <t>AURA</t>
+          <t>TACİRLER</t>
         </is>
       </c>
       <c r="F887" s="0" t="inlineStr">
@@ -28733,27 +28733,27 @@
     <row outlineLevel="0" r="888">
       <c r="A888" s="0" t="inlineStr">
         <is>
-          <t>TLK</t>
+          <t>TLE</t>
         </is>
       </c>
       <c r="B888" s="0" t="inlineStr">
         <is>
-          <t>AKTİF PORTFÖY PARA PİYASASI KATILIM (TL) FONU</t>
+          <t>AURA PORTFÖY YABANCI BORÇLANMA ARAÇLARI FONU</t>
         </is>
       </c>
       <c r="C888" s="0" t="inlineStr">
         <is>
-          <t>Katılım Şemsiye Fonu</t>
+          <t>Borçlanma Araçları Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D888" s="0" t="inlineStr">
         <is>
-          <t>Para Piyasası</t>
+          <t>Borçlanma Araçları</t>
         </is>
       </c>
       <c r="E888" s="0" t="inlineStr">
         <is>
-          <t>AKTİF</t>
+          <t>AURA</t>
         </is>
       </c>
       <c r="F888" s="0" t="inlineStr">
@@ -28765,27 +28765,27 @@
     <row outlineLevel="0" r="889">
       <c r="A889" s="0" t="inlineStr">
         <is>
-          <t>TLV</t>
+          <t>TLH</t>
         </is>
       </c>
       <c r="B889" s="0" t="inlineStr">
         <is>
-          <t>TERA PORTFÖY PARA PİYASASI KATILIM (TL) FONU</t>
+          <t>AURA PORTFÖY HİSSE SENEDİ FONU (HİSSE SENEDİ YOĞUN FON)</t>
         </is>
       </c>
       <c r="C889" s="0" t="inlineStr">
         <is>
-          <t>Katılım Şemsiye Fonu</t>
+          <t>Hisse Senedi Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D889" s="0" t="inlineStr">
         <is>
-          <t>Para Piyasası</t>
+          <t>Hisse Senedi</t>
         </is>
       </c>
       <c r="E889" s="0" t="inlineStr">
         <is>
-          <t>TERA</t>
+          <t>AURA</t>
         </is>
       </c>
       <c r="F889" s="0" t="inlineStr">
@@ -28797,27 +28797,27 @@
     <row outlineLevel="0" r="890">
       <c r="A890" s="0" t="inlineStr">
         <is>
-          <t>TLY</t>
+          <t>TLK</t>
         </is>
       </c>
       <c r="B890" s="0" t="inlineStr">
         <is>
-          <t>TERA PORTFÖY BİRİNCİ SERBEST FON</t>
+          <t>AKTİF PORTFÖY PARA PİYASASI KATILIM (TL) FONU</t>
         </is>
       </c>
       <c r="C890" s="0" t="inlineStr">
         <is>
-          <t>Serbest Şemsiye Fonu</t>
+          <t>Katılım Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D890" s="0" t="inlineStr">
         <is>
-          <t>Diğer Serbest</t>
+          <t>Para Piyasası</t>
         </is>
       </c>
       <c r="E890" s="0" t="inlineStr">
         <is>
-          <t>TERA</t>
+          <t>AKTİF</t>
         </is>
       </c>
       <c r="F890" s="0" t="inlineStr">
@@ -28829,27 +28829,27 @@
     <row outlineLevel="0" r="891">
       <c r="A891" s="0" t="inlineStr">
         <is>
-          <t>TLZ</t>
+          <t>TLV</t>
         </is>
       </c>
       <c r="B891" s="0" t="inlineStr">
         <is>
-          <t>ATA PORTFÖY KATILIM HİSSE SENEDİ (TL) FONU (HİSSE SENEDİ YOĞUN FON)</t>
+          <t>TERA PORTFÖY PARA PİYASASI KATILIM (TL) FONU</t>
         </is>
       </c>
       <c r="C891" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi Şemsiye Fonu</t>
+          <t>Katılım Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D891" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi</t>
+          <t>Para Piyasası</t>
         </is>
       </c>
       <c r="E891" s="0" t="inlineStr">
         <is>
-          <t>ATA</t>
+          <t>TERA</t>
         </is>
       </c>
       <c r="F891" s="0" t="inlineStr">
@@ -28861,27 +28861,27 @@
     <row outlineLevel="0" r="892">
       <c r="A892" s="0" t="inlineStr">
         <is>
-          <t>TMC</t>
+          <t>TLY</t>
         </is>
       </c>
       <c r="B892" s="0" t="inlineStr">
         <is>
-          <t>İŞ PORTFÖY TEMA DEĞİŞKEN FON</t>
+          <t>TERA PORTFÖY BİRİNCİ SERBEST FON</t>
         </is>
       </c>
       <c r="C892" s="0" t="inlineStr">
         <is>
-          <t>Değişken Şemsiye Fonu</t>
+          <t>Serbest Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D892" s="0" t="inlineStr">
         <is>
-          <t>Değişken</t>
+          <t>Diğer Serbest</t>
         </is>
       </c>
       <c r="E892" s="0" t="inlineStr">
         <is>
-          <t>İŞ</t>
+          <t>TERA</t>
         </is>
       </c>
       <c r="F892" s="0" t="inlineStr">
@@ -28893,12 +28893,12 @@
     <row outlineLevel="0" r="893">
       <c r="A893" s="0" t="inlineStr">
         <is>
-          <t>TMG</t>
+          <t>TLZ</t>
         </is>
       </c>
       <c r="B893" s="0" t="inlineStr">
         <is>
-          <t>İŞ PORTFÖY YABANCI HİSSE SENEDİ FONU</t>
+          <t>ATA PORTFÖY KATILIM HİSSE SENEDİ (TL) FONU (HİSSE SENEDİ YOĞUN FON)</t>
         </is>
       </c>
       <c r="C893" s="0" t="inlineStr">
@@ -28908,12 +28908,12 @@
       </c>
       <c r="D893" s="0" t="inlineStr">
         <is>
-          <t>Tematik</t>
+          <t>Hisse Senedi</t>
         </is>
       </c>
       <c r="E893" s="0" t="inlineStr">
         <is>
-          <t>İŞ</t>
+          <t>ATA</t>
         </is>
       </c>
       <c r="F893" s="0" t="inlineStr">
@@ -28925,59 +28925,59 @@
     <row outlineLevel="0" r="894">
       <c r="A894" s="0" t="inlineStr">
         <is>
-          <t>TMM</t>
+          <t>TMC</t>
         </is>
       </c>
       <c r="B894" s="0" t="inlineStr">
         <is>
-          <t>TERA PORTFÖY İKİNCİ SERBEST (DÖVİZ) FON</t>
+          <t>İŞ PORTFÖY TEMA DEĞİŞKEN FON</t>
         </is>
       </c>
       <c r="C894" s="0" t="inlineStr">
         <is>
-          <t>Serbest Şemsiye Fonu</t>
+          <t>Değişken Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D894" s="0" t="inlineStr">
         <is>
-          <t>Döviz</t>
+          <t>Değişken</t>
         </is>
       </c>
       <c r="E894" s="0" t="inlineStr">
         <is>
-          <t>TERA</t>
+          <t>İŞ</t>
         </is>
       </c>
       <c r="F894" s="0" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>TL</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="895">
       <c r="A895" s="0" t="inlineStr">
         <is>
-          <t>TMU</t>
+          <t>TMG</t>
         </is>
       </c>
       <c r="B895" s="0" t="inlineStr">
         <is>
-          <t>AZİMUT PORTFÖY TEMKİNLİ FON SEPETİ FONU</t>
+          <t>İŞ PORTFÖY YABANCI HİSSE SENEDİ FONU</t>
         </is>
       </c>
       <c r="C895" s="0" t="inlineStr">
         <is>
-          <t>Fon Sepeti Şemsiye Fonu</t>
+          <t>Hisse Senedi Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D895" s="0" t="inlineStr">
         <is>
-          <t>Fon Sepeti</t>
+          <t>Tematik</t>
         </is>
       </c>
       <c r="E895" s="0" t="inlineStr">
         <is>
-          <t>AZİMUT</t>
+          <t>İŞ</t>
         </is>
       </c>
       <c r="F895" s="0" t="inlineStr">
@@ -28989,59 +28989,59 @@
     <row outlineLevel="0" r="896">
       <c r="A896" s="0" t="inlineStr">
         <is>
-          <t>TMZ</t>
+          <t>TMM</t>
         </is>
       </c>
       <c r="B896" s="0" t="inlineStr">
         <is>
-          <t>İŞ PORTFÖY SÜRDÜRÜLEBİLİRLİK VE TARIM FON SEPETİ FONU</t>
+          <t>TERA PORTFÖY İKİNCİ SERBEST (DÖVİZ) FON</t>
         </is>
       </c>
       <c r="C896" s="0" t="inlineStr">
         <is>
-          <t>Fon Sepeti Şemsiye Fonu</t>
+          <t>Serbest Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D896" s="0" t="inlineStr">
         <is>
-          <t>Tematik</t>
+          <t>Döviz</t>
         </is>
       </c>
       <c r="E896" s="0" t="inlineStr">
         <is>
-          <t>İŞ</t>
+          <t>TERA</t>
         </is>
       </c>
       <c r="F896" s="0" t="inlineStr">
         <is>
-          <t>TL</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="897">
       <c r="A897" s="0" t="inlineStr">
         <is>
-          <t>TND</t>
+          <t>TMU</t>
         </is>
       </c>
       <c r="B897" s="0" t="inlineStr">
         <is>
-          <t>İŞ PORTFÖY TTF TENİSE DESTEK DEĞİŞKEN FON</t>
+          <t>AZİMUT PORTFÖY TEMKİNLİ FON SEPETİ FONU</t>
         </is>
       </c>
       <c r="C897" s="0" t="inlineStr">
         <is>
-          <t>Değişken Şemsiye Fonu</t>
+          <t>Fon Sepeti Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D897" s="0" t="inlineStr">
         <is>
-          <t>Değişken</t>
+          <t>Fon Sepeti</t>
         </is>
       </c>
       <c r="E897" s="0" t="inlineStr">
         <is>
-          <t>İŞ</t>
+          <t>AZİMUT</t>
         </is>
       </c>
       <c r="F897" s="0" t="inlineStr">
@@ -29053,27 +29053,27 @@
     <row outlineLevel="0" r="898">
       <c r="A898" s="0" t="inlineStr">
         <is>
-          <t>TOT</t>
+          <t>TMZ</t>
         </is>
       </c>
       <c r="B898" s="0" t="inlineStr">
         <is>
-          <t>TEB PORTFÖY ÖZEL SEKTÖR BORÇLANMA ARAÇLARI FONU</t>
+          <t>İŞ PORTFÖY SÜRDÜRÜLEBİLİRLİK VE TARIM FON SEPETİ FONU</t>
         </is>
       </c>
       <c r="C898" s="0" t="inlineStr">
         <is>
-          <t>Borçlanma Araçları Şemsiye Fonu</t>
+          <t>Fon Sepeti Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D898" s="0" t="inlineStr">
         <is>
-          <t>Özel Sektör Borçlanma Araçları</t>
+          <t>Tematik</t>
         </is>
       </c>
       <c r="E898" s="0" t="inlineStr">
         <is>
-          <t>TEB</t>
+          <t>İŞ</t>
         </is>
       </c>
       <c r="F898" s="0" t="inlineStr">
@@ -29085,27 +29085,27 @@
     <row outlineLevel="0" r="899">
       <c r="A899" s="0" t="inlineStr">
         <is>
-          <t>TP2</t>
+          <t>TND</t>
         </is>
       </c>
       <c r="B899" s="0" t="inlineStr">
         <is>
-          <t>TERA PORTFÖY PARA PİYASASI (TL) FONU</t>
+          <t>İŞ PORTFÖY TTF TENİSE DESTEK DEĞİŞKEN FON</t>
         </is>
       </c>
       <c r="C899" s="0" t="inlineStr">
         <is>
-          <t>Para Piyasası Şemsiye Fonu</t>
+          <t>Değişken Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D899" s="0" t="inlineStr">
         <is>
-          <t>Para Piyasası</t>
+          <t>Değişken</t>
         </is>
       </c>
       <c r="E899" s="0" t="inlineStr">
         <is>
-          <t>TERA</t>
+          <t>İŞ</t>
         </is>
       </c>
       <c r="F899" s="0" t="inlineStr">
@@ -29117,22 +29117,22 @@
     <row outlineLevel="0" r="900">
       <c r="A900" s="0" t="inlineStr">
         <is>
-          <t>TPC</t>
+          <t>TOT</t>
         </is>
       </c>
       <c r="B900" s="0" t="inlineStr">
         <is>
-          <t>TEB PORTFÖY BİRİNCİ FON SEPETİ FONU</t>
+          <t>TEB PORTFÖY ÖZEL SEKTÖR BORÇLANMA ARAÇLARI FONU</t>
         </is>
       </c>
       <c r="C900" s="0" t="inlineStr">
         <is>
-          <t>Fon Sepeti Şemsiye Fonu</t>
+          <t>Borçlanma Araçları Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D900" s="0" t="inlineStr">
         <is>
-          <t>Fon Sepeti</t>
+          <t>Özel Sektör Borçlanma Araçları</t>
         </is>
       </c>
       <c r="E900" s="0" t="inlineStr">
@@ -29149,27 +29149,27 @@
     <row outlineLevel="0" r="901">
       <c r="A901" s="0" t="inlineStr">
         <is>
-          <t>TPF</t>
+          <t>TP2</t>
         </is>
       </c>
       <c r="B901" s="0" t="inlineStr">
         <is>
-          <t>TACİRLER PORTFÖY BORÇLANMA ARAÇLARI FONU</t>
+          <t>TERA PORTFÖY PARA PİYASASI (TL) FONU</t>
         </is>
       </c>
       <c r="C901" s="0" t="inlineStr">
         <is>
-          <t>Borçlanma Araçları Şemsiye Fonu</t>
+          <t>Para Piyasası Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D901" s="0" t="inlineStr">
         <is>
-          <t>Borçlanma Araçları</t>
+          <t>Para Piyasası</t>
         </is>
       </c>
       <c r="E901" s="0" t="inlineStr">
         <is>
-          <t>TACİRLER</t>
+          <t>TERA</t>
         </is>
       </c>
       <c r="F901" s="0" t="inlineStr">
@@ -29181,22 +29181,22 @@
     <row outlineLevel="0" r="902">
       <c r="A902" s="0" t="inlineStr">
         <is>
-          <t>TPJ</t>
+          <t>TPC</t>
         </is>
       </c>
       <c r="B902" s="0" t="inlineStr">
         <is>
-          <t>TEB PORTFÖY BİRİNCİ SERBEST (DÖVİZ) FON</t>
+          <t>TEB PORTFÖY BİRİNCİ FON SEPETİ FONU</t>
         </is>
       </c>
       <c r="C902" s="0" t="inlineStr">
         <is>
-          <t>Serbest Şemsiye Fonu</t>
+          <t>Fon Sepeti Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D902" s="0" t="inlineStr">
         <is>
-          <t>Döviz</t>
+          <t>Fon Sepeti</t>
         </is>
       </c>
       <c r="E902" s="0" t="inlineStr">
@@ -29206,19 +29206,19 @@
       </c>
       <c r="F902" s="0" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>TL</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="903">
       <c r="A903" s="0" t="inlineStr">
         <is>
-          <t>TPL</t>
+          <t>TPF</t>
         </is>
       </c>
       <c r="B903" s="0" t="inlineStr">
         <is>
-          <t>TEB PORTFÖY EUROBOND (DÖVİZ) BORÇLANMA ARAÇLARI FONU</t>
+          <t>TACİRLER PORTFÖY BORÇLANMA ARAÇLARI FONU</t>
         </is>
       </c>
       <c r="C903" s="0" t="inlineStr">
@@ -29228,12 +29228,12 @@
       </c>
       <c r="D903" s="0" t="inlineStr">
         <is>
-          <t>Eurobond</t>
+          <t>Borçlanma Araçları</t>
         </is>
       </c>
       <c r="E903" s="0" t="inlineStr">
         <is>
-          <t>TEB</t>
+          <t>TACİRLER</t>
         </is>
       </c>
       <c r="F903" s="0" t="inlineStr">
@@ -29245,12 +29245,12 @@
     <row outlineLevel="0" r="904">
       <c r="A904" s="0" t="inlineStr">
         <is>
-          <t>TPP</t>
+          <t>TPJ</t>
         </is>
       </c>
       <c r="B904" s="0" t="inlineStr">
         <is>
-          <t>TEB PORTFÖY PUSULA SERBEST FON</t>
+          <t>TEB PORTFÖY BİRİNCİ SERBEST (DÖVİZ) FON</t>
         </is>
       </c>
       <c r="C904" s="0" t="inlineStr">
@@ -29260,7 +29260,7 @@
       </c>
       <c r="D904" s="0" t="inlineStr">
         <is>
-          <t>Diğer Serbest</t>
+          <t>Döviz</t>
         </is>
       </c>
       <c r="E904" s="0" t="inlineStr">
@@ -29270,34 +29270,34 @@
       </c>
       <c r="F904" s="0" t="inlineStr">
         <is>
-          <t>TL</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="905">
       <c r="A905" s="0" t="inlineStr">
         <is>
-          <t>TPV</t>
+          <t>TPL</t>
         </is>
       </c>
       <c r="B905" s="0" t="inlineStr">
         <is>
-          <t>AURA PORTFÖY İKİNCİ DEĞİŞKEN FON</t>
+          <t>TEB PORTFÖY EUROBOND (DÖVİZ) BORÇLANMA ARAÇLARI FONU</t>
         </is>
       </c>
       <c r="C905" s="0" t="inlineStr">
         <is>
-          <t>Değişken Şemsiye Fonu</t>
+          <t>Borçlanma Araçları Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D905" s="0" t="inlineStr">
         <is>
-          <t>Değişken</t>
+          <t>Eurobond</t>
         </is>
       </c>
       <c r="E905" s="0" t="inlineStr">
         <is>
-          <t>AURA</t>
+          <t>TEB</t>
         </is>
       </c>
       <c r="F905" s="0" t="inlineStr">
@@ -29309,22 +29309,22 @@
     <row outlineLevel="0" r="906">
       <c r="A906" s="0" t="inlineStr">
         <is>
-          <t>TPZ</t>
+          <t>TPP</t>
         </is>
       </c>
       <c r="B906" s="0" t="inlineStr">
         <is>
-          <t>TEB PORTFÖY KİRA SERTİFİKALARI (DÖVİZ) KATILIM FONU</t>
+          <t>TEB PORTFÖY PUSULA SERBEST FON</t>
         </is>
       </c>
       <c r="C906" s="0" t="inlineStr">
         <is>
-          <t>Katılım Şemsiye Fonu</t>
+          <t>Serbest Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D906" s="0" t="inlineStr">
         <is>
-          <t>Kira Sertifikası</t>
+          <t>Diğer Serbest</t>
         </is>
       </c>
       <c r="E906" s="0" t="inlineStr">
@@ -29341,27 +29341,27 @@
     <row outlineLevel="0" r="907">
       <c r="A907" s="0" t="inlineStr">
         <is>
-          <t>TRJ</t>
+          <t>TPV</t>
         </is>
       </c>
       <c r="B907" s="0" t="inlineStr">
         <is>
-          <t>TERA PORTFÖY BİRİNCİ BORÇLANMA ARAÇLARI (TL) FONU</t>
+          <t>AURA PORTFÖY İKİNCİ DEĞİŞKEN FON</t>
         </is>
       </c>
       <c r="C907" s="0" t="inlineStr">
         <is>
-          <t>Borçlanma Araçları Şemsiye Fonu</t>
+          <t>Değişken Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D907" s="0" t="inlineStr">
         <is>
-          <t>Borçlanma Araçları</t>
+          <t>Değişken</t>
         </is>
       </c>
       <c r="E907" s="0" t="inlineStr">
         <is>
-          <t>TERA</t>
+          <t>AURA</t>
         </is>
       </c>
       <c r="F907" s="0" t="inlineStr">
@@ -29373,27 +29373,27 @@
     <row outlineLevel="0" r="908">
       <c r="A908" s="0" t="inlineStr">
         <is>
-          <t>TRO</t>
+          <t>TPZ</t>
         </is>
       </c>
       <c r="B908" s="0" t="inlineStr">
         <is>
-          <t>TRIVE PORTFÖY ALTIN FONU</t>
+          <t>TEB PORTFÖY KİRA SERTİFİKALARI (DÖVİZ) KATILIM FONU</t>
         </is>
       </c>
       <c r="C908" s="0" t="inlineStr">
         <is>
-          <t>Kıymetli Madenler Şemsiye Fonu</t>
+          <t>Katılım Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D908" s="0" t="inlineStr">
         <is>
-          <t>Altın</t>
+          <t>Kira Sertifikası</t>
         </is>
       </c>
       <c r="E908" s="0" t="inlineStr">
         <is>
-          <t>TRIVE</t>
+          <t>TEB</t>
         </is>
       </c>
       <c r="F908" s="0" t="inlineStr">
@@ -29405,22 +29405,22 @@
     <row outlineLevel="0" r="909">
       <c r="A909" s="0" t="inlineStr">
         <is>
-          <t>TRU</t>
+          <t>TRJ</t>
         </is>
       </c>
       <c r="B909" s="0" t="inlineStr">
         <is>
-          <t>TERA PORTFÖY KATILIM SERBEST (DÖVİZ) FON</t>
+          <t>TERA PORTFÖY BİRİNCİ BORÇLANMA ARAÇLARI (TL) FONU</t>
         </is>
       </c>
       <c r="C909" s="0" t="inlineStr">
         <is>
-          <t>Serbest Şemsiye Fonu</t>
+          <t>Borçlanma Araçları Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D909" s="0" t="inlineStr">
         <is>
-          <t>Döviz</t>
+          <t>Borçlanma Araçları</t>
         </is>
       </c>
       <c r="E909" s="0" t="inlineStr">
@@ -29430,19 +29430,19 @@
       </c>
       <c r="F909" s="0" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>TL</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="910">
       <c r="A910" s="0" t="inlineStr">
         <is>
-          <t>TTA</t>
+          <t>TRO</t>
         </is>
       </c>
       <c r="B910" s="0" t="inlineStr">
         <is>
-          <t>İŞ PORTFÖY ALTIN FONU</t>
+          <t>TRIVE PORTFÖY ALTIN FONU</t>
         </is>
       </c>
       <c r="C910" s="0" t="inlineStr">
@@ -29457,7 +29457,7 @@
       </c>
       <c r="E910" s="0" t="inlineStr">
         <is>
-          <t>İŞ</t>
+          <t>TRIVE</t>
         </is>
       </c>
       <c r="F910" s="0" t="inlineStr">
@@ -29469,59 +29469,59 @@
     <row outlineLevel="0" r="911">
       <c r="A911" s="0" t="inlineStr">
         <is>
-          <t>TTE</t>
+          <t>TRU</t>
         </is>
       </c>
       <c r="B911" s="0" t="inlineStr">
         <is>
-          <t>İŞ PORTFÖY BIST TEKNOLOJİ AĞIRLIK SINIRLAMALI ENDEKSİ HİSSE SENEDİ (TL) FONU (HİSSE SENEDİ YOĞUN FON)</t>
+          <t>TERA PORTFÖY KATILIM SERBEST (DÖVİZ) FON</t>
         </is>
       </c>
       <c r="C911" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi Şemsiye Fonu</t>
+          <t>Serbest Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D911" s="0" t="inlineStr">
         <is>
-          <t>BIST Endeks</t>
+          <t>Döviz</t>
         </is>
       </c>
       <c r="E911" s="0" t="inlineStr">
         <is>
-          <t>İŞ</t>
+          <t>TERA</t>
         </is>
       </c>
       <c r="F911" s="0" t="inlineStr">
         <is>
-          <t>TL</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="912">
       <c r="A912" s="0" t="inlineStr">
         <is>
-          <t>TTL</t>
+          <t>TTA</t>
         </is>
       </c>
       <c r="B912" s="0" t="inlineStr">
         <is>
-          <t>TACİRLER PORTFÖY KARTOPU SERBEST FON</t>
+          <t>İŞ PORTFÖY ALTIN FONU</t>
         </is>
       </c>
       <c r="C912" s="0" t="inlineStr">
         <is>
-          <t>Serbest Şemsiye Fonu</t>
+          <t>Kıymetli Madenler Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D912" s="0" t="inlineStr">
         <is>
-          <t>Diğer Serbest</t>
+          <t>Altın</t>
         </is>
       </c>
       <c r="E912" s="0" t="inlineStr">
         <is>
-          <t>TACİRLER</t>
+          <t>İŞ</t>
         </is>
       </c>
       <c r="F912" s="0" t="inlineStr">
@@ -29533,27 +29533,27 @@
     <row outlineLevel="0" r="913">
       <c r="A913" s="0" t="inlineStr">
         <is>
-          <t>TTV</t>
+          <t>TTE</t>
         </is>
       </c>
       <c r="B913" s="0" t="inlineStr">
         <is>
-          <t>TACİRLER PORTFÖY VEGA SERBEST (TL)  FON</t>
+          <t>İŞ PORTFÖY BIST TEKNOLOJİ AĞIRLIK SINIRLAMALI ENDEKSİ HİSSE SENEDİ (TL) FONU (HİSSE SENEDİ YOĞUN FON)</t>
         </is>
       </c>
       <c r="C913" s="0" t="inlineStr">
         <is>
-          <t>Serbest Şemsiye Fonu</t>
+          <t>Hisse Senedi Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D913" s="0" t="inlineStr">
         <is>
-          <t>Diğer Serbest</t>
+          <t>BIST Endeks</t>
         </is>
       </c>
       <c r="E913" s="0" t="inlineStr">
         <is>
-          <t>TACİRLER</t>
+          <t>İŞ</t>
         </is>
       </c>
       <c r="F913" s="0" t="inlineStr">
@@ -29565,27 +29565,27 @@
     <row outlineLevel="0" r="914">
       <c r="A914" s="0" t="inlineStr">
         <is>
-          <t>TUA</t>
+          <t>TTL</t>
         </is>
       </c>
       <c r="B914" s="0" t="inlineStr">
         <is>
-          <t>TEB PORTFÖY ALTIN FONU</t>
+          <t>TACİRLER PORTFÖY KARTOPU SERBEST FON</t>
         </is>
       </c>
       <c r="C914" s="0" t="inlineStr">
         <is>
-          <t>Kıymetli Madenler Şemsiye Fonu</t>
+          <t>Serbest Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D914" s="0" t="inlineStr">
         <is>
-          <t>Altın</t>
+          <t>Diğer Serbest</t>
         </is>
       </c>
       <c r="E914" s="0" t="inlineStr">
         <is>
-          <t>TEB</t>
+          <t>TACİRLER</t>
         </is>
       </c>
       <c r="F914" s="0" t="inlineStr">
@@ -29597,27 +29597,27 @@
     <row outlineLevel="0" r="915">
       <c r="A915" s="0" t="inlineStr">
         <is>
-          <t>TVE</t>
+          <t>TTV</t>
         </is>
       </c>
       <c r="B915" s="0" t="inlineStr">
         <is>
-          <t>EMAA BLUE PORTFÖY TARIM VE GIDA SEKTÖRÜ KATILIM FONU</t>
+          <t>TACİRLER PORTFÖY VEGA SERBEST (TL)  FON</t>
         </is>
       </c>
       <c r="C915" s="0" t="inlineStr">
         <is>
-          <t>Katılım Şemsiye Fonu</t>
+          <t>Serbest Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D915" s="0" t="inlineStr">
         <is>
-          <t>Tematik</t>
+          <t>Diğer Serbest</t>
         </is>
       </c>
       <c r="E915" s="0" t="inlineStr">
         <is>
-          <t>EMAA BLUE</t>
+          <t>TACİRLER</t>
         </is>
       </c>
       <c r="F915" s="0" t="inlineStr">
@@ -29629,27 +29629,27 @@
     <row outlineLevel="0" r="916">
       <c r="A916" s="0" t="inlineStr">
         <is>
-          <t>TVN</t>
+          <t>TUA</t>
         </is>
       </c>
       <c r="B916" s="0" t="inlineStr">
         <is>
-          <t>TRIVE PORTFÖY BİRİNCİ FON SEPETİ FONU</t>
+          <t>TEB PORTFÖY ALTIN FONU</t>
         </is>
       </c>
       <c r="C916" s="0" t="inlineStr">
         <is>
-          <t>Fon Sepeti Şemsiye Fonu</t>
+          <t>Kıymetli Madenler Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D916" s="0" t="inlineStr">
         <is>
-          <t>Fon Sepeti</t>
+          <t>Altın</t>
         </is>
       </c>
       <c r="E916" s="0" t="inlineStr">
         <is>
-          <t>TRIVE</t>
+          <t>TEB</t>
         </is>
       </c>
       <c r="F916" s="0" t="inlineStr">
@@ -29661,27 +29661,27 @@
     <row outlineLevel="0" r="917">
       <c r="A917" s="0" t="inlineStr">
         <is>
-          <t>TYH</t>
+          <t>TVE</t>
         </is>
       </c>
       <c r="B917" s="0" t="inlineStr">
         <is>
-          <t>TEB PORTFÖY HİSSE SENEDİ FONU (HİSSE SENEDİ YOĞUN FON)</t>
+          <t>EMAA BLUE PORTFÖY TARIM VE GIDA SEKTÖRÜ KATILIM FONU</t>
         </is>
       </c>
       <c r="C917" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi Şemsiye Fonu</t>
+          <t>Katılım Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D917" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi</t>
+          <t>Tematik</t>
         </is>
       </c>
       <c r="E917" s="0" t="inlineStr">
         <is>
-          <t>TEB</t>
+          <t>EMAA BLUE</t>
         </is>
       </c>
       <c r="F917" s="0" t="inlineStr">
@@ -29693,27 +29693,27 @@
     <row outlineLevel="0" r="918">
       <c r="A918" s="0" t="inlineStr">
         <is>
-          <t>TZD</t>
+          <t>TVN</t>
         </is>
       </c>
       <c r="B918" s="0" t="inlineStr">
         <is>
-          <t>ZİRAAT PORTFÖY HİSSE SENEDİ FONU (HİSSE SENEDİ YOĞUN FON)</t>
+          <t>TRIVE PORTFÖY BİRİNCİ FON SEPETİ FONU</t>
         </is>
       </c>
       <c r="C918" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi Şemsiye Fonu</t>
+          <t>Fon Sepeti Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D918" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi</t>
+          <t>Fon Sepeti</t>
         </is>
       </c>
       <c r="E918" s="0" t="inlineStr">
         <is>
-          <t>ZİRAAT</t>
+          <t>TRIVE</t>
         </is>
       </c>
       <c r="F918" s="0" t="inlineStr">
@@ -29725,27 +29725,27 @@
     <row outlineLevel="0" r="919">
       <c r="A919" s="0" t="inlineStr">
         <is>
-          <t>TZT</t>
+          <t>TYH</t>
         </is>
       </c>
       <c r="B919" s="0" t="inlineStr">
         <is>
-          <t>ZİRAAT PORTFÖY BORÇLANMA ARAÇLARI (TL) FONU</t>
+          <t>TEB PORTFÖY HİSSE SENEDİ FONU (HİSSE SENEDİ YOĞUN FON)</t>
         </is>
       </c>
       <c r="C919" s="0" t="inlineStr">
         <is>
-          <t>Borçlanma Araçları Şemsiye Fonu</t>
+          <t>Hisse Senedi Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D919" s="0" t="inlineStr">
         <is>
-          <t>Borçlanma Araçları</t>
+          <t>Hisse Senedi</t>
         </is>
       </c>
       <c r="E919" s="0" t="inlineStr">
         <is>
-          <t>ZİRAAT</t>
+          <t>TEB</t>
         </is>
       </c>
       <c r="F919" s="0" t="inlineStr">
@@ -29757,27 +29757,27 @@
     <row outlineLevel="0" r="920">
       <c r="A920" s="0" t="inlineStr">
         <is>
-          <t>ULH</t>
+          <t>TZD</t>
         </is>
       </c>
       <c r="B920" s="0" t="inlineStr">
         <is>
-          <t>ÜNLÜ PORTFÖY ONUNCU SERBEST FON</t>
+          <t>ZİRAAT PORTFÖY HİSSE SENEDİ FONU (HİSSE SENEDİ YOĞUN FON)</t>
         </is>
       </c>
       <c r="C920" s="0" t="inlineStr">
         <is>
-          <t>Serbest Şemsiye Fonu</t>
+          <t>Hisse Senedi Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D920" s="0" t="inlineStr">
         <is>
-          <t>Diğer Serbest</t>
+          <t>Hisse Senedi</t>
         </is>
       </c>
       <c r="E920" s="0" t="inlineStr">
         <is>
-          <t>ÜNLÜ</t>
+          <t>ZİRAAT</t>
         </is>
       </c>
       <c r="F920" s="0" t="inlineStr">
@@ -29789,27 +29789,27 @@
     <row outlineLevel="0" r="921">
       <c r="A921" s="0" t="inlineStr">
         <is>
-          <t>UNT</t>
+          <t>TZT</t>
         </is>
       </c>
       <c r="B921" s="0" t="inlineStr">
         <is>
-          <t>İŞ PORTFÖY ÜÇÜNCÜ SERBEST (TL) FON</t>
+          <t>ZİRAAT PORTFÖY BORÇLANMA ARAÇLARI (TL) FONU</t>
         </is>
       </c>
       <c r="C921" s="0" t="inlineStr">
         <is>
-          <t>Serbest Şemsiye Fonu</t>
+          <t>Borçlanma Araçları Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D921" s="0" t="inlineStr">
         <is>
-          <t>Diğer Serbest</t>
+          <t>Borçlanma Araçları</t>
         </is>
       </c>
       <c r="E921" s="0" t="inlineStr">
         <is>
-          <t>İŞ</t>
+          <t>ZİRAAT</t>
         </is>
       </c>
       <c r="F921" s="0" t="inlineStr">
@@ -29821,22 +29821,22 @@
     <row outlineLevel="0" r="922">
       <c r="A922" s="0" t="inlineStr">
         <is>
-          <t>UP1</t>
+          <t>ULH</t>
         </is>
       </c>
       <c r="B922" s="0" t="inlineStr">
         <is>
-          <t>ÜNLÜ PORTFÖY ALTIN FONU</t>
+          <t>ÜNLÜ PORTFÖY ONUNCU SERBEST FON</t>
         </is>
       </c>
       <c r="C922" s="0" t="inlineStr">
         <is>
-          <t>Kıymetli Madenler Şemsiye Fonu</t>
+          <t>Serbest Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D922" s="0" t="inlineStr">
         <is>
-          <t>Altın</t>
+          <t>Diğer Serbest</t>
         </is>
       </c>
       <c r="E922" s="0" t="inlineStr">
@@ -29853,12 +29853,12 @@
     <row outlineLevel="0" r="923">
       <c r="A923" s="0" t="inlineStr">
         <is>
-          <t>UP2</t>
+          <t>UNT</t>
         </is>
       </c>
       <c r="B923" s="0" t="inlineStr">
         <is>
-          <t>ÜNLÜ PORTFÖY PARA PİYASASI SERBEST FON</t>
+          <t>İŞ PORTFÖY ÜÇÜNCÜ SERBEST (TL) FON</t>
         </is>
       </c>
       <c r="C923" s="0" t="inlineStr">
@@ -29868,12 +29868,12 @@
       </c>
       <c r="D923" s="0" t="inlineStr">
         <is>
-          <t>Para Piyasası</t>
+          <t>Diğer Serbest</t>
         </is>
       </c>
       <c r="E923" s="0" t="inlineStr">
         <is>
-          <t>ÜNLÜ</t>
+          <t>İŞ</t>
         </is>
       </c>
       <c r="F923" s="0" t="inlineStr">
@@ -29885,22 +29885,22 @@
     <row outlineLevel="0" r="924">
       <c r="A924" s="0" t="inlineStr">
         <is>
-          <t>UPD</t>
+          <t>UP1</t>
         </is>
       </c>
       <c r="B924" s="0" t="inlineStr">
         <is>
-          <t>ÜNLÜ PORTFÖY DÖRDÜNCÜ SERBEST (DÖVIZ) FON</t>
+          <t>ÜNLÜ PORTFÖY ALTIN FONU</t>
         </is>
       </c>
       <c r="C924" s="0" t="inlineStr">
         <is>
-          <t>Serbest Şemsiye Fonu</t>
+          <t>Kıymetli Madenler Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D924" s="0" t="inlineStr">
         <is>
-          <t>Döviz</t>
+          <t>Altın</t>
         </is>
       </c>
       <c r="E924" s="0" t="inlineStr">
@@ -29910,29 +29910,29 @@
       </c>
       <c r="F924" s="0" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>TL</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="925">
       <c r="A925" s="0" t="inlineStr">
         <is>
-          <t>UPH</t>
+          <t>UP2</t>
         </is>
       </c>
       <c r="B925" s="0" t="inlineStr">
         <is>
-          <t>ÜNLÜ PORTFÖY HİSSE SENEDİ (TL) FONU(HİSSE SENEDİ YOĞUN FON)</t>
+          <t>ÜNLÜ PORTFÖY PARA PİYASASI SERBEST FON</t>
         </is>
       </c>
       <c r="C925" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi Şemsiye Fonu</t>
+          <t>Serbest Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D925" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi</t>
+          <t>Para Piyasası</t>
         </is>
       </c>
       <c r="E925" s="0" t="inlineStr">
@@ -29949,22 +29949,22 @@
     <row outlineLevel="0" r="926">
       <c r="A926" s="0" t="inlineStr">
         <is>
-          <t>UPP</t>
+          <t>UPD</t>
         </is>
       </c>
       <c r="B926" s="0" t="inlineStr">
         <is>
-          <t>ÜNLÜ PORTFÖY PARA PİYASASI (TL) FONU</t>
+          <t>ÜNLÜ PORTFÖY DÖRDÜNCÜ SERBEST (DÖVIZ) FON</t>
         </is>
       </c>
       <c r="C926" s="0" t="inlineStr">
         <is>
-          <t>Para Piyasası Şemsiye Fonu</t>
+          <t>Serbest Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D926" s="0" t="inlineStr">
         <is>
-          <t>Para Piyasası</t>
+          <t>Döviz</t>
         </is>
       </c>
       <c r="E926" s="0" t="inlineStr">
@@ -29974,34 +29974,34 @@
       </c>
       <c r="F926" s="0" t="inlineStr">
         <is>
-          <t>TL</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="927">
       <c r="A927" s="0" t="inlineStr">
         <is>
-          <t>URA</t>
+          <t>UPH</t>
         </is>
       </c>
       <c r="B927" s="0" t="inlineStr">
         <is>
-          <t>ATA PORTFÖY ENERJİ DEĞİŞKEN FON</t>
+          <t>ÜNLÜ PORTFÖY HİSSE SENEDİ (TL) FONU(HİSSE SENEDİ YOĞUN FON)</t>
         </is>
       </c>
       <c r="C927" s="0" t="inlineStr">
         <is>
-          <t>Değişken Şemsiye Fonu</t>
+          <t>Hisse Senedi Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D927" s="0" t="inlineStr">
         <is>
-          <t>Tematik</t>
+          <t>Hisse Senedi</t>
         </is>
       </c>
       <c r="E927" s="0" t="inlineStr">
         <is>
-          <t>ATA</t>
+          <t>ÜNLÜ</t>
         </is>
       </c>
       <c r="F927" s="0" t="inlineStr">
@@ -30013,22 +30013,22 @@
     <row outlineLevel="0" r="928">
       <c r="A928" s="0" t="inlineStr">
         <is>
-          <t>USY</t>
+          <t>UPP</t>
         </is>
       </c>
       <c r="B928" s="0" t="inlineStr">
         <is>
-          <t>ÜNLÜ PORTFÖY DEĞER YATIRIMLARI SERBEST FON</t>
+          <t>ÜNLÜ PORTFÖY PARA PİYASASI (TL) FONU</t>
         </is>
       </c>
       <c r="C928" s="0" t="inlineStr">
         <is>
-          <t>Serbest Şemsiye Fonu</t>
+          <t>Para Piyasası Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D928" s="0" t="inlineStr">
         <is>
-          <t>Diğer Serbest</t>
+          <t>Para Piyasası</t>
         </is>
       </c>
       <c r="E928" s="0" t="inlineStr">
@@ -30045,17 +30045,17 @@
     <row outlineLevel="0" r="929">
       <c r="A929" s="0" t="inlineStr">
         <is>
-          <t>VAY</t>
+          <t>URA</t>
         </is>
       </c>
       <c r="B929" s="0" t="inlineStr">
         <is>
-          <t>AK PORTFÖY DEĞER ODAKLI 100 ŞİRKETLERİ HİSSE SENEDİ (TL) FONU (HİSSE SENEDİ YOĞUN FON)</t>
+          <t>ATA PORTFÖY ENERJİ DEĞİŞKEN FON</t>
         </is>
       </c>
       <c r="C929" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi Şemsiye Fonu</t>
+          <t>Değişken Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D929" s="0" t="inlineStr">
@@ -30065,7 +30065,7 @@
       </c>
       <c r="E929" s="0" t="inlineStr">
         <is>
-          <t>AK</t>
+          <t>ATA</t>
         </is>
       </c>
       <c r="F929" s="0" t="inlineStr">
@@ -30077,27 +30077,27 @@
     <row outlineLevel="0" r="930">
       <c r="A930" s="0" t="inlineStr">
         <is>
-          <t>VCY</t>
+          <t>USY</t>
         </is>
       </c>
       <c r="B930" s="0" t="inlineStr">
         <is>
-          <t>AK PORTFÖY ELEKTRİKLİ VE OTONOM ARAÇ TEKNOLOJİLERİ DEĞİŞKEN FON</t>
+          <t>ÜNLÜ PORTFÖY DEĞER YATIRIMLARI SERBEST FON</t>
         </is>
       </c>
       <c r="C930" s="0" t="inlineStr">
         <is>
-          <t>Değişken Şemsiye Fonu</t>
+          <t>Serbest Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D930" s="0" t="inlineStr">
         <is>
-          <t>Teknoloji Temalı</t>
+          <t>Diğer Serbest</t>
         </is>
       </c>
       <c r="E930" s="0" t="inlineStr">
         <is>
-          <t>AK</t>
+          <t>ÜNLÜ</t>
         </is>
       </c>
       <c r="F930" s="0" t="inlineStr">
@@ -30109,27 +30109,27 @@
     <row outlineLevel="0" r="931">
       <c r="A931" s="0" t="inlineStr">
         <is>
-          <t>VFK</t>
+          <t>VAY</t>
         </is>
       </c>
       <c r="B931" s="0" t="inlineStr">
         <is>
-          <t>ZİRAAT PORTFÖY İKİNCİ KISA VADELİ KİRA SERTİFİKALARI KATILIM (TL) FONU</t>
+          <t>AK PORTFÖY DEĞER ODAKLI 100 ŞİRKETLERİ HİSSE SENEDİ (TL) FONU (HİSSE SENEDİ YOĞUN FON)</t>
         </is>
       </c>
       <c r="C931" s="0" t="inlineStr">
         <is>
-          <t>Katılım Şemsiye Fonu</t>
+          <t>Hisse Senedi Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D931" s="0" t="inlineStr">
         <is>
-          <t>Kira Sertifikası</t>
+          <t>Tematik</t>
         </is>
       </c>
       <c r="E931" s="0" t="inlineStr">
         <is>
-          <t>ZİRAAT</t>
+          <t>AK</t>
         </is>
       </c>
       <c r="F931" s="0" t="inlineStr">
@@ -30141,27 +30141,27 @@
     <row outlineLevel="0" r="932">
       <c r="A932" s="0" t="inlineStr">
         <is>
-          <t>VFO</t>
+          <t>VCY</t>
         </is>
       </c>
       <c r="B932" s="0" t="inlineStr">
         <is>
-          <t>V PORTFÖY ALTIN KATILIM FONU</t>
+          <t>AK PORTFÖY ELEKTRİKLİ VE OTONOM ARAÇ TEKNOLOJİLERİ DEĞİŞKEN FON</t>
         </is>
       </c>
       <c r="C932" s="0" t="inlineStr">
         <is>
-          <t>Katılım Şemsiye Fonu</t>
+          <t>Değişken Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D932" s="0" t="inlineStr">
         <is>
-          <t>Altın</t>
+          <t>Teknoloji Temalı</t>
         </is>
       </c>
       <c r="E932" s="0" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>AK</t>
         </is>
       </c>
       <c r="F932" s="0" t="inlineStr">
@@ -30173,27 +30173,27 @@
     <row outlineLevel="0" r="933">
       <c r="A933" s="0" t="inlineStr">
         <is>
-          <t>VHS</t>
+          <t>VFK</t>
         </is>
       </c>
       <c r="B933" s="0" t="inlineStr">
         <is>
-          <t>VAKIF KATILIM PORTFÖY KATILIM HİSSE SENEDİ FONU (HİSSE SENEDİ YOĞUN FON)</t>
+          <t>ZİRAAT PORTFÖY İKİNCİ KISA VADELİ KİRA SERTİFİKALARI KATILIM (TL) FONU</t>
         </is>
       </c>
       <c r="C933" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi Şemsiye Fonu</t>
+          <t>Katılım Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D933" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi</t>
+          <t>Kira Sertifikası</t>
         </is>
       </c>
       <c r="E933" s="0" t="inlineStr">
         <is>
-          <t>VAKIF KATILIM</t>
+          <t>ZİRAAT</t>
         </is>
       </c>
       <c r="F933" s="0" t="inlineStr">
@@ -30205,12 +30205,12 @@
     <row outlineLevel="0" r="934">
       <c r="A934" s="0" t="inlineStr">
         <is>
-          <t>VKK</t>
+          <t>VFO</t>
         </is>
       </c>
       <c r="B934" s="0" t="inlineStr">
         <is>
-          <t>VAKIF KATILIM PORTFÖY KİRA SERTİFİKALARI KATILIM FONU</t>
+          <t>V PORTFÖY ALTIN KATILIM FONU</t>
         </is>
       </c>
       <c r="C934" s="0" t="inlineStr">
@@ -30220,12 +30220,12 @@
       </c>
       <c r="D934" s="0" t="inlineStr">
         <is>
-          <t>Kira Sertifikası</t>
+          <t>Altın</t>
         </is>
       </c>
       <c r="E934" s="0" t="inlineStr">
         <is>
-          <t>VAKIF KATILIM</t>
+          <t>V</t>
         </is>
       </c>
       <c r="F934" s="0" t="inlineStr">
@@ -30237,22 +30237,22 @@
     <row outlineLevel="0" r="935">
       <c r="A935" s="0" t="inlineStr">
         <is>
-          <t>VKV</t>
+          <t>VHS</t>
         </is>
       </c>
       <c r="B935" s="0" t="inlineStr">
         <is>
-          <t>VAKIF KATILIM PORTFÖY KISA VADELİ KİRA SERTİFİKALARI KATILIM FONU</t>
+          <t>VAKIF KATILIM PORTFÖY KATILIM HİSSE SENEDİ FONU (HİSSE SENEDİ YOĞUN FON)</t>
         </is>
       </c>
       <c r="C935" s="0" t="inlineStr">
         <is>
-          <t>Katılım Şemsiye Fonu</t>
+          <t>Hisse Senedi Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D935" s="0" t="inlineStr">
         <is>
-          <t>Kira Sertifikası</t>
+          <t>Hisse Senedi</t>
         </is>
       </c>
       <c r="E935" s="0" t="inlineStr">
@@ -30269,12 +30269,12 @@
     <row outlineLevel="0" r="936">
       <c r="A936" s="0" t="inlineStr">
         <is>
-          <t>VLT</t>
+          <t>VKK</t>
         </is>
       </c>
       <c r="B936" s="0" t="inlineStr">
         <is>
-          <t>VAKIF KATILIM PORTFÖY ALTIN KATILIM FONU</t>
+          <t>VAKIF KATILIM PORTFÖY KİRA SERTİFİKALARI KATILIM FONU</t>
         </is>
       </c>
       <c r="C936" s="0" t="inlineStr">
@@ -30284,7 +30284,7 @@
       </c>
       <c r="D936" s="0" t="inlineStr">
         <is>
-          <t>Altın</t>
+          <t>Kira Sertifikası</t>
         </is>
       </c>
       <c r="E936" s="0" t="inlineStr">
@@ -30301,27 +30301,27 @@
     <row outlineLevel="0" r="937">
       <c r="A937" s="0" t="inlineStr">
         <is>
-          <t>VMV</t>
+          <t>VKV</t>
         </is>
       </c>
       <c r="B937" s="0" t="inlineStr">
         <is>
-          <t>VEGA PORTFÖY MAVİ SERBEST FON</t>
+          <t>VAKIF KATILIM PORTFÖY KISA VADELİ KİRA SERTİFİKALARI KATILIM FONU</t>
         </is>
       </c>
       <c r="C937" s="0" t="inlineStr">
         <is>
-          <t>Serbest Şemsiye Fonu</t>
+          <t>Katılım Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D937" s="0" t="inlineStr">
         <is>
-          <t>Diğer Serbest</t>
+          <t>Kira Sertifikası</t>
         </is>
       </c>
       <c r="E937" s="0" t="inlineStr">
         <is>
-          <t>VEGA</t>
+          <t>VAKIF KATILIM</t>
         </is>
       </c>
       <c r="F937" s="0" t="inlineStr">
@@ -30333,27 +30333,27 @@
     <row outlineLevel="0" r="938">
       <c r="A938" s="0" t="inlineStr">
         <is>
-          <t>VNK</t>
+          <t>VLT</t>
         </is>
       </c>
       <c r="B938" s="0" t="inlineStr">
         <is>
-          <t>VEGA PORTFÖY ANKA SERBEST FON</t>
+          <t>VAKIF KATILIM PORTFÖY ALTIN KATILIM FONU</t>
         </is>
       </c>
       <c r="C938" s="0" t="inlineStr">
         <is>
-          <t>Serbest Şemsiye Fonu</t>
+          <t>Katılım Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D938" s="0" t="inlineStr">
         <is>
-          <t>Diğer Serbest</t>
+          <t>Altın</t>
         </is>
       </c>
       <c r="E938" s="0" t="inlineStr">
         <is>
-          <t>VEGA</t>
+          <t>VAKIF KATILIM</t>
         </is>
       </c>
       <c r="F938" s="0" t="inlineStr">
@@ -30365,27 +30365,27 @@
     <row outlineLevel="0" r="939">
       <c r="A939" s="0" t="inlineStr">
         <is>
-          <t>VPA</t>
+          <t>VMV</t>
         </is>
       </c>
       <c r="B939" s="0" t="inlineStr">
         <is>
-          <t>VAKIF KATILIM PORTFÖY PARA PİYASASI KATILIM FONU</t>
+          <t>VEGA PORTFÖY MAVİ SERBEST FON</t>
         </is>
       </c>
       <c r="C939" s="0" t="inlineStr">
         <is>
-          <t>Katılım Şemsiye Fonu</t>
+          <t>Serbest Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D939" s="0" t="inlineStr">
         <is>
-          <t>Para Piyasası</t>
+          <t>Diğer Serbest</t>
         </is>
       </c>
       <c r="E939" s="0" t="inlineStr">
         <is>
-          <t>VAKIF KATILIM</t>
+          <t>VEGA</t>
         </is>
       </c>
       <c r="F939" s="0" t="inlineStr">
@@ -30397,12 +30397,12 @@
     <row outlineLevel="0" r="940">
       <c r="A940" s="0" t="inlineStr">
         <is>
-          <t>VPP</t>
+          <t>VNK</t>
         </is>
       </c>
       <c r="B940" s="0" t="inlineStr">
         <is>
-          <t>VEGA PORTFÖY PARLA SERBEST (DÖVİZ) FON</t>
+          <t>VEGA PORTFÖY ANKA SERBEST FON</t>
         </is>
       </c>
       <c r="C940" s="0" t="inlineStr">
@@ -30412,7 +30412,7 @@
       </c>
       <c r="D940" s="0" t="inlineStr">
         <is>
-          <t>Döviz</t>
+          <t>Diğer Serbest</t>
         </is>
       </c>
       <c r="E940" s="0" t="inlineStr">
@@ -30422,34 +30422,34 @@
       </c>
       <c r="F940" s="0" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>TL</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="941">
       <c r="A941" s="0" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>VPA</t>
         </is>
       </c>
       <c r="B941" s="0" t="inlineStr">
         <is>
-          <t>VEGA PORTFÖY SALUR HİSSE SENEDİ SERBEST (TL) FON (HİSSE SENEDİ YOĞUN FON)</t>
+          <t>VAKIF KATILIM PORTFÖY PARA PİYASASI KATILIM FONU</t>
         </is>
       </c>
       <c r="C941" s="0" t="inlineStr">
         <is>
-          <t>Serbest Şemsiye Fonu</t>
+          <t>Katılım Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D941" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi</t>
+          <t>Para Piyasası</t>
         </is>
       </c>
       <c r="E941" s="0" t="inlineStr">
         <is>
-          <t>VEGA</t>
+          <t>VAKIF KATILIM</t>
         </is>
       </c>
       <c r="F941" s="0" t="inlineStr">
@@ -30461,59 +30461,59 @@
     <row outlineLevel="0" r="942">
       <c r="A942" s="0" t="inlineStr">
         <is>
-          <t>VRK</t>
+          <t>VPP</t>
         </is>
       </c>
       <c r="B942" s="0" t="inlineStr">
         <is>
-          <t>DENİZ PORTFÖY ÇOKLU VARLIK KATILIM FONU</t>
+          <t>VEGA PORTFÖY PARLA SERBEST (DÖVİZ) FON</t>
         </is>
       </c>
       <c r="C942" s="0" t="inlineStr">
         <is>
-          <t>Katılım Şemsiye Fonu</t>
+          <t>Serbest Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D942" s="0" t="inlineStr">
         <is>
-          <t>Çoklu Varlık</t>
+          <t>Döviz</t>
         </is>
       </c>
       <c r="E942" s="0" t="inlineStr">
         <is>
-          <t>DENİZ</t>
+          <t>VEGA</t>
         </is>
       </c>
       <c r="F942" s="0" t="inlineStr">
         <is>
-          <t>TL</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="943">
       <c r="A943" s="0" t="inlineStr">
         <is>
-          <t>YAC</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="B943" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY İKİNCİ FON SEPETİ FONU</t>
+          <t>VEGA PORTFÖY SALUR HİSSE SENEDİ SERBEST (TL) FON (HİSSE SENEDİ YOĞUN FON)</t>
         </is>
       </c>
       <c r="C943" s="0" t="inlineStr">
         <is>
-          <t>Fon Sepeti Şemsiye Fonu</t>
+          <t>Serbest Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D943" s="0" t="inlineStr">
         <is>
-          <t>Fon Sepeti</t>
+          <t>Hisse Senedi</t>
         </is>
       </c>
       <c r="E943" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ</t>
+          <t>VEGA</t>
         </is>
       </c>
       <c r="F943" s="0" t="inlineStr">
@@ -30525,27 +30525,27 @@
     <row outlineLevel="0" r="944">
       <c r="A944" s="0" t="inlineStr">
         <is>
-          <t>YAE</t>
+          <t>VRK</t>
         </is>
       </c>
       <c r="B944" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY TLREF'E ENDEKSLİ BORÇLANMA ARAÇLARI (TL) FONU</t>
+          <t>DENİZ PORTFÖY ÇOKLU VARLIK KATILIM FONU</t>
         </is>
       </c>
       <c r="C944" s="0" t="inlineStr">
         <is>
-          <t>Borçlanma Araçları Şemsiye Fonu</t>
+          <t>Katılım Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D944" s="0" t="inlineStr">
         <is>
-          <t>Borçlanma Araçları</t>
+          <t>Çoklu Varlık</t>
         </is>
       </c>
       <c r="E944" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ</t>
+          <t>DENİZ</t>
         </is>
       </c>
       <c r="F944" s="0" t="inlineStr">
@@ -30557,22 +30557,22 @@
     <row outlineLevel="0" r="945">
       <c r="A945" s="0" t="inlineStr">
         <is>
-          <t>YAK</t>
+          <t>YAC</t>
         </is>
       </c>
       <c r="B945" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY KARMA FON</t>
+          <t>YAPI KREDİ PORTFÖY İKİNCİ FON SEPETİ FONU</t>
         </is>
       </c>
       <c r="C945" s="0" t="inlineStr">
         <is>
-          <t>Karma Şemsiye Fonu</t>
+          <t>Fon Sepeti Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D945" s="0" t="inlineStr">
         <is>
-          <t>Karma</t>
+          <t>Fon Sepeti</t>
         </is>
       </c>
       <c r="E945" s="0" t="inlineStr">
@@ -30589,22 +30589,22 @@
     <row outlineLevel="0" r="946">
       <c r="A946" s="0" t="inlineStr">
         <is>
-          <t>YAN</t>
+          <t>YAE</t>
         </is>
       </c>
       <c r="B946" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY BİRİNCİ FON SEPETİ FONU</t>
+          <t>YAPI KREDİ PORTFÖY TLREF'E ENDEKSLİ BORÇLANMA ARAÇLARI (TL) FONU</t>
         </is>
       </c>
       <c r="C946" s="0" t="inlineStr">
         <is>
-          <t>Fon Sepeti Şemsiye Fonu</t>
+          <t>Borçlanma Araçları Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D946" s="0" t="inlineStr">
         <is>
-          <t>Fon Sepeti</t>
+          <t>Borçlanma Araçları</t>
         </is>
       </c>
       <c r="E946" s="0" t="inlineStr">
@@ -30621,22 +30621,22 @@
     <row outlineLevel="0" r="947">
       <c r="A947" s="0" t="inlineStr">
         <is>
-          <t>YAS</t>
+          <t>YAK</t>
         </is>
       </c>
       <c r="B947" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY KOÇ HOLDİNG İŞTİRAK VE HİSSE SENEDİ FONU(HİSSE SENEDİ YOĞUN FON)</t>
+          <t>YAPI KREDİ PORTFÖY KARMA FON</t>
         </is>
       </c>
       <c r="C947" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi Şemsiye Fonu</t>
+          <t>Karma Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D947" s="0" t="inlineStr">
         <is>
-          <t>Tematik</t>
+          <t>Karma</t>
         </is>
       </c>
       <c r="E947" s="0" t="inlineStr">
@@ -30653,22 +30653,22 @@
     <row outlineLevel="0" r="948">
       <c r="A948" s="0" t="inlineStr">
         <is>
-          <t>YAY</t>
+          <t>YAN</t>
         </is>
       </c>
       <c r="B948" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY YABANCI TEKNOLOJİ SEKTÖRÜ HİSSE SENEDİ FONU</t>
+          <t>YAPI KREDİ PORTFÖY BİRİNCİ FON SEPETİ FONU</t>
         </is>
       </c>
       <c r="C948" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi Şemsiye Fonu</t>
+          <t>Fon Sepeti Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D948" s="0" t="inlineStr">
         <is>
-          <t>Teknoloji Temalı</t>
+          <t>Fon Sepeti</t>
         </is>
       </c>
       <c r="E948" s="0" t="inlineStr">
@@ -30685,22 +30685,22 @@
     <row outlineLevel="0" r="949">
       <c r="A949" s="0" t="inlineStr">
         <is>
-          <t>YBE</t>
+          <t>YAS</t>
         </is>
       </c>
       <c r="B949" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY EUROBOND (DOLAR) BORÇLANMA ARAÇLARI FONU</t>
+          <t>YAPI KREDİ PORTFÖY KOÇ HOLDİNG İŞTİRAK VE HİSSE SENEDİ FONU(HİSSE SENEDİ YOĞUN FON)</t>
         </is>
       </c>
       <c r="C949" s="0" t="inlineStr">
         <is>
-          <t>Borçlanma Araçları Şemsiye Fonu</t>
+          <t>Hisse Senedi Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D949" s="0" t="inlineStr">
         <is>
-          <t>Eurobond</t>
+          <t>Tematik</t>
         </is>
       </c>
       <c r="E949" s="0" t="inlineStr">
@@ -30717,22 +30717,22 @@
     <row outlineLevel="0" r="950">
       <c r="A950" s="0" t="inlineStr">
         <is>
-          <t>YBH</t>
+          <t>YAY</t>
         </is>
       </c>
       <c r="B950" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY 5-15 YIL VADELİ SERBEST (DÖVİZ) FON</t>
+          <t>YAPI KREDİ PORTFÖY YABANCI TEKNOLOJİ SEKTÖRÜ HİSSE SENEDİ FONU</t>
         </is>
       </c>
       <c r="C950" s="0" t="inlineStr">
         <is>
-          <t>Serbest Şemsiye Fonu</t>
+          <t>Hisse Senedi Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D950" s="0" t="inlineStr">
         <is>
-          <t>Döviz</t>
+          <t>Teknoloji Temalı</t>
         </is>
       </c>
       <c r="E950" s="0" t="inlineStr">
@@ -30742,61 +30742,61 @@
       </c>
       <c r="F950" s="0" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>TL</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="951">
       <c r="A951" s="0" t="inlineStr">
         <is>
-          <t>YBR</t>
+          <t>YBE</t>
         </is>
       </c>
       <c r="B951" s="0" t="inlineStr">
         <is>
-          <t>İŞ PORTFÖY YİRMİBİRİNCİ SERBEST (DÖVİZ) FON</t>
+          <t>YAPI KREDİ PORTFÖY EUROBOND (DOLAR) BORÇLANMA ARAÇLARI FONU</t>
         </is>
       </c>
       <c r="C951" s="0" t="inlineStr">
         <is>
-          <t>Serbest Şemsiye Fonu</t>
+          <t>Borçlanma Araçları Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D951" s="0" t="inlineStr">
         <is>
-          <t>Döviz</t>
+          <t>Eurobond</t>
         </is>
       </c>
       <c r="E951" s="0" t="inlineStr">
         <is>
-          <t>İŞ</t>
+          <t>YAPI KREDİ</t>
         </is>
       </c>
       <c r="F951" s="0" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>TL</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="952">
       <c r="A952" s="0" t="inlineStr">
         <is>
-          <t>YBS</t>
+          <t>YBH</t>
         </is>
       </c>
       <c r="B952" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY ÖZEL SEKTÖR BORÇLANMA ARAÇLARI FONU</t>
+          <t>YAPI KREDİ PORTFÖY 5-15 YIL VADELİ SERBEST (DÖVİZ) FON</t>
         </is>
       </c>
       <c r="C952" s="0" t="inlineStr">
         <is>
-          <t>Borçlanma Araçları Şemsiye Fonu</t>
+          <t>Serbest Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D952" s="0" t="inlineStr">
         <is>
-          <t>Özel Sektör Borçlanma Araçları</t>
+          <t>Döviz</t>
         </is>
       </c>
       <c r="E952" s="0" t="inlineStr">
@@ -30806,19 +30806,19 @@
       </c>
       <c r="F952" s="0" t="inlineStr">
         <is>
-          <t>TL</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="953">
       <c r="A953" s="0" t="inlineStr">
         <is>
-          <t>YCK</t>
+          <t>YBR</t>
         </is>
       </c>
       <c r="B953" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY CİHANGİR SERBEST FON</t>
+          <t>İŞ PORTFÖY YİRMİBİRİNCİ SERBEST (DÖVİZ) FON</t>
         </is>
       </c>
       <c r="C953" s="0" t="inlineStr">
@@ -30828,39 +30828,39 @@
       </c>
       <c r="D953" s="0" t="inlineStr">
         <is>
-          <t>Diğer Serbest</t>
+          <t>Döviz</t>
         </is>
       </c>
       <c r="E953" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ</t>
+          <t>İŞ</t>
         </is>
       </c>
       <c r="F953" s="0" t="inlineStr">
         <is>
-          <t>TL</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="954">
       <c r="A954" s="0" t="inlineStr">
         <is>
-          <t>YCP</t>
+          <t>YBS</t>
         </is>
       </c>
       <c r="B954" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY BANKACILIK SEKTÖRÜ HİSSE SENEDİ SERBEST FON (HİSSE SENEDİ YOĞUN FON)</t>
+          <t>YAPI KREDİ PORTFÖY ÖZEL SEKTÖR BORÇLANMA ARAÇLARI FONU</t>
         </is>
       </c>
       <c r="C954" s="0" t="inlineStr">
         <is>
-          <t>Serbest Şemsiye Fonu</t>
+          <t>Borçlanma Araçları Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D954" s="0" t="inlineStr">
         <is>
-          <t>BIST Endeks</t>
+          <t>Özel Sektör Borçlanma Araçları</t>
         </is>
       </c>
       <c r="E954" s="0" t="inlineStr">
@@ -30877,27 +30877,27 @@
     <row outlineLevel="0" r="955">
       <c r="A955" s="0" t="inlineStr">
         <is>
-          <t>YCY</t>
+          <t>YCK</t>
         </is>
       </c>
       <c r="B955" s="0" t="inlineStr">
         <is>
-          <t>İSTANBUL PORTFÖY KATILIM FON SEPETİ FONU</t>
+          <t>YAPI KREDİ PORTFÖY CİHANGİR SERBEST FON</t>
         </is>
       </c>
       <c r="C955" s="0" t="inlineStr">
         <is>
-          <t>Fon Sepeti Şemsiye Fonu</t>
+          <t>Serbest Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D955" s="0" t="inlineStr">
         <is>
-          <t>Fon Sepeti</t>
+          <t>Diğer Serbest</t>
         </is>
       </c>
       <c r="E955" s="0" t="inlineStr">
         <is>
-          <t>İSTANBUL</t>
+          <t>YAPI KREDİ</t>
         </is>
       </c>
       <c r="F955" s="0" t="inlineStr">
@@ -30909,22 +30909,22 @@
     <row outlineLevel="0" r="956">
       <c r="A956" s="0" t="inlineStr">
         <is>
-          <t>YDI</t>
+          <t>YCP</t>
         </is>
       </c>
       <c r="B956" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY MODEL PORTFÖY HİSSE SENEDİ FONU (HİSSE SENEDİ YOĞUN FON)</t>
+          <t>YAPI KREDİ PORTFÖY BANKACILIK SEKTÖRÜ HİSSE SENEDİ SERBEST FON (HİSSE SENEDİ YOĞUN FON)</t>
         </is>
       </c>
       <c r="C956" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi Şemsiye Fonu</t>
+          <t>Serbest Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D956" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi</t>
+          <t>BIST Endeks</t>
         </is>
       </c>
       <c r="E956" s="0" t="inlineStr">
@@ -30941,27 +30941,27 @@
     <row outlineLevel="0" r="957">
       <c r="A957" s="0" t="inlineStr">
         <is>
-          <t>YDP</t>
+          <t>YCY</t>
         </is>
       </c>
       <c r="B957" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY BİRİNCİ DEĞİŞKEN FON</t>
+          <t>İSTANBUL PORTFÖY KATILIM FON SEPETİ FONU</t>
         </is>
       </c>
       <c r="C957" s="0" t="inlineStr">
         <is>
-          <t>Değişken Şemsiye Fonu</t>
+          <t>Fon Sepeti Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D957" s="0" t="inlineStr">
         <is>
-          <t>Değişken</t>
+          <t>Fon Sepeti</t>
         </is>
       </c>
       <c r="E957" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ</t>
+          <t>İSTANBUL</t>
         </is>
       </c>
       <c r="F957" s="0" t="inlineStr">
@@ -30973,12 +30973,12 @@
     <row outlineLevel="0" r="958">
       <c r="A958" s="0" t="inlineStr">
         <is>
-          <t>YEF</t>
+          <t>YDI</t>
         </is>
       </c>
       <c r="B958" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY BIST 30 ENDEKSİ HİSSE SENEDİ FONU (HİSSE SENEDİ YOĞUN FON)</t>
+          <t>YAPI KREDİ PORTFÖY MODEL PORTFÖY HİSSE SENEDİ FONU (HİSSE SENEDİ YOĞUN FON)</t>
         </is>
       </c>
       <c r="C958" s="0" t="inlineStr">
@@ -30988,7 +30988,7 @@
       </c>
       <c r="D958" s="0" t="inlineStr">
         <is>
-          <t>BIST Endeks</t>
+          <t>Hisse Senedi</t>
         </is>
       </c>
       <c r="E958" s="0" t="inlineStr">
@@ -31005,22 +31005,22 @@
     <row outlineLevel="0" r="959">
       <c r="A959" s="0" t="inlineStr">
         <is>
-          <t>YFV</t>
+          <t>YDP</t>
         </is>
       </c>
       <c r="B959" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY KİRA SERTİFİKALARI KATILIM FONU</t>
+          <t>YAPI KREDİ PORTFÖY BİRİNCİ DEĞİŞKEN FON</t>
         </is>
       </c>
       <c r="C959" s="0" t="inlineStr">
         <is>
-          <t>Katılım Şemsiye Fonu</t>
+          <t>Değişken Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D959" s="0" t="inlineStr">
         <is>
-          <t>Kira Sertifikası</t>
+          <t>Değişken</t>
         </is>
       </c>
       <c r="E959" s="0" t="inlineStr">
@@ -31037,22 +31037,22 @@
     <row outlineLevel="0" r="960">
       <c r="A960" s="0" t="inlineStr">
         <is>
-          <t>YGM</t>
+          <t>YEF</t>
         </is>
       </c>
       <c r="B960" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY EMTİA SERBEST FON</t>
+          <t>YAPI KREDİ PORTFÖY BIST 30 ENDEKSİ HİSSE SENEDİ FONU (HİSSE SENEDİ YOĞUN FON)</t>
         </is>
       </c>
       <c r="C960" s="0" t="inlineStr">
         <is>
-          <t>Serbest Şemsiye Fonu</t>
+          <t>Hisse Senedi Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D960" s="0" t="inlineStr">
         <is>
-          <t>Emtia</t>
+          <t>BIST Endeks</t>
         </is>
       </c>
       <c r="E960" s="0" t="inlineStr">
@@ -31069,22 +31069,22 @@
     <row outlineLevel="0" r="961">
       <c r="A961" s="0" t="inlineStr">
         <is>
-          <t>YHB</t>
+          <t>YFV</t>
         </is>
       </c>
       <c r="B961" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY BIST 100 DIŞI ŞİRKETLER HİSSE SENEDİ FONU (HİSSE SENEDİ YOĞUN FON)</t>
+          <t>YAPI KREDİ PORTFÖY KİRA SERTİFİKALARI KATILIM FONU</t>
         </is>
       </c>
       <c r="C961" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi Şemsiye Fonu</t>
+          <t>Katılım Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D961" s="0" t="inlineStr">
         <is>
-          <t>BIST Endeks</t>
+          <t>Kira Sertifikası</t>
         </is>
       </c>
       <c r="E961" s="0" t="inlineStr">
@@ -31101,12 +31101,12 @@
     <row outlineLevel="0" r="962">
       <c r="A962" s="0" t="inlineStr">
         <is>
-          <t>YHI</t>
+          <t>YGM</t>
         </is>
       </c>
       <c r="B962" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY İNŞAAT SEKTÖRÜ HİSSE SENEDİ SERBEST (TL) FON (HİSSE SENEDİ YOĞUN FON)</t>
+          <t>YAPI KREDİ PORTFÖY EMTİA SERBEST FON</t>
         </is>
       </c>
       <c r="C962" s="0" t="inlineStr">
@@ -31116,7 +31116,7 @@
       </c>
       <c r="D962" s="0" t="inlineStr">
         <is>
-          <t>Tematik</t>
+          <t>Emtia</t>
         </is>
       </c>
       <c r="E962" s="0" t="inlineStr">
@@ -31133,12 +31133,12 @@
     <row outlineLevel="0" r="963">
       <c r="A963" s="0" t="inlineStr">
         <is>
-          <t>YHK</t>
+          <t>YHB</t>
         </is>
       </c>
       <c r="B963" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY KATILIM HİSSE SENEDİ FONU (HİSSE SENEDİ YOĞUN FON)</t>
+          <t>YAPI KREDİ PORTFÖY BIST 100 DIŞI ŞİRKETLER HİSSE SENEDİ FONU (HİSSE SENEDİ YOĞUN FON)</t>
         </is>
       </c>
       <c r="C963" s="0" t="inlineStr">
@@ -31148,7 +31148,7 @@
       </c>
       <c r="D963" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi</t>
+          <t>BIST Endeks</t>
         </is>
       </c>
       <c r="E963" s="0" t="inlineStr">
@@ -31165,12 +31165,12 @@
     <row outlineLevel="0" r="964">
       <c r="A964" s="0" t="inlineStr">
         <is>
-          <t>YHP</t>
+          <t>YHI</t>
         </is>
       </c>
       <c r="B964" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY KADIKÖY SERBEST FON</t>
+          <t>YAPI KREDİ PORTFÖY İNŞAAT SEKTÖRÜ HİSSE SENEDİ SERBEST (TL) FON (HİSSE SENEDİ YOĞUN FON)</t>
         </is>
       </c>
       <c r="C964" s="0" t="inlineStr">
@@ -31180,7 +31180,7 @@
       </c>
       <c r="D964" s="0" t="inlineStr">
         <is>
-          <t>Diğer Serbest</t>
+          <t>Tematik</t>
         </is>
       </c>
       <c r="E964" s="0" t="inlineStr">
@@ -31197,12 +31197,12 @@
     <row outlineLevel="0" r="965">
       <c r="A965" s="0" t="inlineStr">
         <is>
-          <t>YHS</t>
+          <t>YHK</t>
         </is>
       </c>
       <c r="B965" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY BİRİNCİ HİSSE SENEDİ FONU (HİSSE SENEDİ YOĞUN FON)</t>
+          <t>YAPI KREDİ PORTFÖY KATILIM HİSSE SENEDİ FONU (HİSSE SENEDİ YOĞUN FON)</t>
         </is>
       </c>
       <c r="C965" s="0" t="inlineStr">
@@ -31229,22 +31229,22 @@
     <row outlineLevel="0" r="966">
       <c r="A966" s="0" t="inlineStr">
         <is>
-          <t>YHT</t>
+          <t>YHP</t>
         </is>
       </c>
       <c r="B966" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY KISA VADELİ BORÇLANMA ARAÇLARI (TL) FONU</t>
+          <t>YAPI KREDİ PORTFÖY KADIKÖY SERBEST FON</t>
         </is>
       </c>
       <c r="C966" s="0" t="inlineStr">
         <is>
-          <t>Borçlanma Araçları Şemsiye Fonu</t>
+          <t>Serbest Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D966" s="0" t="inlineStr">
         <is>
-          <t>Borçlanma Araçları</t>
+          <t>Diğer Serbest</t>
         </is>
       </c>
       <c r="E966" s="0" t="inlineStr">
@@ -31261,12 +31261,12 @@
     <row outlineLevel="0" r="967">
       <c r="A967" s="0" t="inlineStr">
         <is>
-          <t>YHZ</t>
+          <t>YHS</t>
         </is>
       </c>
       <c r="B967" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY BIST TEKNOLOJİ AĞIRLIK SINIRLAMALI ENDEKSİ HİSSE SENEDİ FONU ( HİSSE SENEDİ YOĞUN FON)</t>
+          <t>YAPI KREDİ PORTFÖY BİRİNCİ HİSSE SENEDİ FONU (HİSSE SENEDİ YOĞUN FON)</t>
         </is>
       </c>
       <c r="C967" s="0" t="inlineStr">
@@ -31276,7 +31276,7 @@
       </c>
       <c r="D967" s="0" t="inlineStr">
         <is>
-          <t>BIST Endeks</t>
+          <t>Hisse Senedi</t>
         </is>
       </c>
       <c r="E967" s="0" t="inlineStr">
@@ -31293,22 +31293,22 @@
     <row outlineLevel="0" r="968">
       <c r="A968" s="0" t="inlineStr">
         <is>
-          <t>YIK</t>
+          <t>YHT</t>
         </is>
       </c>
       <c r="B968" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY İKİNCİ PARA PİYASASI SERBEST (TL) FON</t>
+          <t>YAPI KREDİ PORTFÖY KISA VADELİ BORÇLANMA ARAÇLARI (TL) FONU</t>
         </is>
       </c>
       <c r="C968" s="0" t="inlineStr">
         <is>
-          <t>Serbest Şemsiye Fonu</t>
+          <t>Borçlanma Araçları Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D968" s="0" t="inlineStr">
         <is>
-          <t>Para Piyasası</t>
+          <t>Borçlanma Araçları</t>
         </is>
       </c>
       <c r="E968" s="0" t="inlineStr">
@@ -31325,27 +31325,27 @@
     <row outlineLevel="0" r="969">
       <c r="A969" s="0" t="inlineStr">
         <is>
-          <t>YIT</t>
+          <t>YHZ</t>
         </is>
       </c>
       <c r="B969" s="0" t="inlineStr">
         <is>
-          <t>GARANTİ PORTFÖY YARI İLETKEN TEKNOLOJİLERİ DEĞİŞKEN FON</t>
+          <t>YAPI KREDİ PORTFÖY BIST TEKNOLOJİ AĞIRLIK SINIRLAMALI ENDEKSİ HİSSE SENEDİ FONU ( HİSSE SENEDİ YOĞUN FON)</t>
         </is>
       </c>
       <c r="C969" s="0" t="inlineStr">
         <is>
-          <t>Değişken Şemsiye Fonu</t>
+          <t>Hisse Senedi Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D969" s="0" t="inlineStr">
         <is>
-          <t>Teknoloji Temalı</t>
+          <t>BIST Endeks</t>
         </is>
       </c>
       <c r="E969" s="0" t="inlineStr">
         <is>
-          <t>GARANTİ</t>
+          <t>YAPI KREDİ</t>
         </is>
       </c>
       <c r="F969" s="0" t="inlineStr">
@@ -31357,22 +31357,22 @@
     <row outlineLevel="0" r="970">
       <c r="A970" s="0" t="inlineStr">
         <is>
-          <t>YJH</t>
+          <t>YIK</t>
         </is>
       </c>
       <c r="B970" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY TEMİZ ENERJİ DEĞİŞKEN FONU</t>
+          <t>YAPI KREDİ PORTFÖY İKİNCİ PARA PİYASASI SERBEST (TL) FON</t>
         </is>
       </c>
       <c r="C970" s="0" t="inlineStr">
         <is>
-          <t>Değişken Şemsiye Fonu</t>
+          <t>Serbest Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D970" s="0" t="inlineStr">
         <is>
-          <t>Tematik</t>
+          <t>Para Piyasası</t>
         </is>
       </c>
       <c r="E970" s="0" t="inlineStr">
@@ -31389,17 +31389,17 @@
     <row outlineLevel="0" r="971">
       <c r="A971" s="0" t="inlineStr">
         <is>
-          <t>YJK</t>
+          <t>YIT</t>
         </is>
       </c>
       <c r="B971" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY ROBOTİK VE YARI İLETKEN TEKNOLOJİLERİ FON SEPETİ FONU</t>
+          <t>GARANTİ PORTFÖY YARI İLETKEN TEKNOLOJİLERİ DEĞİŞKEN FON</t>
         </is>
       </c>
       <c r="C971" s="0" t="inlineStr">
         <is>
-          <t>Fon Sepeti Şemsiye Fonu</t>
+          <t>Değişken Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D971" s="0" t="inlineStr">
@@ -31409,7 +31409,7 @@
       </c>
       <c r="E971" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ</t>
+          <t>GARANTİ</t>
         </is>
       </c>
       <c r="F971" s="0" t="inlineStr">
@@ -31421,22 +31421,22 @@
     <row outlineLevel="0" r="972">
       <c r="A972" s="0" t="inlineStr">
         <is>
-          <t>YJY</t>
+          <t>YJH</t>
         </is>
       </c>
       <c r="B972" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY YENİKÖY SERBEST (DÖVİZ) FON</t>
+          <t>YAPI KREDİ PORTFÖY TEMİZ ENERJİ DEĞİŞKEN FONU</t>
         </is>
       </c>
       <c r="C972" s="0" t="inlineStr">
         <is>
-          <t>Serbest Şemsiye Fonu</t>
+          <t>Değişken Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D972" s="0" t="inlineStr">
         <is>
-          <t>Döviz</t>
+          <t>Tematik</t>
         </is>
       </c>
       <c r="E972" s="0" t="inlineStr">
@@ -31446,29 +31446,29 @@
       </c>
       <c r="F972" s="0" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>TL</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="973">
       <c r="A973" s="0" t="inlineStr">
         <is>
-          <t>YKS</t>
+          <t>YJK</t>
         </is>
       </c>
       <c r="B973" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY İSTANBUL SERBEST FON</t>
+          <t>YAPI KREDİ PORTFÖY ROBOTİK VE YARI İLETKEN TEKNOLOJİLERİ FON SEPETİ FONU</t>
         </is>
       </c>
       <c r="C973" s="0" t="inlineStr">
         <is>
-          <t>Serbest Şemsiye Fonu</t>
+          <t>Fon Sepeti Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D973" s="0" t="inlineStr">
         <is>
-          <t>Diğer Serbest</t>
+          <t>Teknoloji Temalı</t>
         </is>
       </c>
       <c r="E973" s="0" t="inlineStr">
@@ -31485,22 +31485,22 @@
     <row outlineLevel="0" r="974">
       <c r="A974" s="0" t="inlineStr">
         <is>
-          <t>YKT</t>
+          <t>YJY</t>
         </is>
       </c>
       <c r="B974" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY ALTIN FONU</t>
+          <t>YAPI KREDİ PORTFÖY YENİKÖY SERBEST (DÖVİZ) FON</t>
         </is>
       </c>
       <c r="C974" s="0" t="inlineStr">
         <is>
-          <t>Kıymetli Madenler Şemsiye Fonu</t>
+          <t>Serbest Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D974" s="0" t="inlineStr">
         <is>
-          <t>Altın</t>
+          <t>Döviz</t>
         </is>
       </c>
       <c r="E974" s="0" t="inlineStr">
@@ -31510,34 +31510,34 @@
       </c>
       <c r="F974" s="0" t="inlineStr">
         <is>
-          <t>TL</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="975">
       <c r="A975" s="0" t="inlineStr">
         <is>
-          <t>YLC</t>
+          <t>YKS</t>
         </is>
       </c>
       <c r="B975" s="0" t="inlineStr">
         <is>
-          <t>ATA PORTFÖY TARIM VE GIDA DEĞİŞKEN FON</t>
+          <t>YAPI KREDİ PORTFÖY İSTANBUL SERBEST FON</t>
         </is>
       </c>
       <c r="C975" s="0" t="inlineStr">
         <is>
-          <t>Değişken Şemsiye Fonu</t>
+          <t>Serbest Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D975" s="0" t="inlineStr">
         <is>
-          <t>Tematik</t>
+          <t>Diğer Serbest</t>
         </is>
       </c>
       <c r="E975" s="0" t="inlineStr">
         <is>
-          <t>ATA</t>
+          <t>YAPI KREDİ</t>
         </is>
       </c>
       <c r="F975" s="0" t="inlineStr">
@@ -31549,22 +31549,22 @@
     <row outlineLevel="0" r="976">
       <c r="A976" s="0" t="inlineStr">
         <is>
-          <t>YLE</t>
+          <t>YKT</t>
         </is>
       </c>
       <c r="B976" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY BIST SÜRDÜRÜLEBİLİRLİK ENDEKSİ HİSSE SENEDİ FONU (HİSSE SENEDİ YOĞUN FON)</t>
+          <t>YAPI KREDİ PORTFÖY ALTIN FONU</t>
         </is>
       </c>
       <c r="C976" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi Şemsiye Fonu</t>
+          <t>Kıymetli Madenler Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D976" s="0" t="inlineStr">
         <is>
-          <t>BIST Endeks</t>
+          <t>Altın</t>
         </is>
       </c>
       <c r="E976" s="0" t="inlineStr">
@@ -31581,12 +31581,12 @@
     <row outlineLevel="0" r="977">
       <c r="A977" s="0" t="inlineStr">
         <is>
-          <t>YLO</t>
+          <t>YLC</t>
         </is>
       </c>
       <c r="B977" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY ELEKTRİKLİ ARAÇLAR DEĞİŞKEN FON</t>
+          <t>ATA PORTFÖY TARIM VE GIDA DEĞİŞKEN FON</t>
         </is>
       </c>
       <c r="C977" s="0" t="inlineStr">
@@ -31601,7 +31601,7 @@
       </c>
       <c r="E977" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ</t>
+          <t>ATA</t>
         </is>
       </c>
       <c r="F977" s="0" t="inlineStr">
@@ -31613,12 +31613,12 @@
     <row outlineLevel="0" r="978">
       <c r="A978" s="0" t="inlineStr">
         <is>
-          <t>YLY</t>
+          <t>YLE</t>
         </is>
       </c>
       <c r="B978" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY KAR PAYI ÖDEYEN HİSSE SENEDİ (TL) FON (HİSSE SENEDİ YOĞUN FON)</t>
+          <t>YAPI KREDİ PORTFÖY BIST SÜRDÜRÜLEBİLİRLİK ENDEKSİ HİSSE SENEDİ FONU (HİSSE SENEDİ YOĞUN FON)</t>
         </is>
       </c>
       <c r="C978" s="0" t="inlineStr">
@@ -31628,7 +31628,7 @@
       </c>
       <c r="D978" s="0" t="inlineStr">
         <is>
-          <t>Kar Payı Ödeyen</t>
+          <t>BIST Endeks</t>
         </is>
       </c>
       <c r="E978" s="0" t="inlineStr">
@@ -31645,22 +31645,22 @@
     <row outlineLevel="0" r="979">
       <c r="A979" s="0" t="inlineStr">
         <is>
-          <t>YMD</t>
+          <t>YLO</t>
         </is>
       </c>
       <c r="B979" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY MASLAK SERBEST (DÖVİZ- ABD DOLARI) FON</t>
+          <t>YAPI KREDİ PORTFÖY ELEKTRİKLİ ARAÇLAR DEĞİŞKEN FON</t>
         </is>
       </c>
       <c r="C979" s="0" t="inlineStr">
         <is>
-          <t>Serbest Şemsiye Fonu</t>
+          <t>Değişken Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D979" s="0" t="inlineStr">
         <is>
-          <t>Döviz</t>
+          <t>Tematik</t>
         </is>
       </c>
       <c r="E979" s="0" t="inlineStr">
@@ -31670,29 +31670,29 @@
       </c>
       <c r="F979" s="0" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>TL</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="980">
       <c r="A980" s="0" t="inlineStr">
         <is>
-          <t>YMH</t>
+          <t>YLY</t>
         </is>
       </c>
       <c r="B980" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY MUTLAK GETİRİ HEDEFLİ HİSSE SENEDİ SERBEST FON (HİSSE SENEDİ YOĞUN FON)</t>
+          <t>YAPI KREDİ PORTFÖY KAR PAYI ÖDEYEN HİSSE SENEDİ (TL) FON (HİSSE SENEDİ YOĞUN FON)</t>
         </is>
       </c>
       <c r="C980" s="0" t="inlineStr">
         <is>
-          <t>Serbest Şemsiye Fonu</t>
+          <t>Hisse Senedi Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D980" s="0" t="inlineStr">
         <is>
-          <t>İstatiksel Arbitraj</t>
+          <t>Kar Payı Ödeyen</t>
         </is>
       </c>
       <c r="E980" s="0" t="inlineStr">
@@ -31709,12 +31709,12 @@
     <row outlineLevel="0" r="981">
       <c r="A981" s="0" t="inlineStr">
         <is>
-          <t>YNK</t>
+          <t>YMD</t>
         </is>
       </c>
       <c r="B981" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY NİŞANTAŞI KAR PAYI ÖDEYEN SERBEST (DÖVİZ) FON</t>
+          <t>YAPI KREDİ PORTFÖY MASLAK SERBEST (DÖVİZ- ABD DOLARI) FON</t>
         </is>
       </c>
       <c r="C981" s="0" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="D981" s="0" t="inlineStr">
         <is>
-          <t>Kar Payı Ödeyen</t>
+          <t>Döviz</t>
         </is>
       </c>
       <c r="E981" s="0" t="inlineStr">
@@ -31741,22 +31741,22 @@
     <row outlineLevel="0" r="982">
       <c r="A982" s="0" t="inlineStr">
         <is>
-          <t>YOT</t>
+          <t>YMH</t>
         </is>
       </c>
       <c r="B982" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY BORÇLANMA ARAÇLARI FONU</t>
+          <t>YAPI KREDİ PORTFÖY MUTLAK GETİRİ HEDEFLİ HİSSE SENEDİ SERBEST FON (HİSSE SENEDİ YOĞUN FON)</t>
         </is>
       </c>
       <c r="C982" s="0" t="inlineStr">
         <is>
-          <t>Borçlanma Araçları Şemsiye Fonu</t>
+          <t>Serbest Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D982" s="0" t="inlineStr">
         <is>
-          <t>Borçlanma Araçları</t>
+          <t>İstatiksel Arbitraj</t>
         </is>
       </c>
       <c r="E982" s="0" t="inlineStr">
@@ -31773,12 +31773,12 @@
     <row outlineLevel="0" r="983">
       <c r="A983" s="0" t="inlineStr">
         <is>
-          <t>YOZ</t>
+          <t>YNK</t>
         </is>
       </c>
       <c r="B983" s="0" t="inlineStr">
         <is>
-          <t>DENİZ PORTFÖY YAKAMOZ SERBEST (DÖVİZ) FON</t>
+          <t>YAPI KREDİ PORTFÖY NİŞANTAŞI KAR PAYI ÖDEYEN SERBEST (DÖVİZ) FON</t>
         </is>
       </c>
       <c r="C983" s="0" t="inlineStr">
@@ -31788,12 +31788,12 @@
       </c>
       <c r="D983" s="0" t="inlineStr">
         <is>
-          <t>Döviz</t>
+          <t>Kar Payı Ödeyen</t>
         </is>
       </c>
       <c r="E983" s="0" t="inlineStr">
         <is>
-          <t>DENİZ</t>
+          <t>YAPI KREDİ</t>
         </is>
       </c>
       <c r="F983" s="0" t="inlineStr">
@@ -31805,22 +31805,22 @@
     <row outlineLevel="0" r="984">
       <c r="A984" s="0" t="inlineStr">
         <is>
-          <t>YP4</t>
+          <t>YOT</t>
         </is>
       </c>
       <c r="B984" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY FERİKÖY SERBEST (DÖVİZ) FON</t>
+          <t>YAPI KREDİ PORTFÖY BORÇLANMA ARAÇLARI FONU</t>
         </is>
       </c>
       <c r="C984" s="0" t="inlineStr">
         <is>
-          <t>Serbest Şemsiye Fonu</t>
+          <t>Borçlanma Araçları Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D984" s="0" t="inlineStr">
         <is>
-          <t>Döviz</t>
+          <t>Borçlanma Araçları</t>
         </is>
       </c>
       <c r="E984" s="0" t="inlineStr">
@@ -31830,51 +31830,51 @@
       </c>
       <c r="F984" s="0" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>TL</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="985">
       <c r="A985" s="0" t="inlineStr">
         <is>
-          <t>YPC</t>
+          <t>YOZ</t>
         </is>
       </c>
       <c r="B985" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY SÜRDÜRÜLEBİLİRLİK DEĞİŞKEN FON</t>
+          <t>DENİZ PORTFÖY YAKAMOZ SERBEST (DÖVİZ) FON</t>
         </is>
       </c>
       <c r="C985" s="0" t="inlineStr">
         <is>
-          <t>Değişken Şemsiye Fonu</t>
+          <t>Serbest Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D985" s="0" t="inlineStr">
         <is>
-          <t>Tematik</t>
+          <t>Döviz</t>
         </is>
       </c>
       <c r="E985" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ</t>
+          <t>DENİZ</t>
         </is>
       </c>
       <c r="F985" s="0" t="inlineStr">
         <is>
-          <t>TL</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="986">
       <c r="A986" s="0" t="inlineStr">
         <is>
-          <t>YPF</t>
+          <t>YP4</t>
         </is>
       </c>
       <c r="B986" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY ALFA SERBEST FON</t>
+          <t>YAPI KREDİ PORTFÖY FERİKÖY SERBEST (DÖVİZ) FON</t>
         </is>
       </c>
       <c r="C986" s="0" t="inlineStr">
@@ -31884,7 +31884,7 @@
       </c>
       <c r="D986" s="0" t="inlineStr">
         <is>
-          <t>Diğer Serbest</t>
+          <t>Döviz</t>
         </is>
       </c>
       <c r="E986" s="0" t="inlineStr">
@@ -31894,29 +31894,29 @@
       </c>
       <c r="F986" s="0" t="inlineStr">
         <is>
-          <t>TL</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="987">
       <c r="A987" s="0" t="inlineStr">
         <is>
-          <t>YPK</t>
+          <t>YPC</t>
         </is>
       </c>
       <c r="B987" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY GALATA SERBEST FON</t>
+          <t>YAPI KREDİ PORTFÖY SÜRDÜRÜLEBİLİRLİK DEĞİŞKEN FON</t>
         </is>
       </c>
       <c r="C987" s="0" t="inlineStr">
         <is>
-          <t>Serbest Şemsiye Fonu</t>
+          <t>Değişken Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D987" s="0" t="inlineStr">
         <is>
-          <t>Diğer Serbest</t>
+          <t>Tematik</t>
         </is>
       </c>
       <c r="E987" s="0" t="inlineStr">
@@ -31933,12 +31933,12 @@
     <row outlineLevel="0" r="988">
       <c r="A988" s="0" t="inlineStr">
         <is>
-          <t>YPL</t>
+          <t>YPF</t>
         </is>
       </c>
       <c r="B988" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY BALAT SERBEST (DÖVİZ) FON</t>
+          <t>YAPI KREDİ PORTFÖY ALFA SERBEST FON</t>
         </is>
       </c>
       <c r="C988" s="0" t="inlineStr">
@@ -31948,7 +31948,7 @@
       </c>
       <c r="D988" s="0" t="inlineStr">
         <is>
-          <t>Döviz</t>
+          <t>Diğer Serbest</t>
         </is>
       </c>
       <c r="E988" s="0" t="inlineStr">
@@ -31958,34 +31958,34 @@
       </c>
       <c r="F988" s="0" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>TL</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="989">
       <c r="A989" s="0" t="inlineStr">
         <is>
-          <t>YPR</t>
+          <t>YPK</t>
         </is>
       </c>
       <c r="B989" s="0" t="inlineStr">
         <is>
-          <t>AZİMUT PORTFÖY YILDIZ PAZAR ŞİRKETLERİ HİSSE SENEDİ FONU (HİSSE SENEDİ YOĞUN FON)</t>
+          <t>YAPI KREDİ PORTFÖY GALATA SERBEST FON</t>
         </is>
       </c>
       <c r="C989" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi Şemsiye Fonu</t>
+          <t>Serbest Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D989" s="0" t="inlineStr">
         <is>
-          <t>BIST Endeks</t>
+          <t>Diğer Serbest</t>
         </is>
       </c>
       <c r="E989" s="0" t="inlineStr">
         <is>
-          <t>AZİMUT</t>
+          <t>YAPI KREDİ</t>
         </is>
       </c>
       <c r="F989" s="0" t="inlineStr">
@@ -31997,22 +31997,22 @@
     <row outlineLevel="0" r="990">
       <c r="A990" s="0" t="inlineStr">
         <is>
-          <t>YPV</t>
+          <t>YPL</t>
         </is>
       </c>
       <c r="B990" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY ÜÇÜNCÜ FON SEPETİ FONU</t>
+          <t>YAPI KREDİ PORTFÖY BALAT SERBEST (DÖVİZ) FON</t>
         </is>
       </c>
       <c r="C990" s="0" t="inlineStr">
         <is>
-          <t>Fon Sepeti Şemsiye Fonu</t>
+          <t>Serbest Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D990" s="0" t="inlineStr">
         <is>
-          <t>Fon Sepeti</t>
+          <t>Döviz</t>
         </is>
       </c>
       <c r="E990" s="0" t="inlineStr">
@@ -32022,61 +32022,61 @@
       </c>
       <c r="F990" s="0" t="inlineStr">
         <is>
-          <t>TL</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="991">
       <c r="A991" s="0" t="inlineStr">
         <is>
-          <t>YSA</t>
+          <t>YPR</t>
         </is>
       </c>
       <c r="B991" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY SUADİYE SERBEST (DÖVİZ) FON</t>
+          <t>AZİMUT PORTFÖY YILDIZ PAZAR ŞİRKETLERİ HİSSE SENEDİ FONU (HİSSE SENEDİ YOĞUN FON)</t>
         </is>
       </c>
       <c r="C991" s="0" t="inlineStr">
         <is>
-          <t>Serbest Şemsiye Fonu</t>
+          <t>Hisse Senedi Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D991" s="0" t="inlineStr">
         <is>
-          <t>Döviz</t>
+          <t>BIST Endeks</t>
         </is>
       </c>
       <c r="E991" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ</t>
+          <t>AZİMUT</t>
         </is>
       </c>
       <c r="F991" s="0" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>TL</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="992">
       <c r="A992" s="0" t="inlineStr">
         <is>
-          <t>YSH</t>
+          <t>YPV</t>
         </is>
       </c>
       <c r="B992" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY BÜYÜK ÖLÇEKLİ ŞİRKETLER DEĞİŞKEN FON</t>
+          <t>YAPI KREDİ PORTFÖY ÜÇÜNCÜ FON SEPETİ FONU</t>
         </is>
       </c>
       <c r="C992" s="0" t="inlineStr">
         <is>
-          <t>Değişken Şemsiye Fonu</t>
+          <t>Fon Sepeti Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D992" s="0" t="inlineStr">
         <is>
-          <t>Tematik</t>
+          <t>Fon Sepeti</t>
         </is>
       </c>
       <c r="E992" s="0" t="inlineStr">
@@ -32093,12 +32093,12 @@
     <row outlineLevel="0" r="993">
       <c r="A993" s="0" t="inlineStr">
         <is>
-          <t>YSL</t>
+          <t>YSA</t>
         </is>
       </c>
       <c r="B993" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY KAR PAYI ÖDEYEN KİRA SERTİFİKALARI KATILIM SERBEST (DÖVİZ) FON</t>
+          <t>YAPI KREDİ PORTFÖY SUADİYE SERBEST (DÖVİZ) FON</t>
         </is>
       </c>
       <c r="C993" s="0" t="inlineStr">
@@ -32108,7 +32108,7 @@
       </c>
       <c r="D993" s="0" t="inlineStr">
         <is>
-          <t>Kar Payı Ödeyen</t>
+          <t>Döviz</t>
         </is>
       </c>
       <c r="E993" s="0" t="inlineStr">
@@ -32125,17 +32125,17 @@
     <row outlineLevel="0" r="994">
       <c r="A994" s="0" t="inlineStr">
         <is>
-          <t>YSO</t>
+          <t>YSH</t>
         </is>
       </c>
       <c r="B994" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY SAĞLIK SEKTÖRÜ SERBEST FON</t>
+          <t>YAPI KREDİ PORTFÖY BÜYÜK ÖLÇEKLİ ŞİRKETLER DEĞİŞKEN FON</t>
         </is>
       </c>
       <c r="C994" s="0" t="inlineStr">
         <is>
-          <t>Serbest Şemsiye Fonu</t>
+          <t>Değişken Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D994" s="0" t="inlineStr">
@@ -32157,22 +32157,22 @@
     <row outlineLevel="0" r="995">
       <c r="A995" s="0" t="inlineStr">
         <is>
-          <t>YSU</t>
+          <t>YSL</t>
         </is>
       </c>
       <c r="B995" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY ÜÇÜNCÜ DEĞİŞKEN FON</t>
+          <t>YAPI KREDİ PORTFÖY KAR PAYI ÖDEYEN KİRA SERTİFİKALARI KATILIM SERBEST (DÖVİZ) FON</t>
         </is>
       </c>
       <c r="C995" s="0" t="inlineStr">
         <is>
-          <t>Değişken Şemsiye Fonu</t>
+          <t>Serbest Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D995" s="0" t="inlineStr">
         <is>
-          <t>Değişken</t>
+          <t>Kar Payı Ödeyen</t>
         </is>
       </c>
       <c r="E995" s="0" t="inlineStr">
@@ -32182,24 +32182,24 @@
       </c>
       <c r="F995" s="0" t="inlineStr">
         <is>
-          <t>TL</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="996">
       <c r="A996" s="0" t="inlineStr">
         <is>
-          <t>YTD</t>
+          <t>YSO</t>
         </is>
       </c>
       <c r="B996" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY YABANCI FON SEPETİ FONU</t>
+          <t>YAPI KREDİ PORTFÖY SAĞLIK SEKTÖRÜ SERBEST FON</t>
         </is>
       </c>
       <c r="C996" s="0" t="inlineStr">
         <is>
-          <t>Fon Sepeti Şemsiye Fonu</t>
+          <t>Serbest Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D996" s="0" t="inlineStr">
@@ -32221,12 +32221,12 @@
     <row outlineLevel="0" r="997">
       <c r="A997" s="0" t="inlineStr">
         <is>
-          <t>YTV</t>
+          <t>YSU</t>
         </is>
       </c>
       <c r="B997" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY TARIM DEĞİŞKEN FON</t>
+          <t>YAPI KREDİ PORTFÖY ÜÇÜNCÜ DEĞİŞKEN FON</t>
         </is>
       </c>
       <c r="C997" s="0" t="inlineStr">
@@ -32236,7 +32236,7 @@
       </c>
       <c r="D997" s="0" t="inlineStr">
         <is>
-          <t>Tematik</t>
+          <t>Değişken</t>
         </is>
       </c>
       <c r="E997" s="0" t="inlineStr">
@@ -32253,22 +32253,22 @@
     <row outlineLevel="0" r="998">
       <c r="A998" s="0" t="inlineStr">
         <is>
-          <t>YTY</t>
+          <t>YTD</t>
         </is>
       </c>
       <c r="B998" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY TARABYA SERBEST (DÖVİZ-AVRO) FON</t>
+          <t>YAPI KREDİ PORTFÖY YABANCI FON SEPETİ FONU</t>
         </is>
       </c>
       <c r="C998" s="0" t="inlineStr">
         <is>
-          <t>Serbest Şemsiye Fonu</t>
+          <t>Fon Sepeti Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D998" s="0" t="inlineStr">
         <is>
-          <t>Döviz</t>
+          <t>Tematik</t>
         </is>
       </c>
       <c r="E998" s="0" t="inlineStr">
@@ -32278,29 +32278,29 @@
       </c>
       <c r="F998" s="0" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>TL</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="999">
       <c r="A999" s="0" t="inlineStr">
         <is>
-          <t>YUB</t>
+          <t>YTV</t>
         </is>
       </c>
       <c r="B999" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY KARAKÖY HİSSE SENEDİ SERBEST FON (HİSSE SENEDİ YOĞUN FON)</t>
+          <t>YAPI KREDİ PORTFÖY TARIM DEĞİŞKEN FON</t>
         </is>
       </c>
       <c r="C999" s="0" t="inlineStr">
         <is>
-          <t>Serbest Şemsiye Fonu</t>
+          <t>Değişken Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D999" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi</t>
+          <t>Tematik</t>
         </is>
       </c>
       <c r="E999" s="0" t="inlineStr">
@@ -32317,12 +32317,12 @@
     <row outlineLevel="0" r="1000">
       <c r="A1000" s="0" t="inlineStr">
         <is>
-          <t>YUN</t>
+          <t>YTY</t>
         </is>
       </c>
       <c r="B1000" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY İSTİNYE SERBEST (DÖVİZ) FON</t>
+          <t>YAPI KREDİ PORTFÖY TARABYA SERBEST (DÖVİZ-AVRO) FON</t>
         </is>
       </c>
       <c r="C1000" s="0" t="inlineStr">
@@ -32342,29 +32342,29 @@
       </c>
       <c r="F1000" s="0" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="1001">
       <c r="A1001" s="0" t="inlineStr">
         <is>
-          <t>YVB</t>
+          <t>YUB</t>
         </is>
       </c>
       <c r="B1001" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY UZUN VADELİ BORÇLANMA ARAÇLARI FONU</t>
+          <t>YAPI KREDİ PORTFÖY KARAKÖY HİSSE SENEDİ SERBEST FON (HİSSE SENEDİ YOĞUN FON)</t>
         </is>
       </c>
       <c r="C1001" s="0" t="inlineStr">
         <is>
-          <t>Borçlanma Araçları Şemsiye Fonu</t>
+          <t>Serbest Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D1001" s="0" t="inlineStr">
         <is>
-          <t>Borçlanma Araçları</t>
+          <t>Hisse Senedi</t>
         </is>
       </c>
       <c r="E1001" s="0" t="inlineStr">
@@ -32381,12 +32381,12 @@
     <row outlineLevel="0" r="1002">
       <c r="A1002" s="0" t="inlineStr">
         <is>
-          <t>YVG</t>
+          <t>YUN</t>
         </is>
       </c>
       <c r="B1002" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY SARIYER SERBEST (DÖVİZ-AVRO) FON</t>
+          <t>YAPI KREDİ PORTFÖY İSTİNYE SERBEST (DÖVİZ) FON</t>
         </is>
       </c>
       <c r="C1002" s="0" t="inlineStr">
@@ -32406,29 +32406,29 @@
       </c>
       <c r="F1002" s="0" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="1003">
       <c r="A1003" s="0" t="inlineStr">
         <is>
-          <t>YZC</t>
+          <t>YVB</t>
         </is>
       </c>
       <c r="B1003" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY FİNTECH VE BLOCKCHAİN TEKNOLOJİLERİ DEĞİŞKEN FON</t>
+          <t>YAPI KREDİ PORTFÖY UZUN VADELİ BORÇLANMA ARAÇLARI FONU</t>
         </is>
       </c>
       <c r="C1003" s="0" t="inlineStr">
         <is>
-          <t>Değişken Şemsiye Fonu</t>
+          <t>Borçlanma Araçları Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D1003" s="0" t="inlineStr">
         <is>
-          <t>Teknoloji Temalı</t>
+          <t>Borçlanma Araçları</t>
         </is>
       </c>
       <c r="E1003" s="0" t="inlineStr">
@@ -32445,22 +32445,22 @@
     <row outlineLevel="0" r="1004">
       <c r="A1004" s="0" t="inlineStr">
         <is>
-          <t>YZG</t>
+          <t>YVG</t>
         </is>
       </c>
       <c r="B1004" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY GÜMÜŞ FON SEPETİ FONU</t>
+          <t>YAPI KREDİ PORTFÖY SARIYER SERBEST (DÖVİZ-AVRO) FON</t>
         </is>
       </c>
       <c r="C1004" s="0" t="inlineStr">
         <is>
-          <t>Fon Sepeti Şemsiye Fonu</t>
+          <t>Serbest Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D1004" s="0" t="inlineStr">
         <is>
-          <t>Gümüş</t>
+          <t>Döviz</t>
         </is>
       </c>
       <c r="E1004" s="0" t="inlineStr">
@@ -32470,34 +32470,34 @@
       </c>
       <c r="F1004" s="0" t="inlineStr">
         <is>
-          <t>TL</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="1005">
       <c r="A1005" s="0" t="inlineStr">
         <is>
-          <t>YZH</t>
+          <t>YZC</t>
         </is>
       </c>
       <c r="B1005" s="0" t="inlineStr">
         <is>
-          <t>TEB PORTFÖY BIST BANKA ENDEKSİ HİSSE SENEDİ FONU (HİSSE SENEDİ YOĞUN)</t>
+          <t>YAPI KREDİ PORTFÖY FİNTECH VE BLOCKCHAİN TEKNOLOJİLERİ DEĞİŞKEN FON</t>
         </is>
       </c>
       <c r="C1005" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi Şemsiye Fonu</t>
+          <t>Değişken Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D1005" s="0" t="inlineStr">
         <is>
-          <t>BIST Endeks</t>
+          <t>Teknoloji Temalı</t>
         </is>
       </c>
       <c r="E1005" s="0" t="inlineStr">
         <is>
-          <t>TEB</t>
+          <t>YAPI KREDİ</t>
         </is>
       </c>
       <c r="F1005" s="0" t="inlineStr">
@@ -32509,22 +32509,22 @@
     <row outlineLevel="0" r="1006">
       <c r="A1006" s="0" t="inlineStr">
         <is>
-          <t>YZK</t>
+          <t>YZG</t>
         </is>
       </c>
       <c r="B1006" s="0" t="inlineStr">
         <is>
-          <t>YAPI KREDİ PORTFÖY KALAMIŞ SERBEST FON</t>
+          <t>YAPI KREDİ PORTFÖY GÜMÜŞ FON SEPETİ FONU</t>
         </is>
       </c>
       <c r="C1006" s="0" t="inlineStr">
         <is>
-          <t>Serbest Şemsiye Fonu</t>
+          <t>Fon Sepeti Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D1006" s="0" t="inlineStr">
         <is>
-          <t>Diğer Serbest</t>
+          <t>Gümüş</t>
         </is>
       </c>
       <c r="E1006" s="0" t="inlineStr">
@@ -32541,27 +32541,27 @@
     <row outlineLevel="0" r="1007">
       <c r="A1007" s="0" t="inlineStr">
         <is>
-          <t>YZT</t>
+          <t>YZH</t>
         </is>
       </c>
       <c r="B1007" s="0" t="inlineStr">
         <is>
-          <t>AK PORTFÖY YAPAY ZEKA TEKNOLOJİLERİ ŞİRKETLERİ DEĞİŞKEN FON</t>
+          <t>TEB PORTFÖY BIST BANKA ENDEKSİ HİSSE SENEDİ FONU (HİSSE SENEDİ YOĞUN)</t>
         </is>
       </c>
       <c r="C1007" s="0" t="inlineStr">
         <is>
-          <t>Değişken Şemsiye Fonu</t>
+          <t>Hisse Senedi Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D1007" s="0" t="inlineStr">
         <is>
-          <t>Teknoloji Temalı</t>
+          <t>BIST Endeks</t>
         </is>
       </c>
       <c r="E1007" s="0" t="inlineStr">
         <is>
-          <t>AK</t>
+          <t>TEB</t>
         </is>
       </c>
       <c r="F1007" s="0" t="inlineStr">
@@ -32573,27 +32573,27 @@
     <row outlineLevel="0" r="1008">
       <c r="A1008" s="0" t="inlineStr">
         <is>
-          <t>ZBD</t>
+          <t>YZK</t>
         </is>
       </c>
       <c r="B1008" s="0" t="inlineStr">
         <is>
-          <t>ZİRAAT PORTFÖY DENGELİ DEĞİŞKEN FON</t>
+          <t>YAPI KREDİ PORTFÖY KALAMIŞ SERBEST FON</t>
         </is>
       </c>
       <c r="C1008" s="0" t="inlineStr">
         <is>
-          <t>Değişken Şemsiye Fonu</t>
+          <t>Serbest Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D1008" s="0" t="inlineStr">
         <is>
-          <t>Değişken</t>
+          <t>Diğer Serbest</t>
         </is>
       </c>
       <c r="E1008" s="0" t="inlineStr">
         <is>
-          <t>ZİRAAT</t>
+          <t>YAPI KREDİ</t>
         </is>
       </c>
       <c r="F1008" s="0" t="inlineStr">
@@ -32605,27 +32605,27 @@
     <row outlineLevel="0" r="1009">
       <c r="A1009" s="0" t="inlineStr">
         <is>
-          <t>ZBI</t>
+          <t>YZT</t>
         </is>
       </c>
       <c r="B1009" s="0" t="inlineStr">
         <is>
-          <t>ZİRAAT PORTFÖY TEMKİNLİ KATILIM FONU</t>
+          <t>AK PORTFÖY YAPAY ZEKA TEKNOLOJİLERİ ŞİRKETLERİ DEĞİŞKEN FON</t>
         </is>
       </c>
       <c r="C1009" s="0" t="inlineStr">
         <is>
-          <t>Katılım Şemsiye Fonu</t>
+          <t>Değişken Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D1009" s="0" t="inlineStr">
         <is>
-          <t>Çoklu Varlık</t>
+          <t>Teknoloji Temalı</t>
         </is>
       </c>
       <c r="E1009" s="0" t="inlineStr">
         <is>
-          <t>ZİRAAT</t>
+          <t>AK</t>
         </is>
       </c>
       <c r="F1009" s="0" t="inlineStr">
@@ -32637,22 +32637,22 @@
     <row outlineLevel="0" r="1010">
       <c r="A1010" s="0" t="inlineStr">
         <is>
-          <t>ZBJ</t>
+          <t>ZBD</t>
         </is>
       </c>
       <c r="B1010" s="0" t="inlineStr">
         <is>
-          <t>ZİRAAT PORTFÖY BAŞAK PARA PİYASASI (TL) FONU</t>
+          <t>ZİRAAT PORTFÖY DENGELİ DEĞİŞKEN FON</t>
         </is>
       </c>
       <c r="C1010" s="0" t="inlineStr">
         <is>
-          <t>Para Piyasası Şemsiye Fonu</t>
+          <t>Değişken Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D1010" s="0" t="inlineStr">
         <is>
-          <t>Para Piyasası</t>
+          <t>Değişken</t>
         </is>
       </c>
       <c r="E1010" s="0" t="inlineStr">
@@ -32669,22 +32669,22 @@
     <row outlineLevel="0" r="1011">
       <c r="A1011" s="0" t="inlineStr">
         <is>
-          <t>ZBO</t>
+          <t>ZBI</t>
         </is>
       </c>
       <c r="B1011" s="0" t="inlineStr">
         <is>
-          <t>ZİRAAT PORTFÖY MUTLAK GETİRİ HEDEFLİ HİSSE SENEDİ SERBEST FON (HİSSE SENEDİ YOĞUN FON)</t>
+          <t>ZİRAAT PORTFÖY TEMKİNLİ KATILIM FONU</t>
         </is>
       </c>
       <c r="C1011" s="0" t="inlineStr">
         <is>
-          <t>Serbest Şemsiye Fonu</t>
+          <t>Katılım Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D1011" s="0" t="inlineStr">
         <is>
-          <t>İstatiksel Arbitraj</t>
+          <t>Çoklu Varlık</t>
         </is>
       </c>
       <c r="E1011" s="0" t="inlineStr">
@@ -32701,22 +32701,22 @@
     <row outlineLevel="0" r="1012">
       <c r="A1012" s="0" t="inlineStr">
         <is>
-          <t>ZCD</t>
+          <t>ZBJ</t>
         </is>
       </c>
       <c r="B1012" s="0" t="inlineStr">
         <is>
-          <t>ZİRAAT PORTFÖY ALTINCI SERBEST (TL) FON</t>
+          <t>ZİRAAT PORTFÖY BAŞAK PARA PİYASASI (TL) FONU</t>
         </is>
       </c>
       <c r="C1012" s="0" t="inlineStr">
         <is>
-          <t>Serbest Şemsiye Fonu</t>
+          <t>Para Piyasası Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D1012" s="0" t="inlineStr">
         <is>
-          <t>Diğer Serbest</t>
+          <t>Para Piyasası</t>
         </is>
       </c>
       <c r="E1012" s="0" t="inlineStr">
@@ -32733,22 +32733,22 @@
     <row outlineLevel="0" r="1013">
       <c r="A1013" s="0" t="inlineStr">
         <is>
-          <t>ZCK</t>
+          <t>ZBO</t>
         </is>
       </c>
       <c r="B1013" s="0" t="inlineStr">
         <is>
-          <t>ZİRAAT PORTFÖY AGRESİF KATILIM FONU</t>
+          <t>ZİRAAT PORTFÖY MUTLAK GETİRİ HEDEFLİ HİSSE SENEDİ SERBEST FON (HİSSE SENEDİ YOĞUN FON)</t>
         </is>
       </c>
       <c r="C1013" s="0" t="inlineStr">
         <is>
-          <t>Katılım Şemsiye Fonu</t>
+          <t>Serbest Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D1013" s="0" t="inlineStr">
         <is>
-          <t>Çoklu Varlık</t>
+          <t>İstatiksel Arbitraj</t>
         </is>
       </c>
       <c r="E1013" s="0" t="inlineStr">
@@ -32765,22 +32765,22 @@
     <row outlineLevel="0" r="1014">
       <c r="A1014" s="0" t="inlineStr">
         <is>
-          <t>ZCN</t>
+          <t>ZCD</t>
         </is>
       </c>
       <c r="B1014" s="0" t="inlineStr">
         <is>
-          <t>ZİRAAT PORTFÖY EMTİA FON SEPETİ FONU</t>
+          <t>ZİRAAT PORTFÖY ALTINCI SERBEST (TL) FON</t>
         </is>
       </c>
       <c r="C1014" s="0" t="inlineStr">
         <is>
-          <t>Fon Sepeti Şemsiye Fonu</t>
+          <t>Serbest Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D1014" s="0" t="inlineStr">
         <is>
-          <t>Emtia</t>
+          <t>Diğer Serbest</t>
         </is>
       </c>
       <c r="E1014" s="0" t="inlineStr">
@@ -32797,22 +32797,22 @@
     <row outlineLevel="0" r="1015">
       <c r="A1015" s="0" t="inlineStr">
         <is>
-          <t>ZDD</t>
+          <t>ZCK</t>
         </is>
       </c>
       <c r="B1015" s="0" t="inlineStr">
         <is>
-          <t>ZİRAAT PORTFÖY TEMKİNLİ DEĞİŞKEN FON</t>
+          <t>ZİRAAT PORTFÖY AGRESİF KATILIM FONU</t>
         </is>
       </c>
       <c r="C1015" s="0" t="inlineStr">
         <is>
-          <t>Değişken Şemsiye Fonu</t>
+          <t>Katılım Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D1015" s="0" t="inlineStr">
         <is>
-          <t>Değişken</t>
+          <t>Çoklu Varlık</t>
         </is>
       </c>
       <c r="E1015" s="0" t="inlineStr">
@@ -32829,22 +32829,22 @@
     <row outlineLevel="0" r="1016">
       <c r="A1016" s="0" t="inlineStr">
         <is>
-          <t>ZDZ</t>
+          <t>ZCN</t>
         </is>
       </c>
       <c r="B1016" s="0" t="inlineStr">
         <is>
-          <t>ZİRAAT PORTFÖY AGRESİF DEĞİŞKEN FON</t>
+          <t>ZİRAAT PORTFÖY EMTİA FON SEPETİ FONU</t>
         </is>
       </c>
       <c r="C1016" s="0" t="inlineStr">
         <is>
-          <t>Değişken Şemsiye Fonu</t>
+          <t>Fon Sepeti Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D1016" s="0" t="inlineStr">
         <is>
-          <t>Değişken</t>
+          <t>Emtia</t>
         </is>
       </c>
       <c r="E1016" s="0" t="inlineStr">
@@ -32861,12 +32861,12 @@
     <row outlineLevel="0" r="1017">
       <c r="A1017" s="0" t="inlineStr">
         <is>
-          <t>ZFB</t>
+          <t>ZDD</t>
         </is>
       </c>
       <c r="B1017" s="0" t="inlineStr">
         <is>
-          <t>AK PORTFÖY FİNTEK VE BLOKZİNCİRİ TEKNOLOJİLERİ DEĞİŞKEN FON</t>
+          <t>ZİRAAT PORTFÖY TEMKİNLİ DEĞİŞKEN FON</t>
         </is>
       </c>
       <c r="C1017" s="0" t="inlineStr">
@@ -32876,12 +32876,12 @@
       </c>
       <c r="D1017" s="0" t="inlineStr">
         <is>
-          <t>Teknoloji Temalı</t>
+          <t>Değişken</t>
         </is>
       </c>
       <c r="E1017" s="0" t="inlineStr">
         <is>
-          <t>AK</t>
+          <t>ZİRAAT</t>
         </is>
       </c>
       <c r="F1017" s="0" t="inlineStr">
@@ -32893,22 +32893,22 @@
     <row outlineLevel="0" r="1018">
       <c r="A1018" s="0" t="inlineStr">
         <is>
-          <t>ZHH</t>
+          <t>ZDZ</t>
         </is>
       </c>
       <c r="B1018" s="0" t="inlineStr">
         <is>
-          <t>ZİRAAT PORTFÖY HALKBANK SÜRDÜRÜLEBİLİRLİK 30 ŞİRKETLERİ HİSSE SENEDİ FONU (HİSSE SENEDİ YOĞUN FON)</t>
+          <t>ZİRAAT PORTFÖY AGRESİF DEĞİŞKEN FON</t>
         </is>
       </c>
       <c r="C1018" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi Şemsiye Fonu</t>
+          <t>Değişken Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D1018" s="0" t="inlineStr">
         <is>
-          <t>BIST Endeks</t>
+          <t>Değişken</t>
         </is>
       </c>
       <c r="E1018" s="0" t="inlineStr">
@@ -32925,27 +32925,27 @@
     <row outlineLevel="0" r="1019">
       <c r="A1019" s="0" t="inlineStr">
         <is>
-          <t>ZJB</t>
+          <t>ZFB</t>
         </is>
       </c>
       <c r="B1019" s="0" t="inlineStr">
         <is>
-          <t>ZİRAAT PORTFÖY BİRİNCİ SERBEST (TL) FON</t>
+          <t>AK PORTFÖY FİNTEK VE BLOKZİNCİRİ TEKNOLOJİLERİ DEĞİŞKEN FON</t>
         </is>
       </c>
       <c r="C1019" s="0" t="inlineStr">
         <is>
-          <t>Serbest Şemsiye Fonu</t>
+          <t>Değişken Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D1019" s="0" t="inlineStr">
         <is>
-          <t>Diğer Serbest</t>
+          <t>Teknoloji Temalı</t>
         </is>
       </c>
       <c r="E1019" s="0" t="inlineStr">
         <is>
-          <t>ZİRAAT</t>
+          <t>AK</t>
         </is>
       </c>
       <c r="F1019" s="0" t="inlineStr">
@@ -32957,22 +32957,22 @@
     <row outlineLevel="0" r="1020">
       <c r="A1020" s="0" t="inlineStr">
         <is>
-          <t>ZJI</t>
+          <t>ZHH</t>
         </is>
       </c>
       <c r="B1020" s="0" t="inlineStr">
         <is>
-          <t>ZİRAAT PORTFÖY İKİNCİ SERBEST (TL) FON</t>
+          <t>ZİRAAT PORTFÖY HALKBANK SÜRDÜRÜLEBİLİRLİK 30 ŞİRKETLERİ HİSSE SENEDİ FONU (HİSSE SENEDİ YOĞUN FON)</t>
         </is>
       </c>
       <c r="C1020" s="0" t="inlineStr">
         <is>
-          <t>Serbest Şemsiye Fonu</t>
+          <t>Hisse Senedi Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D1020" s="0" t="inlineStr">
         <is>
-          <t>Diğer Serbest</t>
+          <t>BIST Endeks</t>
         </is>
       </c>
       <c r="E1020" s="0" t="inlineStr">
@@ -32989,22 +32989,22 @@
     <row outlineLevel="0" r="1021">
       <c r="A1021" s="0" t="inlineStr">
         <is>
-          <t>ZJL</t>
+          <t>ZJB</t>
         </is>
       </c>
       <c r="B1021" s="0" t="inlineStr">
         <is>
-          <t>ZİRAAT PORTFÖY BIST 100 DIŞI ŞİRKETLER HİSSE SENEDİ FONU (HİSSE SENEDİ YOĞUN FON)</t>
+          <t>ZİRAAT PORTFÖY BİRİNCİ SERBEST (TL) FON</t>
         </is>
       </c>
       <c r="C1021" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi Şemsiye Fonu</t>
+          <t>Serbest Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D1021" s="0" t="inlineStr">
         <is>
-          <t>BIST Endeks</t>
+          <t>Diğer Serbest</t>
         </is>
       </c>
       <c r="E1021" s="0" t="inlineStr">
@@ -33021,22 +33021,22 @@
     <row outlineLevel="0" r="1022">
       <c r="A1022" s="0" t="inlineStr">
         <is>
-          <t>ZJV</t>
+          <t>ZJI</t>
         </is>
       </c>
       <c r="B1022" s="0" t="inlineStr">
         <is>
-          <t>ZİRAAT PORTFÖY BIST 30 DIŞI YILDIZ PAZAR ŞİRKETLERİ HİSSE SENEDİ FONU (HİSSE SENEDİ YOĞUN FON)</t>
+          <t>ZİRAAT PORTFÖY İKİNCİ SERBEST (TL) FON</t>
         </is>
       </c>
       <c r="C1022" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi Şemsiye Fonu</t>
+          <t>Serbest Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D1022" s="0" t="inlineStr">
         <is>
-          <t>BIST Endeks</t>
+          <t>Diğer Serbest</t>
         </is>
       </c>
       <c r="E1022" s="0" t="inlineStr">
@@ -33053,12 +33053,12 @@
     <row outlineLevel="0" r="1023">
       <c r="A1023" s="0" t="inlineStr">
         <is>
-          <t>ZLH</t>
+          <t>ZJL</t>
         </is>
       </c>
       <c r="B1023" s="0" t="inlineStr">
         <is>
-          <t>ZİRAAT PORTFÖY BIST 100-30 ŞİRKETLERİ HİSSE SENEDİ FONU ( HİSSE SENEDİ YOĞUN FON)</t>
+          <t>ZİRAAT PORTFÖY BIST 100 DIŞI ŞİRKETLER HİSSE SENEDİ FONU (HİSSE SENEDİ YOĞUN FON)</t>
         </is>
       </c>
       <c r="C1023" s="0" t="inlineStr">
@@ -33085,54 +33085,54 @@
     <row outlineLevel="0" r="1024">
       <c r="A1024" s="0" t="inlineStr">
         <is>
-          <t>ZMT</t>
+          <t>ZJV</t>
         </is>
       </c>
       <c r="B1024" s="0" t="inlineStr">
         <is>
-          <t>AZİMUT PORTFÖY 22.0 SERBEST (DÖVİZ-AVRO) FON</t>
+          <t>ZİRAAT PORTFÖY BIST 30 DIŞI YILDIZ PAZAR ŞİRKETLERİ HİSSE SENEDİ FONU (HİSSE SENEDİ YOĞUN FON)</t>
         </is>
       </c>
       <c r="C1024" s="0" t="inlineStr">
         <is>
-          <t>Serbest Şemsiye Fonu</t>
+          <t>Hisse Senedi Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D1024" s="0" t="inlineStr">
         <is>
-          <t>Döviz</t>
+          <t>BIST Endeks</t>
         </is>
       </c>
       <c r="E1024" s="0" t="inlineStr">
         <is>
-          <t>AZİMUT</t>
+          <t>ZİRAAT</t>
         </is>
       </c>
       <c r="F1024" s="0" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>TL</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="1025">
       <c r="A1025" s="0" t="inlineStr">
         <is>
-          <t>ZMY</t>
+          <t>ZLH</t>
         </is>
       </c>
       <c r="B1025" s="0" t="inlineStr">
         <is>
-          <t>ZİRAAT PORTFÖY METAVERSE VE YENİ TEKNOLOJİLER DEĞİŞKEN FON</t>
+          <t>ZİRAAT PORTFÖY BIST 100-30 ŞİRKETLERİ HİSSE SENEDİ FONU ( HİSSE SENEDİ YOĞUN FON)</t>
         </is>
       </c>
       <c r="C1025" s="0" t="inlineStr">
         <is>
-          <t>Değişken Şemsiye Fonu</t>
+          <t>Hisse Senedi Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D1025" s="0" t="inlineStr">
         <is>
-          <t>Teknoloji Temalı</t>
+          <t>BIST Endeks</t>
         </is>
       </c>
       <c r="E1025" s="0" t="inlineStr">
@@ -33149,12 +33149,12 @@
     <row outlineLevel="0" r="1026">
       <c r="A1026" s="0" t="inlineStr">
         <is>
-          <t>ZP6</t>
+          <t>ZMT</t>
         </is>
       </c>
       <c r="B1026" s="0" t="inlineStr">
         <is>
-          <t>ZİRAAT PORTFÖY SEDEF KATILIM SERBEST (DÖVİZ - AMERİKAN DOLARI) FON</t>
+          <t>AZİMUT PORTFÖY 22.0 SERBEST (DÖVİZ-AVRO) FON</t>
         </is>
       </c>
       <c r="C1026" s="0" t="inlineStr">
@@ -33169,34 +33169,34 @@
       </c>
       <c r="E1026" s="0" t="inlineStr">
         <is>
-          <t>ZİRAAT</t>
+          <t>AZİMUT</t>
         </is>
       </c>
       <c r="F1026" s="0" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="1027">
       <c r="A1027" s="0" t="inlineStr">
         <is>
-          <t>ZP8</t>
+          <t>ZMY</t>
         </is>
       </c>
       <c r="B1027" s="0" t="inlineStr">
         <is>
-          <t>ZİRAAT PORTFÖY KEHRİBAR PARA PİYASASI KATILIM SERBEST (TL) FON</t>
+          <t>ZİRAAT PORTFÖY METAVERSE VE YENİ TEKNOLOJİLER DEĞİŞKEN FON</t>
         </is>
       </c>
       <c r="C1027" s="0" t="inlineStr">
         <is>
-          <t>Serbest Şemsiye Fonu</t>
+          <t>Değişken Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D1027" s="0" t="inlineStr">
         <is>
-          <t>Para Piyasası</t>
+          <t>Teknoloji Temalı</t>
         </is>
       </c>
       <c r="E1027" s="0" t="inlineStr">
@@ -33213,12 +33213,12 @@
     <row outlineLevel="0" r="1028">
       <c r="A1028" s="0" t="inlineStr">
         <is>
-          <t>ZP9</t>
+          <t>ZP6</t>
         </is>
       </c>
       <c r="B1028" s="0" t="inlineStr">
         <is>
-          <t>ZİRAAT PORTFÖY AKİK KATILIM SERBEST (DÖVİZ-AVRO) FON</t>
+          <t>ZİRAAT PORTFÖY SEDEF KATILIM SERBEST (DÖVİZ - AMERİKAN DOLARI) FON</t>
         </is>
       </c>
       <c r="C1028" s="0" t="inlineStr">
@@ -33238,19 +33238,19 @@
       </c>
       <c r="F1028" s="0" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="1029">
       <c r="A1029" s="0" t="inlineStr">
         <is>
-          <t>ZPA</t>
+          <t>ZP8</t>
         </is>
       </c>
       <c r="B1029" s="0" t="inlineStr">
         <is>
-          <t>ZİRAAT PORTFÖY SERBEST (DÖVİZ) FON</t>
+          <t>ZİRAAT PORTFÖY KEHRİBAR PARA PİYASASI KATILIM SERBEST (TL) FON</t>
         </is>
       </c>
       <c r="C1029" s="0" t="inlineStr">
@@ -33260,7 +33260,7 @@
       </c>
       <c r="D1029" s="0" t="inlineStr">
         <is>
-          <t>Döviz</t>
+          <t>Para Piyasası</t>
         </is>
       </c>
       <c r="E1029" s="0" t="inlineStr">
@@ -33270,29 +33270,29 @@
       </c>
       <c r="F1029" s="0" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>TL</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="1030">
       <c r="A1030" s="0" t="inlineStr">
         <is>
-          <t>ZPC</t>
+          <t>ZP9</t>
         </is>
       </c>
       <c r="B1030" s="0" t="inlineStr">
         <is>
-          <t>ZİRAAT PORTFÖY FON SEPETİ FONU</t>
+          <t>ZİRAAT PORTFÖY AKİK KATILIM SERBEST (DÖVİZ-AVRO) FON</t>
         </is>
       </c>
       <c r="C1030" s="0" t="inlineStr">
         <is>
-          <t>Fon Sepeti Şemsiye Fonu</t>
+          <t>Serbest Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D1030" s="0" t="inlineStr">
         <is>
-          <t>Fon Sepeti</t>
+          <t>Döviz</t>
         </is>
       </c>
       <c r="E1030" s="0" t="inlineStr">
@@ -33302,29 +33302,29 @@
       </c>
       <c r="F1030" s="0" t="inlineStr">
         <is>
-          <t>TL</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="1031">
       <c r="A1031" s="0" t="inlineStr">
         <is>
-          <t>ZPE</t>
+          <t>ZPA</t>
         </is>
       </c>
       <c r="B1031" s="0" t="inlineStr">
         <is>
-          <t>ZİRAAT PORTFÖY KATILIM HİSSE SENEDİ FONU (HİSSE SENEDİ YOĞUN FON)</t>
+          <t>ZİRAAT PORTFÖY SERBEST (DÖVİZ) FON</t>
         </is>
       </c>
       <c r="C1031" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi Şemsiye Fonu</t>
+          <t>Serbest Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D1031" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi</t>
+          <t>Döviz</t>
         </is>
       </c>
       <c r="E1031" s="0" t="inlineStr">
@@ -33334,29 +33334,29 @@
       </c>
       <c r="F1031" s="0" t="inlineStr">
         <is>
-          <t>TL</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="1032">
       <c r="A1032" s="0" t="inlineStr">
         <is>
-          <t>ZPF</t>
+          <t>ZPC</t>
         </is>
       </c>
       <c r="B1032" s="0" t="inlineStr">
         <is>
-          <t>ZİRAAT PORTFÖY KATILIM FONU (DÖVİZ)</t>
+          <t>ZİRAAT PORTFÖY FON SEPETİ FONU</t>
         </is>
       </c>
       <c r="C1032" s="0" t="inlineStr">
         <is>
-          <t>Katılım Şemsiye Fonu</t>
+          <t>Fon Sepeti Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D1032" s="0" t="inlineStr">
         <is>
-          <t>Döviz</t>
+          <t>Fon Sepeti</t>
         </is>
       </c>
       <c r="E1032" s="0" t="inlineStr">
@@ -33366,29 +33366,29 @@
       </c>
       <c r="F1032" s="0" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>TL</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="1033">
       <c r="A1033" s="0" t="inlineStr">
         <is>
-          <t>ZPG</t>
+          <t>ZPE</t>
         </is>
       </c>
       <c r="B1033" s="0" t="inlineStr">
         <is>
-          <t>ZİRAAT PORTFÖY KİRA SERTİFİKALARI (SUKUK) KATILIM FONU</t>
+          <t>ZİRAAT PORTFÖY KATILIM HİSSE SENEDİ FONU (HİSSE SENEDİ YOĞUN FON)</t>
         </is>
       </c>
       <c r="C1033" s="0" t="inlineStr">
         <is>
-          <t>Katılım Şemsiye Fonu</t>
+          <t>Hisse Senedi Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D1033" s="0" t="inlineStr">
         <is>
-          <t>Kira Sertifikası</t>
+          <t>Hisse Senedi</t>
         </is>
       </c>
       <c r="E1033" s="0" t="inlineStr">
@@ -33405,12 +33405,12 @@
     <row outlineLevel="0" r="1034">
       <c r="A1034" s="0" t="inlineStr">
         <is>
-          <t>ZPO</t>
+          <t>ZPF</t>
         </is>
       </c>
       <c r="B1034" s="0" t="inlineStr">
         <is>
-          <t>ZİRAAT PORTFÖY PARA PİYASASI KATILIM FONU</t>
+          <t>ZİRAAT PORTFÖY KATILIM FONU (DÖVİZ)</t>
         </is>
       </c>
       <c r="C1034" s="0" t="inlineStr">
@@ -33420,7 +33420,7 @@
       </c>
       <c r="D1034" s="0" t="inlineStr">
         <is>
-          <t>Para Piyasası</t>
+          <t>Döviz</t>
         </is>
       </c>
       <c r="E1034" s="0" t="inlineStr">
@@ -33430,29 +33430,29 @@
       </c>
       <c r="F1034" s="0" t="inlineStr">
         <is>
-          <t>TL</t>
+          <t>USD</t>
         </is>
       </c>
     </row>
     <row outlineLevel="0" r="1035">
       <c r="A1035" s="0" t="inlineStr">
         <is>
-          <t>ZPR</t>
+          <t>ZPG</t>
         </is>
       </c>
       <c r="B1035" s="0" t="inlineStr">
         <is>
-          <t>ZİRAAT PORTFÖY PARA PİYASASI SERBEST FON</t>
+          <t>ZİRAAT PORTFÖY KİRA SERTİFİKALARI (SUKUK) KATILIM FONU</t>
         </is>
       </c>
       <c r="C1035" s="0" t="inlineStr">
         <is>
-          <t>Serbest Şemsiye Fonu</t>
+          <t>Katılım Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D1035" s="0" t="inlineStr">
         <is>
-          <t>Para Piyasası</t>
+          <t>Kira Sertifikası</t>
         </is>
       </c>
       <c r="E1035" s="0" t="inlineStr">
@@ -33469,22 +33469,22 @@
     <row outlineLevel="0" r="1036">
       <c r="A1036" s="0" t="inlineStr">
         <is>
-          <t>ZSF</t>
+          <t>ZPO</t>
         </is>
       </c>
       <c r="B1036" s="0" t="inlineStr">
         <is>
-          <t>ZİRAAT PORTFÖY S&amp;P/OIC COMCEC (İSEDAK) 50 SHARİAH ŞİRKETLERİ YABANCI HİSSE SENEDİ FONU</t>
+          <t>ZİRAAT PORTFÖY PARA PİYASASI KATILIM FONU</t>
         </is>
       </c>
       <c r="C1036" s="0" t="inlineStr">
         <is>
-          <t>Hisse Senedi Şemsiye Fonu</t>
+          <t>Katılım Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D1036" s="0" t="inlineStr">
         <is>
-          <t>Tematik</t>
+          <t>Para Piyasası</t>
         </is>
       </c>
       <c r="E1036" s="0" t="inlineStr">
@@ -33501,22 +33501,22 @@
     <row outlineLevel="0" r="1037">
       <c r="A1037" s="0" t="inlineStr">
         <is>
-          <t>ZSG</t>
+          <t>ZPR</t>
         </is>
       </c>
       <c r="B1037" s="0" t="inlineStr">
         <is>
-          <t>ZİRAAT PORTFÖY ESG SÜRDÜRÜLEBİLİRLİK FON SEPETİ FONU</t>
+          <t>ZİRAAT PORTFÖY PARA PİYASASI SERBEST FON</t>
         </is>
       </c>
       <c r="C1037" s="0" t="inlineStr">
         <is>
-          <t>Fon Sepeti Şemsiye Fonu</t>
+          <t>Serbest Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D1037" s="0" t="inlineStr">
         <is>
-          <t>Tematik</t>
+          <t>Para Piyasası</t>
         </is>
       </c>
       <c r="E1037" s="0" t="inlineStr">
@@ -33533,17 +33533,17 @@
     <row outlineLevel="0" r="1038">
       <c r="A1038" s="0" t="inlineStr">
         <is>
-          <t>ZTG</t>
+          <t>ZSF</t>
         </is>
       </c>
       <c r="B1038" s="0" t="inlineStr">
         <is>
-          <t>ZİRAAT PORTFÖY TARIM VE GIDA FON SEPETİ FONU</t>
+          <t>ZİRAAT PORTFÖY S&amp;P/OIC COMCEC (İSEDAK) 50 SHARİAH ŞİRKETLERİ YABANCI HİSSE SENEDİ FONU</t>
         </is>
       </c>
       <c r="C1038" s="0" t="inlineStr">
         <is>
-          <t>Fon Sepeti Şemsiye Fonu</t>
+          <t>Hisse Senedi Şemsiye Fonu</t>
         </is>
       </c>
       <c r="D1038" s="0" t="inlineStr">
@@ -33565,30 +33565,94 @@
     <row outlineLevel="0" r="1039">
       <c r="A1039" s="0" t="inlineStr">
         <is>
+          <t>ZSG</t>
+        </is>
+      </c>
+      <c r="B1039" s="0" t="inlineStr">
+        <is>
+          <t>ZİRAAT PORTFÖY ESG SÜRDÜRÜLEBİLİRLİK FON SEPETİ FONU</t>
+        </is>
+      </c>
+      <c r="C1039" s="0" t="inlineStr">
+        <is>
+          <t>Fon Sepeti Şemsiye Fonu</t>
+        </is>
+      </c>
+      <c r="D1039" s="0" t="inlineStr">
+        <is>
+          <t>Tematik</t>
+        </is>
+      </c>
+      <c r="E1039" s="0" t="inlineStr">
+        <is>
+          <t>ZİRAAT</t>
+        </is>
+      </c>
+      <c r="F1039" s="0" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="1040">
+      <c r="A1040" s="0" t="inlineStr">
+        <is>
+          <t>ZTG</t>
+        </is>
+      </c>
+      <c r="B1040" s="0" t="inlineStr">
+        <is>
+          <t>ZİRAAT PORTFÖY TARIM VE GIDA FON SEPETİ FONU</t>
+        </is>
+      </c>
+      <c r="C1040" s="0" t="inlineStr">
+        <is>
+          <t>Fon Sepeti Şemsiye Fonu</t>
+        </is>
+      </c>
+      <c r="D1040" s="0" t="inlineStr">
+        <is>
+          <t>Tematik</t>
+        </is>
+      </c>
+      <c r="E1040" s="0" t="inlineStr">
+        <is>
+          <t>ZİRAAT</t>
+        </is>
+      </c>
+      <c r="F1040" s="0" t="inlineStr">
+        <is>
+          <t>TL</t>
+        </is>
+      </c>
+    </row>
+    <row outlineLevel="0" r="1041">
+      <c r="A1041" s="0" t="inlineStr">
+        <is>
           <t>ZVO</t>
         </is>
       </c>
-      <c r="B1039" s="0" t="inlineStr">
+      <c r="B1041" s="0" t="inlineStr">
         <is>
           <t>ZİRAAT PORTFÖY ÜÇÜNCÜ SERBEST (TL) FON</t>
         </is>
       </c>
-      <c r="C1039" s="0" t="inlineStr">
-        <is>
-          <t>Serbest Şemsiye Fonu</t>
-        </is>
-      </c>
-      <c r="D1039" s="0" t="inlineStr">
+      <c r="C1041" s="0" t="inlineStr">
+        <is>
+          <t>Serbest Şemsiye Fonu</t>
+        </is>
+      </c>
+      <c r="D1041" s="0" t="inlineStr">
         <is>
           <t>Diğer Serbest</t>
         </is>
       </c>
-      <c r="E1039" s="0" t="inlineStr">
+      <c r="E1041" s="0" t="inlineStr">
         <is>
           <t>ZİRAAT</t>
         </is>
       </c>
-      <c r="F1039" s="0" t="inlineStr">
+      <c r="F1041" s="0" t="inlineStr">
         <is>
           <t>TL</t>
         </is>
